--- a/annotators/preanno_parcor_coref/de/raw/cbsnews.146237.xlsx
+++ b/annotators/preanno_parcor_coref/de/raw/cbsnews.146237.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="347">
   <si>
     <t>ID</t>
   </si>
@@ -50,7 +50,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>34</t>
+    <t>13</t>
   </si>
   <si>
     <t>_</t>
@@ -59,7 +59,7 @@
     <t>erschießen</t>
   </si>
   <si>
-    <t>Polizei : 3 Opfer in Serienmörderfall beim bei dem Musikhören im in dem Auto erschossen Laut Polizeiberichten , die am an dem Donnerstag veröffentlicht wurden , wurden zwei Frauen und ein 12 Jahre altes Mädchen erschossen , die in einem der tödlichsten Angriffe seit einem Jahrzehnt im in dem ersten Serienmörderfall von Phoenix umgekommen sind , während sie sich im in dem Auto unterhielten und Musik hörten .</t>
+    <t>Polizei : 3 Opfer in Serienmörderfall beim bei dem Musikhören im in dem Auto erschossen</t>
   </si>
   <si>
     <t>file://conllu/de/cbsnews.146237.conllu#s1_0</t>
@@ -68,6 +68,18 @@
     <t>2</t>
   </si>
   <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>Laut Polizeiberichten , die am an dem Donnerstag veröffentlicht wurden , wurden zwei Frauen und ein 12 Jahre altes Mädchen erschossen , die in einem der tödlichsten Angriffe seit einem Jahrzehnt im in dem ersten Serienmörderfall von Phoenix umgekommen sind , während sie sich im in dem Auto unterhielten und Musik hörten .</t>
+  </si>
+  <si>
+    <t>file://conllu/de/cbsnews.146237.conllu#s2_0</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>12</t>
   </si>
   <si>
@@ -77,13 +89,10 @@
     <t>Angela Rochelle Liner , Stefanie R. Ellis and Ellis Tochter Maleah wurden am an dem 12 .</t>
   </si>
   <si>
-    <t>file://conllu/de/cbsnews.146237.conllu#s2_0</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>file://conllu/de/cbsnews.146237.conllu#s3_0</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>sagen</t>
@@ -92,10 +101,10 @@
     <t>Juni erschossen , während das Auto in einer Einfahrt geparkt war , sagten die Behörden .</t>
   </si>
   <si>
-    <t>file://conllu/de/cbsnews.146237.conllu#s3_0</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>file://conllu/de/cbsnews.146237.conllu#s4_0</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
   <si>
     <t>feueren</t>
@@ -104,10 +113,10 @@
     <t>Der Täter feuerte acht Schüsse aus einer Handfeuerwaffe , während er auf der Beifahrerseite des Autos stand und floh anschließend mit einem anderen Fahrzeug , ist im in dem Bericht zu lesen .</t>
   </si>
   <si>
-    <t>file://conllu/de/cbsnews.146237.conllu#s4_0</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>file://conllu/de/cbsnews.146237.conllu#s5_0</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
   <si>
     <t>teilen</t>
@@ -116,10 +125,10 @@
     <t>Die Polizei teilte mit , dass der dreifache Mord nicht das Ergebnis eines Raubüberfalles gewesen zu sein scheint , da der Angreifer nicht die Handtaschen oder die $ 2.900 mitnahm , die sich im in dem Besitz einer der erwachsenen Opfer befanden .</t>
   </si>
   <si>
-    <t>file://conllu/de/cbsnews.146237.conllu#s5_0</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>file://conllu/de/cbsnews.146237.conllu#s6_0</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
   <si>
     <t>Polizeisprecher</t>
@@ -128,19 +137,19 @@
     <t>Der Polizeisprecher von Phoenix Sgt .</t>
   </si>
   <si>
-    <t>file://conllu/de/cbsnews.146237.conllu#s6_0</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>file://conllu/de/cbsnews.146237.conllu#s7_0</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>Jonathan Howard sagte , dass die Schießerei die Ermittler dazu verleitete , einen näheren Blick darauf zu werden , ob sie mit vier vorherigen Angriffen verbunden ist .</t>
   </si>
   <si>
-    <t>file://conllu/de/cbsnews.146237.conllu#s7_0</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>file://conllu/de/cbsnews.146237.conllu#s8_0</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>16</t>
@@ -152,10 +161,10 @@
     <t>Insgesamt wurden vorwiegend in hispanischen Wohngegenden innerhalb von vier Monaten in neun Angriffen sieben Personen getötet und zwei weitere verletzt .</t>
   </si>
   <si>
-    <t>file://conllu/de/cbsnews.146237.conllu#s8_0</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>file://conllu/de/cbsnews.146237.conllu#s9_0</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>geschehen</t>
@@ -164,10 +173,10 @@
     <t>&amp;quot; Es geschieht in einer Wohngegend vor einem Haus , &amp;quot; teilte Howard der KHPO , einer Tochtergesellschaft von CBS , Anfang des Monats mit .</t>
   </si>
   <si>
-    <t>file://conllu/de/cbsnews.146237.conllu#s9_0</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>file://conllu/de/cbsnews.146237.conllu#s10_0</t>
+  </si>
+  <si>
+    <t>11</t>
   </si>
   <si>
     <t>annehmen</t>
@@ -176,10 +185,7 @@
     <t>Es wird angenommen , dass der Verdächtige mehrere Fahrzeuge benutzt hat , einschließlich eines braunen Nissans aus den späten 1990ern , einem schwarzen BMW aus den späten 1990ern und einem weißen Cadillac oder Lincoln .</t>
   </si>
   <si>
-    <t>file://conllu/de/cbsnews.146237.conllu#s10_0</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>file://conllu/de/cbsnews.146237.conllu#s11_0</t>
   </si>
   <si>
     <t>weigern</t>
@@ -188,7 +194,7 @@
     <t>Die Ermittler weigerten sich , die Beweise offenzulegen , die sie zu der Schlußfolgerung geführt haben , dass die Angriffe verknüpft sind und von dem selben Mörder begangen wurden .</t>
   </si>
   <si>
-    <t>file://conllu/de/cbsnews.146237.conllu#s11_0</t>
+    <t>file://conllu/de/cbsnews.146237.conllu#s12_0</t>
   </si>
   <si>
     <t>hospitalisieren</t>
@@ -197,7 +203,10 @@
     <t>Ellis , 33 , wurde aufgrund ihrer Verletzungen hospitalisiert und verstarb später .</t>
   </si>
   <si>
-    <t>file://conllu/de/cbsnews.146237.conllu#s12_0</t>
+    <t>file://conllu/de/cbsnews.146237.conllu#s13_0</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
   <si>
     <t>verstarben</t>
@@ -206,19 +215,16 @@
     <t>Liner , 31 , und Ellis Tochter Maleah verstarben noch vor Ort .</t>
   </si>
   <si>
-    <t>file://conllu/de/cbsnews.146237.conllu#s13_0</t>
-  </si>
-  <si>
-    <t>14</t>
+    <t>file://conllu/de/cbsnews.146237.conllu#s14_0</t>
+  </si>
+  <si>
+    <t>15</t>
   </si>
   <si>
     <t>Ein Zeuge teilte der Polizei mit , dass es für sie nicht ungewöhnlich war , in einem geparkten Auto zu sitzen und Musik zu hören .</t>
   </si>
   <si>
-    <t>file://conllu/de/cbsnews.146237.conllu#s14_0</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>file://conllu/de/cbsnews.146237.conllu#s15_0</t>
   </si>
   <si>
     <t>veröffentlichen</t>
@@ -227,7 +233,10 @@
     <t>Die Behörden veröffentlichten auch einen Polizeibericht über die Schießerei , die auf einen leeren Pickup Truck eine halbe Stunde vor dem dreifachen Mord abzielte und von dem ausgegangen wird , dass es das Werk des Serienmörders war .</t>
   </si>
   <si>
-    <t>file://conllu/de/cbsnews.146237.conllu#s15_0</t>
+    <t>file://conllu/de/cbsnews.146237.conllu#s16_0</t>
+  </si>
+  <si>
+    <t>17</t>
   </si>
   <si>
     <t>finden</t>
@@ -236,7 +245,7 @@
     <t>Ermittler fanden Patronenhülsen und sicherten eine Kugel aus dem Sitz sowie Kugelfragmente aus dem Motorraum .</t>
   </si>
   <si>
-    <t>file://conllu/de/cbsnews.146237.conllu#s16_0</t>
+    <t>file://conllu/de/cbsnews.146237.conllu#s17_0</t>
   </si>
   <si>
     <t>WORD</t>
@@ -272,232 +281,235 @@
     <t>REF_DIST_ANTE</t>
   </si>
   <si>
-    <t># text = Polizei: 3 Opfer in Serienmörderfall beim Musikhören im Auto erschossen Laut Polizeiberichten, die am Donnerstag veröffentlicht wurden, wurden zwei Frauen und ein 12-Jahre altes Mädchen erschossen, die in einem der tödlichsten Angriffe seit einem Jahrzehnt im ersten Serienmörderfall von Phoenix umgekommen sind, während sie sich im Auto unterhielten und Musik hörten.</t>
+    <t># text = Polizei: 3 Opfer in Serienmörderfall beim Musikhören im Auto erschossen</t>
   </si>
   <si>
     <t>Polizei</t>
   </si>
   <si>
+    <t>SBJ</t>
+  </si>
+  <si>
+    <t>indef-np.bare</t>
+  </si>
+  <si>
+    <t>:</t>
+  </si>
+  <si>
+    <t>Opfer</t>
+  </si>
+  <si>
+    <t>OBJ</t>
+  </si>
+  <si>
+    <t>indef-np.quant</t>
+  </si>
+  <si>
+    <t>in</t>
+  </si>
+  <si>
+    <t>Serienmörderfall</t>
+  </si>
+  <si>
+    <t>other_2</t>
+  </si>
+  <si>
+    <t>bei</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>Musikhören</t>
+  </si>
+  <si>
+    <t>other_3</t>
+  </si>
+  <si>
+    <t>def-np.the</t>
+  </si>
+  <si>
+    <t>?OLD</t>
+  </si>
+  <si>
+    <t>Auto</t>
+  </si>
+  <si>
+    <t>other_4</t>
+  </si>
+  <si>
+    <t>erschossen</t>
+  </si>
+  <si>
+    <t># text = Laut Polizeiberichten, die am Donnerstag veröffentlicht wurden, wurden zwei Frauen und ein 12-Jahre altes Mädchen erschossen, die in einem der tödlichsten Angriffe seit einem Jahrzehnt im ersten Serienmörderfall von Phoenix umgekommen sind, während sie sich im Auto unterhielten und Musik hörten.</t>
+  </si>
+  <si>
+    <t>Laut</t>
+  </si>
+  <si>
+    <t>Polizeiberichten</t>
+  </si>
+  <si>
     <t>other</t>
   </si>
   <si>
-    <t>indef-np.bare</t>
-  </si>
-  <si>
-    <t>:</t>
-  </si>
-  <si>
-    <t>Opfer</t>
-  </si>
-  <si>
-    <t>SBJ</t>
-  </si>
-  <si>
-    <t>indef-np.quant</t>
-  </si>
-  <si>
-    <t>in</t>
-  </si>
-  <si>
-    <t>Serienmörderfall</t>
-  </si>
-  <si>
-    <t>other_2</t>
-  </si>
-  <si>
-    <t>bei</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>Musikhören</t>
-  </si>
-  <si>
-    <t>def-np.the</t>
-  </si>
-  <si>
-    <t>?OLD</t>
-  </si>
-  <si>
-    <t>Auto</t>
-  </si>
-  <si>
-    <t>other_3</t>
-  </si>
-  <si>
-    <t>erschossen</t>
-  </si>
-  <si>
-    <t>Laut</t>
-  </si>
-  <si>
-    <t>Polizeiberichten</t>
-  </si>
-  <si>
     <t>,</t>
   </si>
   <si>
     <t>die</t>
   </si>
   <si>
+    <t>SBJ_3</t>
+  </si>
+  <si>
+    <t>an</t>
+  </si>
+  <si>
+    <t>Donnerstag</t>
+  </si>
+  <si>
+    <t>ne</t>
+  </si>
+  <si>
+    <t>veröffentlicht</t>
+  </si>
+  <si>
+    <t>wurden</t>
+  </si>
+  <si>
+    <t>zwei</t>
+  </si>
+  <si>
+    <t>Frauen</t>
+  </si>
+  <si>
+    <t>und</t>
+  </si>
+  <si>
+    <t>ein</t>
+  </si>
+  <si>
+    <t>Jahre</t>
+  </si>
+  <si>
+    <t>altes</t>
+  </si>
+  <si>
+    <t>Mädchen</t>
+  </si>
+  <si>
+    <t>indef-np.a</t>
+  </si>
+  <si>
+    <t>SBJ_2</t>
+  </si>
+  <si>
+    <t>einem</t>
+  </si>
+  <si>
+    <t>pron.pind</t>
+  </si>
+  <si>
+    <t>der</t>
+  </si>
+  <si>
+    <t>tödlichsten</t>
+  </si>
+  <si>
+    <t>Angriffe</t>
+  </si>
+  <si>
+    <t>seit</t>
+  </si>
+  <si>
+    <t>Jahrzehnt</t>
+  </si>
+  <si>
+    <t>ersten</t>
+  </si>
+  <si>
+    <t>von</t>
+  </si>
+  <si>
+    <t>Phoenix</t>
+  </si>
+  <si>
+    <t>umgekommen</t>
+  </si>
+  <si>
+    <t>sind</t>
+  </si>
+  <si>
+    <t>während</t>
+  </si>
+  <si>
+    <t>sie</t>
+  </si>
+  <si>
+    <t>pron</t>
+  </si>
+  <si>
+    <t>sich</t>
+  </si>
+  <si>
+    <t>OBJ_3</t>
+  </si>
+  <si>
+    <t>unterhielten</t>
+  </si>
+  <si>
+    <t>Musik</t>
+  </si>
+  <si>
+    <t>OBJ_4</t>
+  </si>
+  <si>
+    <t>hörten</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t># text = Angela Rochelle Liner, Stefanie R. Ellis and Ellis Tochter Maleah wurden am 12.</t>
+  </si>
+  <si>
+    <t>Angela</t>
+  </si>
+  <si>
+    <t>Rochelle</t>
+  </si>
+  <si>
+    <t>Liner</t>
+  </si>
+  <si>
+    <t>Stefanie</t>
+  </si>
+  <si>
+    <t>R.</t>
+  </si>
+  <si>
+    <t>Ellis</t>
+  </si>
+  <si>
+    <t>and</t>
+  </si>
+  <si>
+    <t>Tochter</t>
+  </si>
+  <si>
+    <t>Maleah</t>
+  </si>
+  <si>
+    <t># text = Juni erschossen, während das Auto in einer Einfahrt geparkt war, sagten die Behörden.</t>
+  </si>
+  <si>
+    <t>Juni</t>
+  </si>
+  <si>
+    <t>das</t>
+  </si>
+  <si>
     <t>SBJ_4</t>
-  </si>
-  <si>
-    <t>an</t>
-  </si>
-  <si>
-    <t>Donnerstag</t>
-  </si>
-  <si>
-    <t>other_4</t>
-  </si>
-  <si>
-    <t>ne</t>
-  </si>
-  <si>
-    <t>veröffentlicht</t>
-  </si>
-  <si>
-    <t>wurden</t>
-  </si>
-  <si>
-    <t>zwei</t>
-  </si>
-  <si>
-    <t>Frauen</t>
-  </si>
-  <si>
-    <t>OBJ</t>
-  </si>
-  <si>
-    <t>und</t>
-  </si>
-  <si>
-    <t>ein</t>
-  </si>
-  <si>
-    <t>Jahre</t>
-  </si>
-  <si>
-    <t>altes</t>
-  </si>
-  <si>
-    <t>Mädchen</t>
-  </si>
-  <si>
-    <t>indef-np.a</t>
-  </si>
-  <si>
-    <t>SBJ_2</t>
-  </si>
-  <si>
-    <t>einem</t>
-  </si>
-  <si>
-    <t>pron.pind</t>
-  </si>
-  <si>
-    <t>der</t>
-  </si>
-  <si>
-    <t>tödlichsten</t>
-  </si>
-  <si>
-    <t>Angriffe</t>
-  </si>
-  <si>
-    <t>seit</t>
-  </si>
-  <si>
-    <t>Jahrzehnt</t>
-  </si>
-  <si>
-    <t>ersten</t>
-  </si>
-  <si>
-    <t>von</t>
-  </si>
-  <si>
-    <t>Phoenix</t>
-  </si>
-  <si>
-    <t>umgekommen</t>
-  </si>
-  <si>
-    <t>sind</t>
-  </si>
-  <si>
-    <t>während</t>
-  </si>
-  <si>
-    <t>sie</t>
-  </si>
-  <si>
-    <t>SBJ_3</t>
-  </si>
-  <si>
-    <t>pron</t>
-  </si>
-  <si>
-    <t>sich</t>
-  </si>
-  <si>
-    <t>OBJ_3</t>
-  </si>
-  <si>
-    <t>unterhielten</t>
-  </si>
-  <si>
-    <t>Musik</t>
-  </si>
-  <si>
-    <t>OBJ_4</t>
-  </si>
-  <si>
-    <t>hörten</t>
-  </si>
-  <si>
-    <t>.</t>
-  </si>
-  <si>
-    <t># text = Angela Rochelle Liner, Stefanie R. Ellis and Ellis Tochter Maleah wurden am 12.</t>
-  </si>
-  <si>
-    <t>Angela</t>
-  </si>
-  <si>
-    <t>Rochelle</t>
-  </si>
-  <si>
-    <t>Liner</t>
-  </si>
-  <si>
-    <t>Stefanie</t>
-  </si>
-  <si>
-    <t>R.</t>
-  </si>
-  <si>
-    <t>Ellis</t>
-  </si>
-  <si>
-    <t>and</t>
-  </si>
-  <si>
-    <t>Tochter</t>
-  </si>
-  <si>
-    <t>Maleah</t>
-  </si>
-  <si>
-    <t># text = Juni erschossen, während das Auto in einer Einfahrt geparkt war, sagten die Behörden.</t>
-  </si>
-  <si>
-    <t>Juni</t>
-  </si>
-  <si>
-    <t>das</t>
   </si>
   <si>
     <t>einer</t>
@@ -1519,7 +1531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="60" customHeight="1"/>
   <cols>
     <col min="2" max="3" width="0" hidden="1" customWidth="1"/>
@@ -1605,13 +1617,13 @@
         <v>12</v>
       </c>
       <c r="D3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="G3" s="9">
         <f>IF(A3=1,"_",IF(C3="_","???",C3))</f>
@@ -1627,22 +1639,22 @@
     </row>
     <row r="4" spans="1:10" ht="60" customHeight="1">
       <c r="A4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="G4" s="9">
         <f>IF(A4=1,"_",IF(C4="_","???",C4))</f>
@@ -1658,22 +1670,22 @@
     </row>
     <row r="5" spans="1:10" ht="60" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="F5" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="G5" s="9">
         <f>IF(A5=1,"_",IF(C5="_","???",C5))</f>
@@ -1689,22 +1701,22 @@
     </row>
     <row r="6" spans="1:10" ht="60" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="F6" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="G6" s="9">
         <f>IF(A6=1,"_",IF(C6="_","???",C6))</f>
@@ -1720,22 +1732,22 @@
     </row>
     <row r="7" spans="1:10" ht="60" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="F7" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>37</v>
       </c>
       <c r="G7" s="9">
         <f>IF(A7=1,"_",IF(C7="_","???",C7))</f>
@@ -1751,16 +1763,16 @@
     </row>
     <row r="8" spans="1:10" ht="60" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>39</v>
@@ -1785,19 +1797,19 @@
         <v>41</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>45</v>
       </c>
       <c r="G9" s="9">
         <f>IF(A9=1,"_",IF(C9="_","???",C9))</f>
@@ -1813,22 +1825,22 @@
     </row>
     <row r="10" spans="1:10" ht="60" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="F10" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="G10" s="9">
         <f>IF(A10=1,"_",IF(C10="_","???",C10))</f>
@@ -1844,22 +1856,22 @@
     </row>
     <row r="11" spans="1:10" ht="60" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="F11" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="G11" s="9">
         <f>IF(A11=1,"_",IF(C11="_","???",C11))</f>
@@ -1875,22 +1887,22 @@
     </row>
     <row r="12" spans="1:10" ht="60" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="F12" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="G12" s="9">
         <f>IF(A12=1,"_",IF(C12="_","???",C12))</f>
@@ -1906,22 +1918,22 @@
     </row>
     <row r="13" spans="1:10" ht="60" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="F13" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="G13" s="9">
         <f>IF(A13=1,"_",IF(C13="_","???",C13))</f>
@@ -1937,22 +1949,22 @@
     </row>
     <row r="14" spans="1:10" ht="60" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="F14" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="G14" s="9">
         <f>IF(A14=1,"_",IF(C14="_","???",C14))</f>
@@ -1968,16 +1980,16 @@
     </row>
     <row r="15" spans="1:10" ht="60" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>65</v>
@@ -2002,19 +2014,19 @@
         <v>67</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="F16" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="G16" s="9">
         <f>IF(A16=1,"_",IF(C16="_","???",C16))</f>
@@ -2030,22 +2042,22 @@
     </row>
     <row r="17" spans="1:10" ht="60" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="F17" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>73</v>
       </c>
       <c r="G17" s="9">
         <f>IF(A17=1,"_",IF(C17="_","???",C17))</f>
@@ -2058,6 +2070,37 @@
         <v>12</v>
       </c>
       <c r="J17" s="12"/>
+    </row>
+    <row r="18" spans="1:10" ht="60" customHeight="1">
+      <c r="A18" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="9">
+        <f>IF(A18=1,"_",IF(C18="_","???",C18))</f>
+        <v/>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J18" s="12"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
@@ -2067,7 +2110,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L457"/>
+  <dimension ref="A1:L459"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2079,37 +2122,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L1" s="19" t="s">
         <v>9</v>
@@ -2117,18 +2160,18 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="20" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="20" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E3" s="22">
         <f>IF(D3="?OLD","!!!","")</f>
@@ -2162,7 +2205,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="20" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E4" s="22">
         <f>IF(D4="?OLD","!!!","")</f>
@@ -2196,7 +2239,7 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" s="22">
         <f>IF(D5="?OLD","!!!","")</f>
@@ -2230,13 +2273,13 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="20" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E6" s="22">
         <f>IF(D6="?OLD","!!!","")</f>
@@ -2270,7 +2313,7 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E7" s="22">
         <f>IF(D7="?OLD","!!!","")</f>
@@ -2304,13 +2347,13 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="20" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E8" s="22">
         <f>IF(D8="?OLD","!!!","")</f>
@@ -2344,7 +2387,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="20" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E9" s="22">
         <f>IF(D9="?OLD","!!!","")</f>
@@ -2378,7 +2421,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="20" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E10" s="22">
         <f>IF(D10="?OLD","!!!","")</f>
@@ -2412,16 +2455,16 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="20" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E11" s="22">
         <f>IF(D11="?OLD","!!!","")</f>
@@ -2455,7 +2498,7 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="20" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E12" s="22">
         <f>IF(D12="?OLD","!!!","")</f>
@@ -2489,7 +2532,7 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="20" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E13" s="22">
         <f>IF(D13="?OLD","!!!","")</f>
@@ -2523,16 +2566,16 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="20" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E14" s="22">
         <f>IF(D14="?OLD","!!!","")</f>
@@ -2566,7 +2609,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="20" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E15" s="22">
         <f>IF(D15="?OLD","!!!","")</f>
@@ -2599,82 +2642,16 @@
       <c r="L15" s="27"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="E16" s="22">
-        <f>IF(D16="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F16" s="23" t="str">
-        <f>IF(OR(E16="",E16="!!!"),"",IF(NOT(ISNA(VLOOKUP(E16,E$1:E15,1,FALSE()))),"OLD",IF(AND(E16&lt;&gt;"",E16&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G16" s="24" t="str">
-        <f>IF(OR(E16="",E16="!!!"),"",IF(OR(J16=0,AND(J16=1,K16=1),AND(J16=1,I16="SBJ"),AND(J16=1,I16=0)),"?IN_FOCUS",IF(J16&lt;=2,"?ACTIVATED",IF(J16&lt;&gt;"","?FAMILIAR",IF(F16="NEW",IF(ISNA(VLOOKUP(E16,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H16" s="25" t="str">
-        <f>IF(J16&lt;&gt;1,"",IF(I16="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I16" s="26" t="str">
-        <f>IF(OR(E16="",E16="!!!",F16="NEW"),"",INDEX(B15:B$2,-1+SUMPRODUCT(MAX(ROW(E15:E$2)*(E16=E15:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J16" s="26" t="str">
-        <f>IF(OR(E16="",E16="!!!",F16="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E16)*(E16=E$2:E16)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E15)*(E2=E$1:E15))))))</f>
-        <v> </v>
-      </c>
-      <c r="K16" s="26" t="str">
-        <f>IF(OR(E16="",E16="!!!",F16="NEW"),"",INDEX(J$1:J15,SUMPRODUCT(MAX(ROW(E$1:E15)*(E16=E$1:E15)))))</f>
-        <v> </v>
-      </c>
-      <c r="L16" s="27"/>
+      <c r="A16" s="20"/>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="E17" s="22">
-        <f>IF(D17="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F17" s="23" t="str">
-        <f>IF(OR(E17="",E17="!!!"),"",IF(NOT(ISNA(VLOOKUP(E17,E$1:E16,1,FALSE()))),"OLD",IF(AND(E17&lt;&gt;"",E17&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G17" s="24" t="str">
-        <f>IF(OR(E17="",E17="!!!"),"",IF(OR(J17=0,AND(J17=1,K17=1),AND(J17=1,I17="SBJ"),AND(J17=1,I17=0)),"?IN_FOCUS",IF(J17&lt;=2,"?ACTIVATED",IF(J17&lt;&gt;"","?FAMILIAR",IF(F17="NEW",IF(ISNA(VLOOKUP(E17,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H17" s="25" t="str">
-        <f>IF(J17&lt;&gt;1,"",IF(I17="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I17" s="26" t="str">
-        <f>IF(OR(E17="",E17="!!!",F17="NEW"),"",INDEX(B16:B$2,-1+SUMPRODUCT(MAX(ROW(E16:E$2)*(E17=E16:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J17" s="26" t="str">
-        <f>IF(OR(E17="",E17="!!!",F17="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E17)*(E17=E$2:E17)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E16)*(E2=E$1:E16))))))</f>
-        <v> </v>
-      </c>
-      <c r="K17" s="26" t="str">
-        <f>IF(OR(E17="",E17="!!!",F17="NEW"),"",INDEX(J$1:J16,SUMPRODUCT(MAX(ROW(E$1:E16)*(E17=E$1:E16)))))</f>
-        <v> </v>
-      </c>
-      <c r="L17" s="27"/>
+        <v>108</v>
+      </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="20" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E18" s="22">
         <f>IF(D18="?OLD","!!!","")</f>
@@ -2708,10 +2685,13 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="20" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>108</v>
+        <v>111</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>91</v>
       </c>
       <c r="E19" s="22">
         <f>IF(D19="?OLD","!!!","")</f>
@@ -2745,7 +2725,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="20" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E20" s="22">
         <f>IF(D20="?OLD","!!!","")</f>
@@ -2779,7 +2759,10 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="20" t="s">
-        <v>97</v>
+        <v>113</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>114</v>
       </c>
       <c r="E21" s="22">
         <f>IF(D21="?OLD","!!!","")</f>
@@ -2813,16 +2796,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="B22" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="E22" s="22">
         <f>IF(D22="?OLD","!!!","")</f>
@@ -2856,7 +2830,7 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="20" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="E23" s="22">
         <f>IF(D23="?OLD","!!!","")</f>
@@ -2890,7 +2864,16 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="20" t="s">
-        <v>114</v>
+        <v>116</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E24" s="22">
         <f>IF(D24="?OLD","!!!","")</f>
@@ -2924,7 +2907,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="20" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="E25" s="22">
         <f>IF(D25="?OLD","!!!","")</f>
@@ -2958,7 +2941,7 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="20" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E26" s="22">
         <f>IF(D26="?OLD","!!!","")</f>
@@ -2992,7 +2975,7 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="20" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E27" s="22">
         <f>IF(D27="?OLD","!!!","")</f>
@@ -3026,13 +3009,7 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="B28" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="E28" s="22">
         <f>IF(D28="?OLD","!!!","")</f>
@@ -3066,7 +3043,7 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="20" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E29" s="22">
         <f>IF(D29="?OLD","!!!","")</f>
@@ -3100,7 +3077,13 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="20" t="s">
-        <v>119</v>
+        <v>121</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>95</v>
       </c>
       <c r="E30" s="22">
         <f>IF(D30="?OLD","!!!","")</f>
@@ -3134,7 +3117,7 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" s="20" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="E31" s="22">
         <f>IF(D31="?OLD","!!!","")</f>
@@ -3168,7 +3151,7 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="20" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="E32" s="22">
         <f>IF(D32="?OLD","!!!","")</f>
@@ -3202,13 +3185,7 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="B33" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="E33" s="22">
         <f>IF(D33="?OLD","!!!","")</f>
@@ -3242,7 +3219,7 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="20" t="s">
-        <v>121</v>
+        <v>12</v>
       </c>
       <c r="E34" s="22">
         <f>IF(D34="?OLD","!!!","")</f>
@@ -3276,13 +3253,13 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="20" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B35" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" s="21" t="s">
         <v>95</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>123</v>
       </c>
       <c r="E35" s="22">
         <f>IF(D35="?OLD","!!!","")</f>
@@ -3316,7 +3293,7 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="20" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="E36" s="22">
         <f>IF(D36="?OLD","!!!","")</f>
@@ -3350,7 +3327,13 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="20" t="s">
-        <v>106</v>
+        <v>126</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>127</v>
       </c>
       <c r="E37" s="22">
         <f>IF(D37="?OLD","!!!","")</f>
@@ -3386,9 +3369,6 @@
       <c r="A38" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="B38" s="21" t="s">
-        <v>124</v>
-      </c>
       <c r="E38" s="22">
         <f>IF(D38="?OLD","!!!","")</f>
         <v/>
@@ -3421,7 +3401,7 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="20" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="E39" s="22">
         <f>IF(D39="?OLD","!!!","")</f>
@@ -3455,13 +3435,10 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="20" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E40" s="22">
         <f>IF(D40="?OLD","!!!","")</f>
@@ -3495,7 +3472,7 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="20" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="E41" s="22">
         <f>IF(D41="?OLD","!!!","")</f>
@@ -3529,7 +3506,13 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="20" t="s">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>130</v>
       </c>
       <c r="E42" s="22">
         <f>IF(D42="?OLD","!!!","")</f>
@@ -3563,16 +3546,7 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="B43" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="C43" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D43" s="21" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="E43" s="22">
         <f>IF(D43="?OLD","!!!","")</f>
@@ -3606,7 +3580,7 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" s="20" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E44" s="22">
         <f>IF(D44="?OLD","!!!","")</f>
@@ -3640,7 +3614,16 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" s="20" t="s">
-        <v>125</v>
+        <v>133</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E45" s="22">
         <f>IF(D45="?OLD","!!!","")</f>
@@ -3674,13 +3657,7 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="B46" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C46" s="21" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="E46" s="22">
         <f>IF(D46="?OLD","!!!","")</f>
@@ -3714,7 +3691,7 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="20" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="E47" s="22">
         <f>IF(D47="?OLD","!!!","")</f>
@@ -3748,7 +3725,13 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" s="20" t="s">
-        <v>97</v>
+        <v>135</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>127</v>
       </c>
       <c r="E48" s="22">
         <f>IF(D48="?OLD","!!!","")</f>
@@ -3782,7 +3765,7 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="20" t="s">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="E49" s="22">
         <f>IF(D49="?OLD","!!!","")</f>
@@ -3816,15 +3799,6 @@
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="B50" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C50" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D50" s="21" t="s">
         <v>100</v>
       </c>
       <c r="E50" s="22">
@@ -3859,7 +3833,7 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="20" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E51" s="22">
         <f>IF(D51="?OLD","!!!","")</f>
@@ -3893,16 +3867,16 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" s="20" t="s">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E52" s="22">
         <f>IF(D52="?OLD","!!!","")</f>
@@ -3936,7 +3910,7 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" s="20" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E53" s="22">
         <f>IF(D53="?OLD","!!!","")</f>
@@ -3970,7 +3944,16 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="20" t="s">
-        <v>136</v>
+        <v>138</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E54" s="22">
         <f>IF(D54="?OLD","!!!","")</f>
@@ -4004,7 +3987,7 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="20" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="E55" s="22">
         <f>IF(D55="?OLD","!!!","")</f>
@@ -4038,7 +4021,7 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="20" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E56" s="22">
         <f>IF(D56="?OLD","!!!","")</f>
@@ -4072,16 +4055,7 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="B57" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="C57" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="D57" s="21" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E57" s="22">
         <f>IF(D57="?OLD","!!!","")</f>
@@ -4117,9 +4091,6 @@
       <c r="A58" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="B58" s="21" t="s">
-        <v>142</v>
-      </c>
       <c r="E58" s="22">
         <f>IF(D58="?OLD","!!!","")</f>
         <v/>
@@ -4152,7 +4123,16 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="20" t="s">
-        <v>93</v>
+        <v>142</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C59" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E59" s="22">
         <f>IF(D59="?OLD","!!!","")</f>
@@ -4186,7 +4166,10 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="20" t="s">
-        <v>97</v>
+        <v>144</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>145</v>
       </c>
       <c r="E60" s="22">
         <f>IF(D60="?OLD","!!!","")</f>
@@ -4220,16 +4203,7 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="B61" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C61" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D61" s="21" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E61" s="22">
         <f>IF(D61="?OLD","!!!","")</f>
@@ -4263,7 +4237,7 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="20" t="s">
-        <v>143</v>
+        <v>100</v>
       </c>
       <c r="E62" s="22">
         <f>IF(D62="?OLD","!!!","")</f>
@@ -4297,7 +4271,16 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="20" t="s">
-        <v>118</v>
+        <v>105</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C63" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E63" s="22">
         <f>IF(D63="?OLD","!!!","")</f>
@@ -4331,13 +4314,7 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="B64" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="C64" s="21" t="s">
-        <v>88</v>
+        <v>146</v>
       </c>
       <c r="E64" s="22">
         <f>IF(D64="?OLD","!!!","")</f>
@@ -4371,7 +4348,7 @@
     </row>
     <row r="65" spans="1:12">
       <c r="A65" s="20" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="E65" s="22">
         <f>IF(D65="?OLD","!!!","")</f>
@@ -4407,6 +4384,12 @@
       <c r="A66" s="20" t="s">
         <v>147</v>
       </c>
+      <c r="B66" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="C66" s="21" t="s">
+        <v>91</v>
+      </c>
       <c r="E66" s="22">
         <f>IF(D66="?OLD","!!!","")</f>
         <v/>
@@ -4438,93 +4421,93 @@
       <c r="L66" s="27"/>
     </row>
     <row r="67" spans="1:12">
-      <c r="A67" s="20"/>
+      <c r="A67" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="E67" s="22">
+        <f>IF(D67="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F67" s="23" t="str">
+        <f>IF(OR(E67="",E67="!!!"),"",IF(NOT(ISNA(VLOOKUP(E67,E$1:E66,1,FALSE()))),"OLD",IF(AND(E67&lt;&gt;"",E67&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G67" s="24" t="str">
+        <f>IF(OR(E67="",E67="!!!"),"",IF(OR(J67=0,AND(J67=1,K67=1),AND(J67=1,I67="SBJ"),AND(J67=1,I67=0)),"?IN_FOCUS",IF(J67&lt;=2,"?ACTIVATED",IF(J67&lt;&gt;"","?FAMILIAR",IF(F67="NEW",IF(ISNA(VLOOKUP(E67,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H67" s="25" t="str">
+        <f>IF(J67&lt;&gt;1,"",IF(I67="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I67" s="26" t="str">
+        <f>IF(OR(E67="",E67="!!!",F67="NEW"),"",INDEX(B66:B$2,-1+SUMPRODUCT(MAX(ROW(E66:E$2)*(E67=E66:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J67" s="26" t="str">
+        <f>IF(OR(E67="",E67="!!!",F67="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E67)*(E67=E$2:E67)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E66)*(E2=E$1:E66))))))</f>
+        <v> </v>
+      </c>
+      <c r="K67" s="26" t="str">
+        <f>IF(OR(E67="",E67="!!!",F67="NEW"),"",INDEX(J$1:J66,SUMPRODUCT(MAX(ROW(E$1:E66)*(E67=E$1:E66)))))</f>
+        <v> </v>
+      </c>
+      <c r="L67" s="27"/>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" s="20" t="s">
-        <v>148</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E68" s="22">
+        <f>IF(D68="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F68" s="23" t="str">
+        <f>IF(OR(E68="",E68="!!!"),"",IF(NOT(ISNA(VLOOKUP(E68,E$1:E67,1,FALSE()))),"OLD",IF(AND(E68&lt;&gt;"",E68&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G68" s="24" t="str">
+        <f>IF(OR(E68="",E68="!!!"),"",IF(OR(J68=0,AND(J68=1,K68=1),AND(J68=1,I68="SBJ"),AND(J68=1,I68=0)),"?IN_FOCUS",IF(J68&lt;=2,"?ACTIVATED",IF(J68&lt;&gt;"","?FAMILIAR",IF(F68="NEW",IF(ISNA(VLOOKUP(E68,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H68" s="25" t="str">
+        <f>IF(J68&lt;&gt;1,"",IF(I68="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I68" s="26" t="str">
+        <f>IF(OR(E68="",E68="!!!",F68="NEW"),"",INDEX(B67:B$2,-1+SUMPRODUCT(MAX(ROW(E67:E$2)*(E68=E67:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J68" s="26" t="str">
+        <f>IF(OR(E68="",E68="!!!",F68="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E68)*(E68=E$2:E68)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E67)*(E2=E$1:E67))))))</f>
+        <v> </v>
+      </c>
+      <c r="K68" s="26" t="str">
+        <f>IF(OR(E68="",E68="!!!",F68="NEW"),"",INDEX(J$1:J67,SUMPRODUCT(MAX(ROW(E$1:E67)*(E68=E$1:E67)))))</f>
+        <v> </v>
+      </c>
+      <c r="L68" s="27"/>
     </row>
     <row r="69" spans="1:12">
-      <c r="A69" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="B69" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C69" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D69" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="E69" s="22">
-        <f>IF(D69="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F69" s="23" t="str">
-        <f>IF(OR(E69="",E69="!!!"),"",IF(NOT(ISNA(VLOOKUP(E69,E$1:E68,1,FALSE()))),"OLD",IF(AND(E69&lt;&gt;"",E69&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G69" s="24" t="str">
-        <f>IF(OR(E69="",E69="!!!"),"",IF(OR(J69=0,AND(J69=1,K69=1),AND(J69=1,I69="SBJ"),AND(J69=1,I69=0)),"?IN_FOCUS",IF(J69&lt;=2,"?ACTIVATED",IF(J69&lt;&gt;"","?FAMILIAR",IF(F69="NEW",IF(ISNA(VLOOKUP(E69,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H69" s="25" t="str">
-        <f>IF(J69&lt;&gt;1,"",IF(I69="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I69" s="26" t="str">
-        <f>IF(OR(E69="",E69="!!!",F69="NEW"),"",INDEX(B68:B$2,-1+SUMPRODUCT(MAX(ROW(E68:E$2)*(E69=E68:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J69" s="26" t="str">
-        <f>IF(OR(E69="",E69="!!!",F69="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E69)*(E69=E$2:E69)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E68)*(E2=E$1:E68))))))</f>
-        <v> </v>
-      </c>
-      <c r="K69" s="26" t="str">
-        <f>IF(OR(E69="",E69="!!!",F69="NEW"),"",INDEX(J$1:J68,SUMPRODUCT(MAX(ROW(E$1:E68)*(E69=E$1:E68)))))</f>
-        <v> </v>
-      </c>
-      <c r="L69" s="27"/>
+      <c r="A69" s="20"/>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="E70" s="22">
-        <f>IF(D70="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F70" s="23" t="str">
-        <f>IF(OR(E70="",E70="!!!"),"",IF(NOT(ISNA(VLOOKUP(E70,E$1:E69,1,FALSE()))),"OLD",IF(AND(E70&lt;&gt;"",E70&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G70" s="24" t="str">
-        <f>IF(OR(E70="",E70="!!!"),"",IF(OR(J70=0,AND(J70=1,K70=1),AND(J70=1,I70="SBJ"),AND(J70=1,I70=0)),"?IN_FOCUS",IF(J70&lt;=2,"?ACTIVATED",IF(J70&lt;&gt;"","?FAMILIAR",IF(F70="NEW",IF(ISNA(VLOOKUP(E70,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H70" s="25" t="str">
-        <f>IF(J70&lt;&gt;1,"",IF(I70="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I70" s="26" t="str">
-        <f>IF(OR(E70="",E70="!!!",F70="NEW"),"",INDEX(B69:B$2,-1+SUMPRODUCT(MAX(ROW(E69:E$2)*(E70=E69:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J70" s="26" t="str">
-        <f>IF(OR(E70="",E70="!!!",F70="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E70)*(E70=E$2:E70)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E69)*(E2=E$1:E69))))))</f>
-        <v> </v>
-      </c>
-      <c r="K70" s="26" t="str">
-        <f>IF(OR(E70="",E70="!!!",F70="NEW"),"",INDEX(J$1:J69,SUMPRODUCT(MAX(ROW(E$1:E69)*(E70=E$1:E69)))))</f>
-        <v> </v>
-      </c>
-      <c r="L70" s="27"/>
+        <v>151</v>
+      </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" s="20" t="s">
-        <v>151</v>
+        <v>152</v>
+      </c>
+      <c r="B71" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C71" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E71" s="22">
         <f>IF(D71="?OLD","!!!","")</f>
@@ -4558,7 +4541,7 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72" s="20" t="s">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="E72" s="22">
         <f>IF(D72="?OLD","!!!","")</f>
@@ -4592,16 +4575,7 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="B73" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C73" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D73" s="21" t="s">
-        <v>100</v>
+        <v>154</v>
       </c>
       <c r="E73" s="22">
         <f>IF(D73="?OLD","!!!","")</f>
@@ -4635,7 +4609,7 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" s="20" t="s">
-        <v>153</v>
+        <v>112</v>
       </c>
       <c r="E74" s="22">
         <f>IF(D74="?OLD","!!!","")</f>
@@ -4669,16 +4643,16 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" s="20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D75" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E75" s="22">
         <f>IF(D75="?OLD","!!!","")</f>
@@ -4712,7 +4686,7 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" s="20" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E76" s="22">
         <f>IF(D76="?OLD","!!!","")</f>
@@ -4746,16 +4720,16 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" s="20" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B77" s="21" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E77" s="22">
         <f>IF(D77="?OLD","!!!","")</f>
@@ -4789,16 +4763,7 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="B78" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C78" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D78" s="21" t="s">
-        <v>100</v>
+        <v>158</v>
       </c>
       <c r="E78" s="22">
         <f>IF(D78="?OLD","!!!","")</f>
@@ -4834,6 +4799,15 @@
       <c r="A79" s="20" t="s">
         <v>157</v>
       </c>
+      <c r="B79" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C79" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D79" s="21" t="s">
+        <v>104</v>
+      </c>
       <c r="E79" s="22">
         <f>IF(D79="?OLD","!!!","")</f>
         <v/>
@@ -4866,7 +4840,16 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" s="20" t="s">
-        <v>114</v>
+        <v>159</v>
+      </c>
+      <c r="B80" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D80" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E80" s="22">
         <f>IF(D80="?OLD","!!!","")</f>
@@ -4900,7 +4883,7 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" s="20" t="s">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="E81" s="22">
         <f>IF(D81="?OLD","!!!","")</f>
@@ -4934,7 +4917,7 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82" s="20" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="E82" s="22">
         <f>IF(D82="?OLD","!!!","")</f>
@@ -4968,7 +4951,7 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" s="20" t="s">
-        <v>17</v>
+        <v>115</v>
       </c>
       <c r="E83" s="22">
         <f>IF(D83="?OLD","!!!","")</f>
@@ -5002,7 +4985,7 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84" s="20" t="s">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="E84" s="22">
         <f>IF(D84="?OLD","!!!","")</f>
@@ -5035,93 +5018,93 @@
       <c r="L84" s="27"/>
     </row>
     <row r="85" spans="1:12">
-      <c r="A85" s="20"/>
+      <c r="A85" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E85" s="22">
+        <f>IF(D85="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F85" s="23" t="str">
+        <f>IF(OR(E85="",E85="!!!"),"",IF(NOT(ISNA(VLOOKUP(E85,E$1:E84,1,FALSE()))),"OLD",IF(AND(E85&lt;&gt;"",E85&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G85" s="24" t="str">
+        <f>IF(OR(E85="",E85="!!!"),"",IF(OR(J85=0,AND(J85=1,K85=1),AND(J85=1,I85="SBJ"),AND(J85=1,I85=0)),"?IN_FOCUS",IF(J85&lt;=2,"?ACTIVATED",IF(J85&lt;&gt;"","?FAMILIAR",IF(F85="NEW",IF(ISNA(VLOOKUP(E85,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H85" s="25" t="str">
+        <f>IF(J85&lt;&gt;1,"",IF(I85="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I85" s="26" t="str">
+        <f>IF(OR(E85="",E85="!!!",F85="NEW"),"",INDEX(B84:B$2,-1+SUMPRODUCT(MAX(ROW(E84:E$2)*(E85=E84:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J85" s="26" t="str">
+        <f>IF(OR(E85="",E85="!!!",F85="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E85)*(E85=E$2:E85)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E84)*(E2=E$1:E84))))))</f>
+        <v> </v>
+      </c>
+      <c r="K85" s="26" t="str">
+        <f>IF(OR(E85="",E85="!!!",F85="NEW"),"",INDEX(J$1:J84,SUMPRODUCT(MAX(ROW(E$1:E84)*(E85=E$1:E84)))))</f>
+        <v> </v>
+      </c>
+      <c r="L85" s="27"/>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" s="20" t="s">
-        <v>158</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E86" s="22">
+        <f>IF(D86="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F86" s="23" t="str">
+        <f>IF(OR(E86="",E86="!!!"),"",IF(NOT(ISNA(VLOOKUP(E86,E$1:E85,1,FALSE()))),"OLD",IF(AND(E86&lt;&gt;"",E86&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G86" s="24" t="str">
+        <f>IF(OR(E86="",E86="!!!"),"",IF(OR(J86=0,AND(J86=1,K86=1),AND(J86=1,I86="SBJ"),AND(J86=1,I86=0)),"?IN_FOCUS",IF(J86&lt;=2,"?ACTIVATED",IF(J86&lt;&gt;"","?FAMILIAR",IF(F86="NEW",IF(ISNA(VLOOKUP(E86,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H86" s="25" t="str">
+        <f>IF(J86&lt;&gt;1,"",IF(I86="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I86" s="26" t="str">
+        <f>IF(OR(E86="",E86="!!!",F86="NEW"),"",INDEX(B85:B$2,-1+SUMPRODUCT(MAX(ROW(E85:E$2)*(E86=E85:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J86" s="26" t="str">
+        <f>IF(OR(E86="",E86="!!!",F86="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E86)*(E86=E$2:E86)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E85)*(E2=E$1:E85))))))</f>
+        <v> </v>
+      </c>
+      <c r="K86" s="26" t="str">
+        <f>IF(OR(E86="",E86="!!!",F86="NEW"),"",INDEX(J$1:J85,SUMPRODUCT(MAX(ROW(E$1:E85)*(E86=E$1:E85)))))</f>
+        <v> </v>
+      </c>
+      <c r="L86" s="27"/>
     </row>
     <row r="87" spans="1:12">
-      <c r="A87" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="B87" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C87" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D87" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="E87" s="22">
-        <f>IF(D87="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F87" s="23" t="str">
-        <f>IF(OR(E87="",E87="!!!"),"",IF(NOT(ISNA(VLOOKUP(E87,E$1:E86,1,FALSE()))),"OLD",IF(AND(E87&lt;&gt;"",E87&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G87" s="24" t="str">
-        <f>IF(OR(E87="",E87="!!!"),"",IF(OR(J87=0,AND(J87=1,K87=1),AND(J87=1,I87="SBJ"),AND(J87=1,I87=0)),"?IN_FOCUS",IF(J87&lt;=2,"?ACTIVATED",IF(J87&lt;&gt;"","?FAMILIAR",IF(F87="NEW",IF(ISNA(VLOOKUP(E87,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H87" s="25" t="str">
-        <f>IF(J87&lt;&gt;1,"",IF(I87="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I87" s="26" t="str">
-        <f>IF(OR(E87="",E87="!!!",F87="NEW"),"",INDEX(B86:B$2,-1+SUMPRODUCT(MAX(ROW(E86:E$2)*(E87=E86:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J87" s="26" t="str">
-        <f>IF(OR(E87="",E87="!!!",F87="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E87)*(E87=E$2:E87)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E86)*(E2=E$1:E86))))))</f>
-        <v> </v>
-      </c>
-      <c r="K87" s="26" t="str">
-        <f>IF(OR(E87="",E87="!!!",F87="NEW"),"",INDEX(J$1:J86,SUMPRODUCT(MAX(ROW(E$1:E86)*(E87=E$1:E86)))))</f>
-        <v> </v>
-      </c>
-      <c r="L87" s="27"/>
+      <c r="A87" s="20"/>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="E88" s="22">
-        <f>IF(D88="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F88" s="23" t="str">
-        <f>IF(OR(E88="",E88="!!!"),"",IF(NOT(ISNA(VLOOKUP(E88,E$1:E87,1,FALSE()))),"OLD",IF(AND(E88&lt;&gt;"",E88&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G88" s="24" t="str">
-        <f>IF(OR(E88="",E88="!!!"),"",IF(OR(J88=0,AND(J88=1,K88=1),AND(J88=1,I88="SBJ"),AND(J88=1,I88=0)),"?IN_FOCUS",IF(J88&lt;=2,"?ACTIVATED",IF(J88&lt;&gt;"","?FAMILIAR",IF(F88="NEW",IF(ISNA(VLOOKUP(E88,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H88" s="25" t="str">
-        <f>IF(J88&lt;&gt;1,"",IF(I88="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I88" s="26" t="str">
-        <f>IF(OR(E88="",E88="!!!",F88="NEW"),"",INDEX(B87:B$2,-1+SUMPRODUCT(MAX(ROW(E87:E$2)*(E88=E87:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J88" s="26" t="str">
-        <f>IF(OR(E88="",E88="!!!",F88="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E88)*(E88=E$2:E88)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E87)*(E2=E$1:E87))))))</f>
-        <v> </v>
-      </c>
-      <c r="K88" s="26" t="str">
-        <f>IF(OR(E88="",E88="!!!",F88="NEW"),"",INDEX(J$1:J87,SUMPRODUCT(MAX(ROW(E$1:E87)*(E88=E$1:E87)))))</f>
-        <v> </v>
-      </c>
-      <c r="L88" s="27"/>
+        <v>161</v>
+      </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" s="20" t="s">
-        <v>106</v>
+        <v>162</v>
+      </c>
+      <c r="B89" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C89" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D89" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E89" s="22">
         <f>IF(D89="?OLD","!!!","")</f>
@@ -5155,7 +5138,7 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90" s="20" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="E90" s="22">
         <f>IF(D90="?OLD","!!!","")</f>
@@ -5189,7 +5172,7 @@
     </row>
     <row r="91" spans="1:12">
       <c r="A91" s="20" t="s">
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="E91" s="22">
         <f>IF(D91="?OLD","!!!","")</f>
@@ -5223,16 +5206,7 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="B92" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="C92" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D92" s="21" t="s">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="E92" s="22">
         <f>IF(D92="?OLD","!!!","")</f>
@@ -5266,7 +5240,7 @@
     </row>
     <row r="93" spans="1:12">
       <c r="A93" s="20" t="s">
-        <v>93</v>
+        <v>163</v>
       </c>
       <c r="E93" s="22">
         <f>IF(D93="?OLD","!!!","")</f>
@@ -5300,7 +5274,16 @@
     </row>
     <row r="94" spans="1:12">
       <c r="A94" s="20" t="s">
-        <v>161</v>
+        <v>105</v>
+      </c>
+      <c r="B94" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="C94" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D94" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E94" s="22">
         <f>IF(D94="?OLD","!!!","")</f>
@@ -5334,13 +5317,7 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="B95" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C95" s="21" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="E95" s="22">
         <f>IF(D95="?OLD","!!!","")</f>
@@ -5374,7 +5351,7 @@
     </row>
     <row r="96" spans="1:12">
       <c r="A96" s="20" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E96" s="22">
         <f>IF(D96="?OLD","!!!","")</f>
@@ -5408,7 +5385,13 @@
     </row>
     <row r="97" spans="1:12">
       <c r="A97" s="20" t="s">
-        <v>164</v>
+        <v>166</v>
+      </c>
+      <c r="B97" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C97" s="21" t="s">
+        <v>127</v>
       </c>
       <c r="E97" s="22">
         <f>IF(D97="?OLD","!!!","")</f>
@@ -5442,7 +5425,7 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98" s="20" t="s">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="E98" s="22">
         <f>IF(D98="?OLD","!!!","")</f>
@@ -5476,7 +5459,7 @@
     </row>
     <row r="99" spans="1:12">
       <c r="A99" s="20" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E99" s="22">
         <f>IF(D99="?OLD","!!!","")</f>
@@ -5510,7 +5493,7 @@
     </row>
     <row r="100" spans="1:12">
       <c r="A100" s="20" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E100" s="22">
         <f>IF(D100="?OLD","!!!","")</f>
@@ -5544,16 +5527,7 @@
     </row>
     <row r="101" spans="1:12">
       <c r="A101" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="B101" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C101" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D101" s="21" t="s">
-        <v>100</v>
+        <v>169</v>
       </c>
       <c r="E101" s="22">
         <f>IF(D101="?OLD","!!!","")</f>
@@ -5587,7 +5561,7 @@
     </row>
     <row r="102" spans="1:12">
       <c r="A102" s="20" t="s">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="E102" s="22">
         <f>IF(D102="?OLD","!!!","")</f>
@@ -5620,93 +5594,93 @@
       <c r="L102" s="27"/>
     </row>
     <row r="103" spans="1:12">
-      <c r="A103" s="20"/>
+      <c r="A103" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="B103" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C103" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D103" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="E103" s="22">
+        <f>IF(D103="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F103" s="23" t="str">
+        <f>IF(OR(E103="",E103="!!!"),"",IF(NOT(ISNA(VLOOKUP(E103,E$1:E102,1,FALSE()))),"OLD",IF(AND(E103&lt;&gt;"",E103&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G103" s="24" t="str">
+        <f>IF(OR(E103="",E103="!!!"),"",IF(OR(J103=0,AND(J103=1,K103=1),AND(J103=1,I103="SBJ"),AND(J103=1,I103=0)),"?IN_FOCUS",IF(J103&lt;=2,"?ACTIVATED",IF(J103&lt;&gt;"","?FAMILIAR",IF(F103="NEW",IF(ISNA(VLOOKUP(E103,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H103" s="25" t="str">
+        <f>IF(J103&lt;&gt;1,"",IF(I103="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I103" s="26" t="str">
+        <f>IF(OR(E103="",E103="!!!",F103="NEW"),"",INDEX(B102:B$2,-1+SUMPRODUCT(MAX(ROW(E102:E$2)*(E103=E102:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J103" s="26" t="str">
+        <f>IF(OR(E103="",E103="!!!",F103="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E103)*(E103=E$2:E103)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E102)*(E2=E$1:E102))))))</f>
+        <v> </v>
+      </c>
+      <c r="K103" s="26" t="str">
+        <f>IF(OR(E103="",E103="!!!",F103="NEW"),"",INDEX(J$1:J102,SUMPRODUCT(MAX(ROW(E$1:E102)*(E103=E$1:E102)))))</f>
+        <v> </v>
+      </c>
+      <c r="L103" s="27"/>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" s="20" t="s">
-        <v>167</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E104" s="22">
+        <f>IF(D104="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F104" s="23" t="str">
+        <f>IF(OR(E104="",E104="!!!"),"",IF(NOT(ISNA(VLOOKUP(E104,E$1:E103,1,FALSE()))),"OLD",IF(AND(E104&lt;&gt;"",E104&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G104" s="24" t="str">
+        <f>IF(OR(E104="",E104="!!!"),"",IF(OR(J104=0,AND(J104=1,K104=1),AND(J104=1,I104="SBJ"),AND(J104=1,I104=0)),"?IN_FOCUS",IF(J104&lt;=2,"?ACTIVATED",IF(J104&lt;&gt;"","?FAMILIAR",IF(F104="NEW",IF(ISNA(VLOOKUP(E104,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H104" s="25" t="str">
+        <f>IF(J104&lt;&gt;1,"",IF(I104="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I104" s="26" t="str">
+        <f>IF(OR(E104="",E104="!!!",F104="NEW"),"",INDEX(B103:B$2,-1+SUMPRODUCT(MAX(ROW(E103:E$2)*(E104=E103:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J104" s="26" t="str">
+        <f>IF(OR(E104="",E104="!!!",F104="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E104)*(E104=E$2:E104)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E103)*(E2=E$1:E103))))))</f>
+        <v> </v>
+      </c>
+      <c r="K104" s="26" t="str">
+        <f>IF(OR(E104="",E104="!!!",F104="NEW"),"",INDEX(J$1:J103,SUMPRODUCT(MAX(ROW(E$1:E103)*(E104=E$1:E103)))))</f>
+        <v> </v>
+      </c>
+      <c r="L104" s="27"/>
     </row>
     <row r="105" spans="1:12">
-      <c r="A105" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="E105" s="22">
-        <f>IF(D105="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F105" s="23" t="str">
-        <f>IF(OR(E105="",E105="!!!"),"",IF(NOT(ISNA(VLOOKUP(E105,E$1:E104,1,FALSE()))),"OLD",IF(AND(E105&lt;&gt;"",E105&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G105" s="24" t="str">
-        <f>IF(OR(E105="",E105="!!!"),"",IF(OR(J105=0,AND(J105=1,K105=1),AND(J105=1,I105="SBJ"),AND(J105=1,I105=0)),"?IN_FOCUS",IF(J105&lt;=2,"?ACTIVATED",IF(J105&lt;&gt;"","?FAMILIAR",IF(F105="NEW",IF(ISNA(VLOOKUP(E105,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H105" s="25" t="str">
-        <f>IF(J105&lt;&gt;1,"",IF(I105="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I105" s="26" t="str">
-        <f>IF(OR(E105="",E105="!!!",F105="NEW"),"",INDEX(B104:B$2,-1+SUMPRODUCT(MAX(ROW(E104:E$2)*(E105=E104:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J105" s="26" t="str">
-        <f>IF(OR(E105="",E105="!!!",F105="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E105)*(E105=E$2:E105)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E104)*(E2=E$1:E104))))))</f>
-        <v> </v>
-      </c>
-      <c r="K105" s="26" t="str">
-        <f>IF(OR(E105="",E105="!!!",F105="NEW"),"",INDEX(J$1:J104,SUMPRODUCT(MAX(ROW(E$1:E104)*(E105=E$1:E104)))))</f>
-        <v> </v>
-      </c>
-      <c r="L105" s="27"/>
+      <c r="A105" s="20"/>
     </row>
     <row r="106" spans="1:12">
       <c r="A106" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="B106" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C106" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D106" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="E106" s="22">
-        <f>IF(D106="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F106" s="23" t="str">
-        <f>IF(OR(E106="",E106="!!!"),"",IF(NOT(ISNA(VLOOKUP(E106,E$1:E105,1,FALSE()))),"OLD",IF(AND(E106&lt;&gt;"",E106&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G106" s="24" t="str">
-        <f>IF(OR(E106="",E106="!!!"),"",IF(OR(J106=0,AND(J106=1,K106=1),AND(J106=1,I106="SBJ"),AND(J106=1,I106=0)),"?IN_FOCUS",IF(J106&lt;=2,"?ACTIVATED",IF(J106&lt;&gt;"","?FAMILIAR",IF(F106="NEW",IF(ISNA(VLOOKUP(E106,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H106" s="25" t="str">
-        <f>IF(J106&lt;&gt;1,"",IF(I106="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I106" s="26" t="str">
-        <f>IF(OR(E106="",E106="!!!",F106="NEW"),"",INDEX(B105:B$2,-1+SUMPRODUCT(MAX(ROW(E105:E$2)*(E106=E105:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J106" s="26" t="str">
-        <f>IF(OR(E106="",E106="!!!",F106="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E106)*(E106=E$2:E106)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E105)*(E2=E$1:E105))))))</f>
-        <v> </v>
-      </c>
-      <c r="K106" s="26" t="str">
-        <f>IF(OR(E106="",E106="!!!",F106="NEW"),"",INDEX(J$1:J105,SUMPRODUCT(MAX(ROW(E$1:E105)*(E106=E$1:E105)))))</f>
-        <v> </v>
-      </c>
-      <c r="L106" s="27"/>
+        <v>171</v>
+      </c>
     </row>
     <row r="107" spans="1:12">
       <c r="A107" s="20" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E107" s="22">
         <f>IF(D107="?OLD","!!!","")</f>
@@ -5740,7 +5714,16 @@
     </row>
     <row r="108" spans="1:12">
       <c r="A108" s="20" t="s">
-        <v>171</v>
+        <v>173</v>
+      </c>
+      <c r="B108" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C108" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D108" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E108" s="22">
         <f>IF(D108="?OLD","!!!","")</f>
@@ -5774,13 +5757,7 @@
     </row>
     <row r="109" spans="1:12">
       <c r="A109" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="B109" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="C109" s="21" t="s">
-        <v>92</v>
+        <v>174</v>
       </c>
       <c r="E109" s="22">
         <f>IF(D109="?OLD","!!!","")</f>
@@ -5814,7 +5791,7 @@
     </row>
     <row r="110" spans="1:12">
       <c r="A110" s="20" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E110" s="22">
         <f>IF(D110="?OLD","!!!","")</f>
@@ -5848,7 +5825,13 @@
     </row>
     <row r="111" spans="1:12">
       <c r="A111" s="20" t="s">
-        <v>161</v>
+        <v>176</v>
+      </c>
+      <c r="B111" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C111" s="21" t="s">
+        <v>95</v>
       </c>
       <c r="E111" s="22">
         <f>IF(D111="?OLD","!!!","")</f>
@@ -5882,13 +5865,7 @@
     </row>
     <row r="112" spans="1:12">
       <c r="A112" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="B112" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C112" s="21" t="s">
-        <v>123</v>
+        <v>177</v>
       </c>
       <c r="E112" s="22">
         <f>IF(D112="?OLD","!!!","")</f>
@@ -5922,7 +5899,7 @@
     </row>
     <row r="113" spans="1:12">
       <c r="A113" s="20" t="s">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="E113" s="22">
         <f>IF(D113="?OLD","!!!","")</f>
@@ -5956,7 +5933,13 @@
     </row>
     <row r="114" spans="1:12">
       <c r="A114" s="20" t="s">
-        <v>137</v>
+        <v>178</v>
+      </c>
+      <c r="B114" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C114" s="21" t="s">
+        <v>127</v>
       </c>
       <c r="E114" s="22">
         <f>IF(D114="?OLD","!!!","")</f>
@@ -5990,16 +5973,7 @@
     </row>
     <row r="115" spans="1:12">
       <c r="A115" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="B115" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="C115" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="D115" s="21" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E115" s="22">
         <f>IF(D115="?OLD","!!!","")</f>
@@ -6033,7 +6007,7 @@
     </row>
     <row r="116" spans="1:12">
       <c r="A116" s="20" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="E116" s="22">
         <f>IF(D116="?OLD","!!!","")</f>
@@ -6067,7 +6041,16 @@
     </row>
     <row r="117" spans="1:12">
       <c r="A117" s="20" t="s">
-        <v>127</v>
+        <v>179</v>
+      </c>
+      <c r="B117" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C117" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="D117" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E117" s="22">
         <f>IF(D117="?OLD","!!!","")</f>
@@ -6101,16 +6084,7 @@
     </row>
     <row r="118" spans="1:12">
       <c r="A118" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="B118" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C118" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D118" s="21" t="s">
-        <v>100</v>
+        <v>181</v>
       </c>
       <c r="E118" s="22">
         <f>IF(D118="?OLD","!!!","")</f>
@@ -6144,7 +6118,7 @@
     </row>
     <row r="119" spans="1:12">
       <c r="A119" s="20" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="E119" s="22">
         <f>IF(D119="?OLD","!!!","")</f>
@@ -6178,16 +6152,16 @@
     </row>
     <row r="120" spans="1:12">
       <c r="A120" s="20" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B120" s="21" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C120" s="21" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D120" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E120" s="22">
         <f>IF(D120="?OLD","!!!","")</f>
@@ -6221,7 +6195,7 @@
     </row>
     <row r="121" spans="1:12">
       <c r="A121" s="20" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E121" s="22">
         <f>IF(D121="?OLD","!!!","")</f>
@@ -6255,7 +6229,16 @@
     </row>
     <row r="122" spans="1:12">
       <c r="A122" s="20" t="s">
-        <v>118</v>
+        <v>184</v>
+      </c>
+      <c r="B122" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C122" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D122" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E122" s="22">
         <f>IF(D122="?OLD","!!!","")</f>
@@ -6289,7 +6272,7 @@
     </row>
     <row r="123" spans="1:12">
       <c r="A123" s="20" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E123" s="22">
         <f>IF(D123="?OLD","!!!","")</f>
@@ -6323,7 +6306,7 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124" s="20" t="s">
-        <v>183</v>
+        <v>122</v>
       </c>
       <c r="E124" s="22">
         <f>IF(D124="?OLD","!!!","")</f>
@@ -6357,7 +6340,7 @@
     </row>
     <row r="125" spans="1:12">
       <c r="A125" s="20" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E125" s="22">
         <f>IF(D125="?OLD","!!!","")</f>
@@ -6391,7 +6374,7 @@
     </row>
     <row r="126" spans="1:12">
       <c r="A126" s="20" t="s">
-        <v>125</v>
+        <v>187</v>
       </c>
       <c r="E126" s="22">
         <f>IF(D126="?OLD","!!!","")</f>
@@ -6425,7 +6408,7 @@
     </row>
     <row r="127" spans="1:12">
       <c r="A127" s="20" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E127" s="22">
         <f>IF(D127="?OLD","!!!","")</f>
@@ -6459,13 +6442,7 @@
     </row>
     <row r="128" spans="1:12">
       <c r="A128" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="B128" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C128" s="21" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E128" s="22">
         <f>IF(D128="?OLD","!!!","")</f>
@@ -6499,7 +6476,7 @@
     </row>
     <row r="129" spans="1:12">
       <c r="A129" s="20" t="s">
-        <v>106</v>
+        <v>189</v>
       </c>
       <c r="E129" s="22">
         <f>IF(D129="?OLD","!!!","")</f>
@@ -6533,7 +6510,13 @@
     </row>
     <row r="130" spans="1:12">
       <c r="A130" s="20" t="s">
-        <v>187</v>
+        <v>190</v>
+      </c>
+      <c r="B130" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C130" s="21" t="s">
+        <v>127</v>
       </c>
       <c r="E130" s="22">
         <f>IF(D130="?OLD","!!!","")</f>
@@ -6567,7 +6550,7 @@
     </row>
     <row r="131" spans="1:12">
       <c r="A131" s="20" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="E131" s="22">
         <f>IF(D131="?OLD","!!!","")</f>
@@ -6601,7 +6584,7 @@
     </row>
     <row r="132" spans="1:12">
       <c r="A132" s="20" t="s">
-        <v>97</v>
+        <v>191</v>
       </c>
       <c r="E132" s="22">
         <f>IF(D132="?OLD","!!!","")</f>
@@ -6635,16 +6618,7 @@
     </row>
     <row r="133" spans="1:12">
       <c r="A133" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="B133" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C133" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D133" s="21" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E133" s="22">
         <f>IF(D133="?OLD","!!!","")</f>
@@ -6678,7 +6652,7 @@
     </row>
     <row r="134" spans="1:12">
       <c r="A134" s="20" t="s">
-        <v>189</v>
+        <v>100</v>
       </c>
       <c r="E134" s="22">
         <f>IF(D134="?OLD","!!!","")</f>
@@ -6712,7 +6686,16 @@
     </row>
     <row r="135" spans="1:12">
       <c r="A135" s="20" t="s">
-        <v>190</v>
+        <v>192</v>
+      </c>
+      <c r="B135" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C135" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D135" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E135" s="22">
         <f>IF(D135="?OLD","!!!","")</f>
@@ -6746,7 +6729,7 @@
     </row>
     <row r="136" spans="1:12">
       <c r="A136" s="20" t="s">
-        <v>147</v>
+        <v>193</v>
       </c>
       <c r="E136" s="22">
         <f>IF(D136="?OLD","!!!","")</f>
@@ -6779,93 +6762,84 @@
       <c r="L136" s="27"/>
     </row>
     <row r="137" spans="1:12">
-      <c r="A137" s="20"/>
+      <c r="A137" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="E137" s="22">
+        <f>IF(D137="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F137" s="23" t="str">
+        <f>IF(OR(E137="",E137="!!!"),"",IF(NOT(ISNA(VLOOKUP(E137,E$1:E136,1,FALSE()))),"OLD",IF(AND(E137&lt;&gt;"",E137&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G137" s="24" t="str">
+        <f>IF(OR(E137="",E137="!!!"),"",IF(OR(J137=0,AND(J137=1,K137=1),AND(J137=1,I137="SBJ"),AND(J137=1,I137=0)),"?IN_FOCUS",IF(J137&lt;=2,"?ACTIVATED",IF(J137&lt;&gt;"","?FAMILIAR",IF(F137="NEW",IF(ISNA(VLOOKUP(E137,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H137" s="25" t="str">
+        <f>IF(J137&lt;&gt;1,"",IF(I137="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I137" s="26" t="str">
+        <f>IF(OR(E137="",E137="!!!",F137="NEW"),"",INDEX(B136:B$2,-1+SUMPRODUCT(MAX(ROW(E136:E$2)*(E137=E136:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J137" s="26" t="str">
+        <f>IF(OR(E137="",E137="!!!",F137="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E137)*(E137=E$2:E137)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E136)*(E2=E$1:E136))))))</f>
+        <v> </v>
+      </c>
+      <c r="K137" s="26" t="str">
+        <f>IF(OR(E137="",E137="!!!",F137="NEW"),"",INDEX(J$1:J136,SUMPRODUCT(MAX(ROW(E$1:E136)*(E137=E$1:E136)))))</f>
+        <v> </v>
+      </c>
+      <c r="L137" s="27"/>
     </row>
     <row r="138" spans="1:12">
       <c r="A138" s="20" t="s">
-        <v>191</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E138" s="22">
+        <f>IF(D138="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F138" s="23" t="str">
+        <f>IF(OR(E138="",E138="!!!"),"",IF(NOT(ISNA(VLOOKUP(E138,E$1:E137,1,FALSE()))),"OLD",IF(AND(E138&lt;&gt;"",E138&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G138" s="24" t="str">
+        <f>IF(OR(E138="",E138="!!!"),"",IF(OR(J138=0,AND(J138=1,K138=1),AND(J138=1,I138="SBJ"),AND(J138=1,I138=0)),"?IN_FOCUS",IF(J138&lt;=2,"?ACTIVATED",IF(J138&lt;&gt;"","?FAMILIAR",IF(F138="NEW",IF(ISNA(VLOOKUP(E138,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H138" s="25" t="str">
+        <f>IF(J138&lt;&gt;1,"",IF(I138="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I138" s="26" t="str">
+        <f>IF(OR(E138="",E138="!!!",F138="NEW"),"",INDEX(B137:B$2,-1+SUMPRODUCT(MAX(ROW(E137:E$2)*(E138=E137:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J138" s="26" t="str">
+        <f>IF(OR(E138="",E138="!!!",F138="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E138)*(E138=E$2:E138)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E137)*(E2=E$1:E137))))))</f>
+        <v> </v>
+      </c>
+      <c r="K138" s="26" t="str">
+        <f>IF(OR(E138="",E138="!!!",F138="NEW"),"",INDEX(J$1:J137,SUMPRODUCT(MAX(ROW(E$1:E137)*(E138=E$1:E137)))))</f>
+        <v> </v>
+      </c>
+      <c r="L138" s="27"/>
     </row>
     <row r="139" spans="1:12">
-      <c r="A139" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="E139" s="22">
-        <f>IF(D139="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F139" s="23" t="str">
-        <f>IF(OR(E139="",E139="!!!"),"",IF(NOT(ISNA(VLOOKUP(E139,E$1:E138,1,FALSE()))),"OLD",IF(AND(E139&lt;&gt;"",E139&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G139" s="24" t="str">
-        <f>IF(OR(E139="",E139="!!!"),"",IF(OR(J139=0,AND(J139=1,K139=1),AND(J139=1,I139="SBJ"),AND(J139=1,I139=0)),"?IN_FOCUS",IF(J139&lt;=2,"?ACTIVATED",IF(J139&lt;&gt;"","?FAMILIAR",IF(F139="NEW",IF(ISNA(VLOOKUP(E139,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H139" s="25" t="str">
-        <f>IF(J139&lt;&gt;1,"",IF(I139="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I139" s="26" t="str">
-        <f>IF(OR(E139="",E139="!!!",F139="NEW"),"",INDEX(B138:B$2,-1+SUMPRODUCT(MAX(ROW(E138:E$2)*(E139=E138:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J139" s="26" t="str">
-        <f>IF(OR(E139="",E139="!!!",F139="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E139)*(E139=E$2:E139)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E138)*(E2=E$1:E138))))))</f>
-        <v> </v>
-      </c>
-      <c r="K139" s="26" t="str">
-        <f>IF(OR(E139="",E139="!!!",F139="NEW"),"",INDEX(J$1:J138,SUMPRODUCT(MAX(ROW(E$1:E138)*(E139=E$1:E138)))))</f>
-        <v> </v>
-      </c>
-      <c r="L139" s="27"/>
+      <c r="A139" s="20"/>
     </row>
     <row r="140" spans="1:12">
       <c r="A140" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="B140" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C140" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D140" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="E140" s="22">
-        <f>IF(D140="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F140" s="23" t="str">
-        <f>IF(OR(E140="",E140="!!!"),"",IF(NOT(ISNA(VLOOKUP(E140,E$1:E139,1,FALSE()))),"OLD",IF(AND(E140&lt;&gt;"",E140&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G140" s="24" t="str">
-        <f>IF(OR(E140="",E140="!!!"),"",IF(OR(J140=0,AND(J140=1,K140=1),AND(J140=1,I140="SBJ"),AND(J140=1,I140=0)),"?IN_FOCUS",IF(J140&lt;=2,"?ACTIVATED",IF(J140&lt;&gt;"","?FAMILIAR",IF(F140="NEW",IF(ISNA(VLOOKUP(E140,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H140" s="25" t="str">
-        <f>IF(J140&lt;&gt;1,"",IF(I140="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I140" s="26" t="str">
-        <f>IF(OR(E140="",E140="!!!",F140="NEW"),"",INDEX(B139:B$2,-1+SUMPRODUCT(MAX(ROW(E139:E$2)*(E140=E139:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J140" s="26" t="str">
-        <f>IF(OR(E140="",E140="!!!",F140="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E140)*(E140=E$2:E140)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E139)*(E2=E$1:E139))))))</f>
-        <v> </v>
-      </c>
-      <c r="K140" s="26" t="str">
-        <f>IF(OR(E140="",E140="!!!",F140="NEW"),"",INDEX(J$1:J139,SUMPRODUCT(MAX(ROW(E$1:E139)*(E140=E$1:E139)))))</f>
-        <v> </v>
-      </c>
-      <c r="L140" s="27"/>
+        <v>195</v>
+      </c>
     </row>
     <row r="141" spans="1:12">
       <c r="A141" s="20" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E141" s="22">
         <f>IF(D141="?OLD","!!!","")</f>
@@ -6899,7 +6873,16 @@
     </row>
     <row r="142" spans="1:12">
       <c r="A142" s="20" t="s">
-        <v>184</v>
+        <v>89</v>
+      </c>
+      <c r="B142" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C142" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D142" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E142" s="22">
         <f>IF(D142="?OLD","!!!","")</f>
@@ -6933,7 +6916,7 @@
     </row>
     <row r="143" spans="1:12">
       <c r="A143" s="20" t="s">
-        <v>106</v>
+        <v>197</v>
       </c>
       <c r="E143" s="22">
         <f>IF(D143="?OLD","!!!","")</f>
@@ -6967,7 +6950,7 @@
     </row>
     <row r="144" spans="1:12">
       <c r="A144" s="20" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E144" s="22">
         <f>IF(D144="?OLD","!!!","")</f>
@@ -7001,7 +6984,7 @@
     </row>
     <row r="145" spans="1:12">
       <c r="A145" s="20" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="E145" s="22">
         <f>IF(D145="?OLD","!!!","")</f>
@@ -7035,16 +7018,7 @@
     </row>
     <row r="146" spans="1:12">
       <c r="A146" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="B146" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C146" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="D146" s="21" t="s">
-        <v>100</v>
+        <v>198</v>
       </c>
       <c r="E146" s="22">
         <f>IF(D146="?OLD","!!!","")</f>
@@ -7078,16 +7052,7 @@
     </row>
     <row r="147" spans="1:12">
       <c r="A147" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="B147" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="C147" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D147" s="21" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="E147" s="22">
         <f>IF(D147="?OLD","!!!","")</f>
@@ -7121,7 +7086,16 @@
     </row>
     <row r="148" spans="1:12">
       <c r="A148" s="20" t="s">
-        <v>197</v>
+        <v>199</v>
+      </c>
+      <c r="B148" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C148" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D148" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E148" s="22">
         <f>IF(D148="?OLD","!!!","")</f>
@@ -7155,7 +7129,16 @@
     </row>
     <row r="149" spans="1:12">
       <c r="A149" s="20" t="s">
-        <v>160</v>
+        <v>200</v>
+      </c>
+      <c r="B149" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C149" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D149" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E149" s="22">
         <f>IF(D149="?OLD","!!!","")</f>
@@ -7189,16 +7172,7 @@
     </row>
     <row r="150" spans="1:12">
       <c r="A150" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="B150" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C150" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D150" s="21" t="s">
-        <v>100</v>
+        <v>201</v>
       </c>
       <c r="E150" s="22">
         <f>IF(D150="?OLD","!!!","")</f>
@@ -7232,7 +7206,7 @@
     </row>
     <row r="151" spans="1:12">
       <c r="A151" s="20" t="s">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="E151" s="22">
         <f>IF(D151="?OLD","!!!","")</f>
@@ -7266,13 +7240,16 @@
     </row>
     <row r="152" spans="1:12">
       <c r="A152" s="20" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B152" s="21" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C152" s="21" t="s">
-        <v>123</v>
+        <v>103</v>
+      </c>
+      <c r="D152" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E152" s="22">
         <f>IF(D152="?OLD","!!!","")</f>
@@ -7306,7 +7283,7 @@
     </row>
     <row r="153" spans="1:12">
       <c r="A153" s="20" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E153" s="22">
         <f>IF(D153="?OLD","!!!","")</f>
@@ -7340,7 +7317,13 @@
     </row>
     <row r="154" spans="1:12">
       <c r="A154" s="20" t="s">
-        <v>189</v>
+        <v>204</v>
+      </c>
+      <c r="B154" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C154" s="21" t="s">
+        <v>127</v>
       </c>
       <c r="E154" s="22">
         <f>IF(D154="?OLD","!!!","")</f>
@@ -7374,7 +7357,7 @@
     </row>
     <row r="155" spans="1:12">
       <c r="A155" s="20" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E155" s="22">
         <f>IF(D155="?OLD","!!!","")</f>
@@ -7408,7 +7391,7 @@
     </row>
     <row r="156" spans="1:12">
       <c r="A156" s="20" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="E156" s="22">
         <f>IF(D156="?OLD","!!!","")</f>
@@ -7442,7 +7425,7 @@
     </row>
     <row r="157" spans="1:12">
       <c r="A157" s="20" t="s">
-        <v>106</v>
+        <v>206</v>
       </c>
       <c r="E157" s="22">
         <f>IF(D157="?OLD","!!!","")</f>
@@ -7476,7 +7459,7 @@
     </row>
     <row r="158" spans="1:12">
       <c r="A158" s="20" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E158" s="22">
         <f>IF(D158="?OLD","!!!","")</f>
@@ -7510,7 +7493,7 @@
     </row>
     <row r="159" spans="1:12">
       <c r="A159" s="20" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="E159" s="22">
         <f>IF(D159="?OLD","!!!","")</f>
@@ -7544,16 +7527,7 @@
     </row>
     <row r="160" spans="1:12">
       <c r="A160" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="B160" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="C160" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D160" s="21" t="s">
-        <v>100</v>
+        <v>208</v>
       </c>
       <c r="E160" s="22">
         <f>IF(D160="?OLD","!!!","")</f>
@@ -7587,7 +7561,7 @@
     </row>
     <row r="161" spans="1:12">
       <c r="A161" s="20" t="s">
-        <v>197</v>
+        <v>131</v>
       </c>
       <c r="E161" s="22">
         <f>IF(D161="?OLD","!!!","")</f>
@@ -7621,7 +7595,16 @@
     </row>
     <row r="162" spans="1:12">
       <c r="A162" s="20" t="s">
-        <v>107</v>
+        <v>209</v>
+      </c>
+      <c r="B162" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C162" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D162" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E162" s="22">
         <f>IF(D162="?OLD","!!!","")</f>
@@ -7655,16 +7638,7 @@
     </row>
     <row r="163" spans="1:12">
       <c r="A163" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="B163" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="C163" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D163" s="21" t="s">
-        <v>100</v>
+        <v>201</v>
       </c>
       <c r="E163" s="22">
         <f>IF(D163="?OLD","!!!","")</f>
@@ -7698,7 +7672,7 @@
     </row>
     <row r="164" spans="1:12">
       <c r="A164" s="20" t="s">
-        <v>207</v>
+        <v>113</v>
       </c>
       <c r="E164" s="22">
         <f>IF(D164="?OLD","!!!","")</f>
@@ -7732,7 +7706,16 @@
     </row>
     <row r="165" spans="1:12">
       <c r="A165" s="20" t="s">
-        <v>107</v>
+        <v>210</v>
+      </c>
+      <c r="B165" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C165" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D165" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E165" s="22">
         <f>IF(D165="?OLD","!!!","")</f>
@@ -7766,16 +7749,7 @@
     </row>
     <row r="166" spans="1:12">
       <c r="A166" s="20" t="s">
-        <v>208</v>
-      </c>
-      <c r="B166" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C166" s="21" t="s">
-        <v>209</v>
-      </c>
-      <c r="D166" s="21" t="s">
-        <v>100</v>
+        <v>211</v>
       </c>
       <c r="E166" s="22">
         <f>IF(D166="?OLD","!!!","")</f>
@@ -7809,7 +7783,7 @@
     </row>
     <row r="167" spans="1:12">
       <c r="A167" s="20" t="s">
-        <v>210</v>
+        <v>113</v>
       </c>
       <c r="E167" s="22">
         <f>IF(D167="?OLD","!!!","")</f>
@@ -7843,7 +7817,16 @@
     </row>
     <row r="168" spans="1:12">
       <c r="A168" s="20" t="s">
-        <v>211</v>
+        <v>212</v>
+      </c>
+      <c r="B168" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C168" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="D168" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E168" s="22">
         <f>IF(D168="?OLD","!!!","")</f>
@@ -7877,7 +7860,7 @@
     </row>
     <row r="169" spans="1:12">
       <c r="A169" s="20" t="s">
-        <v>106</v>
+        <v>214</v>
       </c>
       <c r="E169" s="22">
         <f>IF(D169="?OLD","!!!","")</f>
@@ -7911,10 +7894,7 @@
     </row>
     <row r="170" spans="1:12">
       <c r="A170" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="B170" s="21" t="s">
-        <v>124</v>
+        <v>215</v>
       </c>
       <c r="E170" s="22">
         <f>IF(D170="?OLD","!!!","")</f>
@@ -7948,7 +7928,7 @@
     </row>
     <row r="171" spans="1:12">
       <c r="A171" s="20" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="E171" s="22">
         <f>IF(D171="?OLD","!!!","")</f>
@@ -7982,7 +7962,10 @@
     </row>
     <row r="172" spans="1:12">
       <c r="A172" s="20" t="s">
-        <v>93</v>
+        <v>113</v>
+      </c>
+      <c r="B172" s="21" t="s">
+        <v>128</v>
       </c>
       <c r="E172" s="22">
         <f>IF(D172="?OLD","!!!","")</f>
@@ -8016,7 +7999,7 @@
     </row>
     <row r="173" spans="1:12">
       <c r="A173" s="20" t="s">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="E173" s="22">
         <f>IF(D173="?OLD","!!!","")</f>
@@ -8050,16 +8033,7 @@
     </row>
     <row r="174" spans="1:12">
       <c r="A174" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="B174" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C174" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D174" s="21" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E174" s="22">
         <f>IF(D174="?OLD","!!!","")</f>
@@ -8093,15 +8067,6 @@
     </row>
     <row r="175" spans="1:12">
       <c r="A175" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="B175" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="C175" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="D175" s="21" t="s">
         <v>100</v>
       </c>
       <c r="E175" s="22">
@@ -8136,7 +8101,16 @@
     </row>
     <row r="176" spans="1:12">
       <c r="A176" s="20" t="s">
-        <v>127</v>
+        <v>216</v>
+      </c>
+      <c r="B176" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C176" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D176" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E176" s="22">
         <f>IF(D176="?OLD","!!!","")</f>
@@ -8170,7 +8144,16 @@
     </row>
     <row r="177" spans="1:12">
       <c r="A177" s="20" t="s">
-        <v>213</v>
+        <v>165</v>
+      </c>
+      <c r="B177" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C177" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D177" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E177" s="22">
         <f>IF(D177="?OLD","!!!","")</f>
@@ -8204,16 +8187,7 @@
     </row>
     <row r="178" spans="1:12">
       <c r="A178" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="B178" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="C178" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D178" s="21" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="E178" s="22">
         <f>IF(D178="?OLD","!!!","")</f>
@@ -8247,7 +8221,7 @@
     </row>
     <row r="179" spans="1:12">
       <c r="A179" s="20" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E179" s="22">
         <f>IF(D179="?OLD","!!!","")</f>
@@ -8281,7 +8255,16 @@
     </row>
     <row r="180" spans="1:12">
       <c r="A180" s="20" t="s">
-        <v>147</v>
+        <v>93</v>
+      </c>
+      <c r="B180" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="C180" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D180" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E180" s="22">
         <f>IF(D180="?OLD","!!!","")</f>
@@ -8314,93 +8297,84 @@
       <c r="L180" s="27"/>
     </row>
     <row r="181" spans="1:12">
-      <c r="A181" s="20"/>
+      <c r="A181" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="E181" s="22">
+        <f>IF(D181="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F181" s="23" t="str">
+        <f>IF(OR(E181="",E181="!!!"),"",IF(NOT(ISNA(VLOOKUP(E181,E$1:E180,1,FALSE()))),"OLD",IF(AND(E181&lt;&gt;"",E181&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G181" s="24" t="str">
+        <f>IF(OR(E181="",E181="!!!"),"",IF(OR(J181=0,AND(J181=1,K181=1),AND(J181=1,I181="SBJ"),AND(J181=1,I181=0)),"?IN_FOCUS",IF(J181&lt;=2,"?ACTIVATED",IF(J181&lt;&gt;"","?FAMILIAR",IF(F181="NEW",IF(ISNA(VLOOKUP(E181,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H181" s="25" t="str">
+        <f>IF(J181&lt;&gt;1,"",IF(I181="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I181" s="26" t="str">
+        <f>IF(OR(E181="",E181="!!!",F181="NEW"),"",INDEX(B180:B$2,-1+SUMPRODUCT(MAX(ROW(E180:E$2)*(E181=E180:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J181" s="26" t="str">
+        <f>IF(OR(E181="",E181="!!!",F181="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E181)*(E181=E$2:E181)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E180)*(E2=E$1:E180))))))</f>
+        <v> </v>
+      </c>
+      <c r="K181" s="26" t="str">
+        <f>IF(OR(E181="",E181="!!!",F181="NEW"),"",INDEX(J$1:J180,SUMPRODUCT(MAX(ROW(E$1:E180)*(E181=E$1:E180)))))</f>
+        <v> </v>
+      </c>
+      <c r="L181" s="27"/>
     </row>
     <row r="182" spans="1:12">
       <c r="A182" s="20" t="s">
-        <v>216</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E182" s="22">
+        <f>IF(D182="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F182" s="23" t="str">
+        <f>IF(OR(E182="",E182="!!!"),"",IF(NOT(ISNA(VLOOKUP(E182,E$1:E181,1,FALSE()))),"OLD",IF(AND(E182&lt;&gt;"",E182&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G182" s="24" t="str">
+        <f>IF(OR(E182="",E182="!!!"),"",IF(OR(J182=0,AND(J182=1,K182=1),AND(J182=1,I182="SBJ"),AND(J182=1,I182=0)),"?IN_FOCUS",IF(J182&lt;=2,"?ACTIVATED",IF(J182&lt;&gt;"","?FAMILIAR",IF(F182="NEW",IF(ISNA(VLOOKUP(E182,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H182" s="25" t="str">
+        <f>IF(J182&lt;&gt;1,"",IF(I182="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I182" s="26" t="str">
+        <f>IF(OR(E182="",E182="!!!",F182="NEW"),"",INDEX(B181:B$2,-1+SUMPRODUCT(MAX(ROW(E181:E$2)*(E182=E181:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J182" s="26" t="str">
+        <f>IF(OR(E182="",E182="!!!",F182="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E182)*(E182=E$2:E182)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E181)*(E2=E$1:E181))))))</f>
+        <v> </v>
+      </c>
+      <c r="K182" s="26" t="str">
+        <f>IF(OR(E182="",E182="!!!",F182="NEW"),"",INDEX(J$1:J181,SUMPRODUCT(MAX(ROW(E$1:E181)*(E182=E$1:E181)))))</f>
+        <v> </v>
+      </c>
+      <c r="L182" s="27"/>
     </row>
     <row r="183" spans="1:12">
-      <c r="A183" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="E183" s="22">
-        <f>IF(D183="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F183" s="23" t="str">
-        <f>IF(OR(E183="",E183="!!!"),"",IF(NOT(ISNA(VLOOKUP(E183,E$1:E182,1,FALSE()))),"OLD",IF(AND(E183&lt;&gt;"",E183&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G183" s="24" t="str">
-        <f>IF(OR(E183="",E183="!!!"),"",IF(OR(J183=0,AND(J183=1,K183=1),AND(J183=1,I183="SBJ"),AND(J183=1,I183=0)),"?IN_FOCUS",IF(J183&lt;=2,"?ACTIVATED",IF(J183&lt;&gt;"","?FAMILIAR",IF(F183="NEW",IF(ISNA(VLOOKUP(E183,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H183" s="25" t="str">
-        <f>IF(J183&lt;&gt;1,"",IF(I183="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I183" s="26" t="str">
-        <f>IF(OR(E183="",E183="!!!",F183="NEW"),"",INDEX(B182:B$2,-1+SUMPRODUCT(MAX(ROW(E182:E$2)*(E183=E182:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J183" s="26" t="str">
-        <f>IF(OR(E183="",E183="!!!",F183="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E183)*(E183=E$2:E183)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E182)*(E2=E$1:E182))))))</f>
-        <v> </v>
-      </c>
-      <c r="K183" s="26" t="str">
-        <f>IF(OR(E183="",E183="!!!",F183="NEW"),"",INDEX(J$1:J182,SUMPRODUCT(MAX(ROW(E$1:E182)*(E183=E$1:E182)))))</f>
-        <v> </v>
-      </c>
-      <c r="L183" s="27"/>
+      <c r="A183" s="20"/>
     </row>
     <row r="184" spans="1:12">
       <c r="A184" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B184" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C184" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D184" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="E184" s="22">
-        <f>IF(D184="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F184" s="23" t="str">
-        <f>IF(OR(E184="",E184="!!!"),"",IF(NOT(ISNA(VLOOKUP(E184,E$1:E183,1,FALSE()))),"OLD",IF(AND(E184&lt;&gt;"",E184&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G184" s="24" t="str">
-        <f>IF(OR(E184="",E184="!!!"),"",IF(OR(J184=0,AND(J184=1,K184=1),AND(J184=1,I184="SBJ"),AND(J184=1,I184=0)),"?IN_FOCUS",IF(J184&lt;=2,"?ACTIVATED",IF(J184&lt;&gt;"","?FAMILIAR",IF(F184="NEW",IF(ISNA(VLOOKUP(E184,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H184" s="25" t="str">
-        <f>IF(J184&lt;&gt;1,"",IF(I184="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I184" s="26" t="str">
-        <f>IF(OR(E184="",E184="!!!",F184="NEW"),"",INDEX(B183:B$2,-1+SUMPRODUCT(MAX(ROW(E183:E$2)*(E184=E183:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J184" s="26" t="str">
-        <f>IF(OR(E184="",E184="!!!",F184="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E184)*(E184=E$2:E184)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E183)*(E2=E$1:E183))))))</f>
-        <v> </v>
-      </c>
-      <c r="K184" s="26" t="str">
-        <f>IF(OR(E184="",E184="!!!",F184="NEW"),"",INDEX(J$1:J183,SUMPRODUCT(MAX(ROW(E$1:E183)*(E184=E$1:E183)))))</f>
-        <v> </v>
-      </c>
-      <c r="L184" s="27"/>
+        <v>220</v>
+      </c>
     </row>
     <row r="185" spans="1:12">
       <c r="A185" s="20" t="s">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="E185" s="22">
         <f>IF(D185="?OLD","!!!","")</f>
@@ -8434,16 +8408,16 @@
     </row>
     <row r="186" spans="1:12">
       <c r="A186" s="20" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="B186" s="21" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="C186" s="21" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D186" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E186" s="22">
         <f>IF(D186="?OLD","!!!","")</f>
@@ -8477,7 +8451,7 @@
     </row>
     <row r="187" spans="1:12">
       <c r="A187" s="20" t="s">
-        <v>217</v>
+        <v>137</v>
       </c>
       <c r="E187" s="22">
         <f>IF(D187="?OLD","!!!","")</f>
@@ -8511,7 +8485,16 @@
     </row>
     <row r="188" spans="1:12">
       <c r="A188" s="20" t="s">
-        <v>147</v>
+        <v>138</v>
+      </c>
+      <c r="B188" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C188" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D188" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E188" s="22">
         <f>IF(D188="?OLD","!!!","")</f>
@@ -8544,93 +8527,93 @@
       <c r="L188" s="27"/>
     </row>
     <row r="189" spans="1:12">
-      <c r="A189" s="20"/>
+      <c r="A189" s="20" t="s">
+        <v>221</v>
+      </c>
+      <c r="E189" s="22">
+        <f>IF(D189="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F189" s="23" t="str">
+        <f>IF(OR(E189="",E189="!!!"),"",IF(NOT(ISNA(VLOOKUP(E189,E$1:E188,1,FALSE()))),"OLD",IF(AND(E189&lt;&gt;"",E189&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G189" s="24" t="str">
+        <f>IF(OR(E189="",E189="!!!"),"",IF(OR(J189=0,AND(J189=1,K189=1),AND(J189=1,I189="SBJ"),AND(J189=1,I189=0)),"?IN_FOCUS",IF(J189&lt;=2,"?ACTIVATED",IF(J189&lt;&gt;"","?FAMILIAR",IF(F189="NEW",IF(ISNA(VLOOKUP(E189,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H189" s="25" t="str">
+        <f>IF(J189&lt;&gt;1,"",IF(I189="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I189" s="26" t="str">
+        <f>IF(OR(E189="",E189="!!!",F189="NEW"),"",INDEX(B188:B$2,-1+SUMPRODUCT(MAX(ROW(E188:E$2)*(E189=E188:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J189" s="26" t="str">
+        <f>IF(OR(E189="",E189="!!!",F189="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E189)*(E189=E$2:E189)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E188)*(E2=E$1:E188))))))</f>
+        <v> </v>
+      </c>
+      <c r="K189" s="26" t="str">
+        <f>IF(OR(E189="",E189="!!!",F189="NEW"),"",INDEX(J$1:J188,SUMPRODUCT(MAX(ROW(E$1:E188)*(E189=E$1:E188)))))</f>
+        <v> </v>
+      </c>
+      <c r="L189" s="27"/>
     </row>
     <row r="190" spans="1:12">
       <c r="A190" s="20" t="s">
-        <v>218</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E190" s="22">
+        <f>IF(D190="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F190" s="23" t="str">
+        <f>IF(OR(E190="",E190="!!!"),"",IF(NOT(ISNA(VLOOKUP(E190,E$1:E189,1,FALSE()))),"OLD",IF(AND(E190&lt;&gt;"",E190&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G190" s="24" t="str">
+        <f>IF(OR(E190="",E190="!!!"),"",IF(OR(J190=0,AND(J190=1,K190=1),AND(J190=1,I190="SBJ"),AND(J190=1,I190=0)),"?IN_FOCUS",IF(J190&lt;=2,"?ACTIVATED",IF(J190&lt;&gt;"","?FAMILIAR",IF(F190="NEW",IF(ISNA(VLOOKUP(E190,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H190" s="25" t="str">
+        <f>IF(J190&lt;&gt;1,"",IF(I190="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I190" s="26" t="str">
+        <f>IF(OR(E190="",E190="!!!",F190="NEW"),"",INDEX(B189:B$2,-1+SUMPRODUCT(MAX(ROW(E189:E$2)*(E190=E189:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J190" s="26" t="str">
+        <f>IF(OR(E190="",E190="!!!",F190="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E190)*(E190=E$2:E190)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E189)*(E2=E$1:E189))))))</f>
+        <v> </v>
+      </c>
+      <c r="K190" s="26" t="str">
+        <f>IF(OR(E190="",E190="!!!",F190="NEW"),"",INDEX(J$1:J189,SUMPRODUCT(MAX(ROW(E$1:E189)*(E190=E$1:E189)))))</f>
+        <v> </v>
+      </c>
+      <c r="L190" s="27"/>
     </row>
     <row r="191" spans="1:12">
-      <c r="A191" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="B191" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C191" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D191" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="E191" s="22">
-        <f>IF(D191="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F191" s="23" t="str">
-        <f>IF(OR(E191="",E191="!!!"),"",IF(NOT(ISNA(VLOOKUP(E191,E$1:E190,1,FALSE()))),"OLD",IF(AND(E191&lt;&gt;"",E191&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G191" s="24" t="str">
-        <f>IF(OR(E191="",E191="!!!"),"",IF(OR(J191=0,AND(J191=1,K191=1),AND(J191=1,I191="SBJ"),AND(J191=1,I191=0)),"?IN_FOCUS",IF(J191&lt;=2,"?ACTIVATED",IF(J191&lt;&gt;"","?FAMILIAR",IF(F191="NEW",IF(ISNA(VLOOKUP(E191,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H191" s="25" t="str">
-        <f>IF(J191&lt;&gt;1,"",IF(I191="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I191" s="26" t="str">
-        <f>IF(OR(E191="",E191="!!!",F191="NEW"),"",INDEX(B190:B$2,-1+SUMPRODUCT(MAX(ROW(E190:E$2)*(E191=E190:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J191" s="26" t="str">
-        <f>IF(OR(E191="",E191="!!!",F191="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E191)*(E191=E$2:E191)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E190)*(E2=E$1:E190))))))</f>
-        <v> </v>
-      </c>
-      <c r="K191" s="26" t="str">
-        <f>IF(OR(E191="",E191="!!!",F191="NEW"),"",INDEX(J$1:J190,SUMPRODUCT(MAX(ROW(E$1:E190)*(E191=E$1:E190)))))</f>
-        <v> </v>
-      </c>
-      <c r="L191" s="27"/>
+      <c r="A191" s="20"/>
     </row>
     <row r="192" spans="1:12">
       <c r="A192" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="E192" s="22">
-        <f>IF(D192="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F192" s="23" t="str">
-        <f>IF(OR(E192="",E192="!!!"),"",IF(NOT(ISNA(VLOOKUP(E192,E$1:E191,1,FALSE()))),"OLD",IF(AND(E192&lt;&gt;"",E192&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G192" s="24" t="str">
-        <f>IF(OR(E192="",E192="!!!"),"",IF(OR(J192=0,AND(J192=1,K192=1),AND(J192=1,I192="SBJ"),AND(J192=1,I192=0)),"?IN_FOCUS",IF(J192&lt;=2,"?ACTIVATED",IF(J192&lt;&gt;"","?FAMILIAR",IF(F192="NEW",IF(ISNA(VLOOKUP(E192,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H192" s="25" t="str">
-        <f>IF(J192&lt;&gt;1,"",IF(I192="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I192" s="26" t="str">
-        <f>IF(OR(E192="",E192="!!!",F192="NEW"),"",INDEX(B191:B$2,-1+SUMPRODUCT(MAX(ROW(E191:E$2)*(E192=E191:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J192" s="26" t="str">
-        <f>IF(OR(E192="",E192="!!!",F192="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E192)*(E192=E$2:E192)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E191)*(E2=E$1:E191))))))</f>
-        <v> </v>
-      </c>
-      <c r="K192" s="26" t="str">
-        <f>IF(OR(E192="",E192="!!!",F192="NEW"),"",INDEX(J$1:J191,SUMPRODUCT(MAX(ROW(E$1:E191)*(E192=E$1:E191)))))</f>
-        <v> </v>
-      </c>
-      <c r="L192" s="27"/>
+        <v>222</v>
+      </c>
     </row>
     <row r="193" spans="1:12">
       <c r="A193" s="20" t="s">
-        <v>221</v>
+        <v>223</v>
+      </c>
+      <c r="B193" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C193" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D193" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E193" s="22">
         <f>IF(D193="?OLD","!!!","")</f>
@@ -8664,7 +8647,7 @@
     </row>
     <row r="194" spans="1:12">
       <c r="A194" s="20" t="s">
-        <v>106</v>
+        <v>224</v>
       </c>
       <c r="E194" s="22">
         <f>IF(D194="?OLD","!!!","")</f>
@@ -8698,7 +8681,7 @@
     </row>
     <row r="195" spans="1:12">
       <c r="A195" s="20" t="s">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="E195" s="22">
         <f>IF(D195="?OLD","!!!","")</f>
@@ -8732,7 +8715,7 @@
     </row>
     <row r="196" spans="1:12">
       <c r="A196" s="20" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E196" s="22">
         <f>IF(D196="?OLD","!!!","")</f>
@@ -8766,16 +8749,7 @@
     </row>
     <row r="197" spans="1:12">
       <c r="A197" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="B197" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="C197" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D197" s="21" t="s">
-        <v>100</v>
+        <v>198</v>
       </c>
       <c r="E197" s="22">
         <f>IF(D197="?OLD","!!!","")</f>
@@ -8809,7 +8783,7 @@
     </row>
     <row r="198" spans="1:12">
       <c r="A198" s="20" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E198" s="22">
         <f>IF(D198="?OLD","!!!","")</f>
@@ -8843,16 +8817,16 @@
     </row>
     <row r="199" spans="1:12">
       <c r="A199" s="20" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B199" s="21" t="s">
-        <v>214</v>
+        <v>128</v>
       </c>
       <c r="C199" s="21" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D199" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E199" s="22">
         <f>IF(D199="?OLD","!!!","")</f>
@@ -8886,7 +8860,7 @@
     </row>
     <row r="200" spans="1:12">
       <c r="A200" s="20" t="s">
-        <v>224</v>
+        <v>113</v>
       </c>
       <c r="E200" s="22">
         <f>IF(D200="?OLD","!!!","")</f>
@@ -8920,7 +8894,16 @@
     </row>
     <row r="201" spans="1:12">
       <c r="A201" s="20" t="s">
-        <v>225</v>
+        <v>227</v>
+      </c>
+      <c r="B201" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="C201" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D201" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E201" s="22">
         <f>IF(D201="?OLD","!!!","")</f>
@@ -8954,7 +8937,7 @@
     </row>
     <row r="202" spans="1:12">
       <c r="A202" s="20" t="s">
-        <v>106</v>
+        <v>228</v>
       </c>
       <c r="E202" s="22">
         <f>IF(D202="?OLD","!!!","")</f>
@@ -8988,7 +8971,7 @@
     </row>
     <row r="203" spans="1:12">
       <c r="A203" s="20" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E203" s="22">
         <f>IF(D203="?OLD","!!!","")</f>
@@ -9022,7 +9005,7 @@
     </row>
     <row r="204" spans="1:12">
       <c r="A204" s="20" t="s">
-        <v>227</v>
+        <v>112</v>
       </c>
       <c r="E204" s="22">
         <f>IF(D204="?OLD","!!!","")</f>
@@ -9056,13 +9039,7 @@
     </row>
     <row r="205" spans="1:12">
       <c r="A205" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="B205" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C205" s="21" t="s">
-        <v>123</v>
+        <v>230</v>
       </c>
       <c r="E205" s="22">
         <f>IF(D205="?OLD","!!!","")</f>
@@ -9096,7 +9073,7 @@
     </row>
     <row r="206" spans="1:12">
       <c r="A206" s="20" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E206" s="22">
         <f>IF(D206="?OLD","!!!","")</f>
@@ -9130,7 +9107,13 @@
     </row>
     <row r="207" spans="1:12">
       <c r="A207" s="20" t="s">
-        <v>189</v>
+        <v>232</v>
+      </c>
+      <c r="B207" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C207" s="21" t="s">
+        <v>127</v>
       </c>
       <c r="E207" s="22">
         <f>IF(D207="?OLD","!!!","")</f>
@@ -9164,7 +9147,7 @@
     </row>
     <row r="208" spans="1:12">
       <c r="A208" s="20" t="s">
-        <v>18</v>
+        <v>233</v>
       </c>
       <c r="E208" s="22">
         <f>IF(D208="?OLD","!!!","")</f>
@@ -9198,7 +9181,7 @@
     </row>
     <row r="209" spans="1:12">
       <c r="A209" s="20" t="s">
-        <v>106</v>
+        <v>193</v>
       </c>
       <c r="E209" s="22">
         <f>IF(D209="?OLD","!!!","")</f>
@@ -9232,7 +9215,7 @@
     </row>
     <row r="210" spans="1:12">
       <c r="A210" s="20" t="s">
-        <v>230</v>
+        <v>22</v>
       </c>
       <c r="E210" s="22">
         <f>IF(D210="?OLD","!!!","")</f>
@@ -9266,16 +9249,7 @@
     </row>
     <row r="211" spans="1:12">
       <c r="A211" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="B211" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="C211" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="D211" s="21" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E211" s="22">
         <f>IF(D211="?OLD","!!!","")</f>
@@ -9309,7 +9283,7 @@
     </row>
     <row r="212" spans="1:12">
       <c r="A212" s="20" t="s">
-        <v>184</v>
+        <v>234</v>
       </c>
       <c r="E212" s="22">
         <f>IF(D212="?OLD","!!!","")</f>
@@ -9343,7 +9317,16 @@
     </row>
     <row r="213" spans="1:12">
       <c r="A213" s="20" t="s">
-        <v>231</v>
+        <v>142</v>
+      </c>
+      <c r="B213" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C213" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D213" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E213" s="22">
         <f>IF(D213="?OLD","!!!","")</f>
@@ -9377,7 +9360,7 @@
     </row>
     <row r="214" spans="1:12">
       <c r="A214" s="20" t="s">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="E214" s="22">
         <f>IF(D214="?OLD","!!!","")</f>
@@ -9411,13 +9394,7 @@
     </row>
     <row r="215" spans="1:12">
       <c r="A215" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="B215" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C215" s="21" t="s">
-        <v>92</v>
+        <v>235</v>
       </c>
       <c r="E215" s="22">
         <f>IF(D215="?OLD","!!!","")</f>
@@ -9451,7 +9428,7 @@
     </row>
     <row r="216" spans="1:12">
       <c r="A216" s="20" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E216" s="22">
         <f>IF(D216="?OLD","!!!","")</f>
@@ -9485,7 +9462,13 @@
     </row>
     <row r="217" spans="1:12">
       <c r="A217" s="20" t="s">
-        <v>187</v>
+        <v>237</v>
+      </c>
+      <c r="B217" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C217" s="21" t="s">
+        <v>95</v>
       </c>
       <c r="E217" s="22">
         <f>IF(D217="?OLD","!!!","")</f>
@@ -9519,7 +9502,7 @@
     </row>
     <row r="218" spans="1:12">
       <c r="A218" s="20" t="s">
-        <v>147</v>
+        <v>238</v>
       </c>
       <c r="E218" s="22">
         <f>IF(D218="?OLD","!!!","")</f>
@@ -9552,84 +9535,84 @@
       <c r="L218" s="27"/>
     </row>
     <row r="219" spans="1:12">
-      <c r="A219" s="20"/>
+      <c r="A219" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="E219" s="22">
+        <f>IF(D219="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F219" s="23" t="str">
+        <f>IF(OR(E219="",E219="!!!"),"",IF(NOT(ISNA(VLOOKUP(E219,E$1:E218,1,FALSE()))),"OLD",IF(AND(E219&lt;&gt;"",E219&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G219" s="24" t="str">
+        <f>IF(OR(E219="",E219="!!!"),"",IF(OR(J219=0,AND(J219=1,K219=1),AND(J219=1,I219="SBJ"),AND(J219=1,I219=0)),"?IN_FOCUS",IF(J219&lt;=2,"?ACTIVATED",IF(J219&lt;&gt;"","?FAMILIAR",IF(F219="NEW",IF(ISNA(VLOOKUP(E219,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H219" s="25" t="str">
+        <f>IF(J219&lt;&gt;1,"",IF(I219="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I219" s="26" t="str">
+        <f>IF(OR(E219="",E219="!!!",F219="NEW"),"",INDEX(B218:B$2,-1+SUMPRODUCT(MAX(ROW(E218:E$2)*(E219=E218:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J219" s="26" t="str">
+        <f>IF(OR(E219="",E219="!!!",F219="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E219)*(E219=E$2:E219)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E218)*(E2=E$1:E218))))))</f>
+        <v> </v>
+      </c>
+      <c r="K219" s="26" t="str">
+        <f>IF(OR(E219="",E219="!!!",F219="NEW"),"",INDEX(J$1:J218,SUMPRODUCT(MAX(ROW(E$1:E218)*(E219=E$1:E218)))))</f>
+        <v> </v>
+      </c>
+      <c r="L219" s="27"/>
     </row>
     <row r="220" spans="1:12">
       <c r="A220" s="20" t="s">
-        <v>235</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E220" s="22">
+        <f>IF(D220="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F220" s="23" t="str">
+        <f>IF(OR(E220="",E220="!!!"),"",IF(NOT(ISNA(VLOOKUP(E220,E$1:E219,1,FALSE()))),"OLD",IF(AND(E220&lt;&gt;"",E220&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G220" s="24" t="str">
+        <f>IF(OR(E220="",E220="!!!"),"",IF(OR(J220=0,AND(J220=1,K220=1),AND(J220=1,I220="SBJ"),AND(J220=1,I220=0)),"?IN_FOCUS",IF(J220&lt;=2,"?ACTIVATED",IF(J220&lt;&gt;"","?FAMILIAR",IF(F220="NEW",IF(ISNA(VLOOKUP(E220,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H220" s="25" t="str">
+        <f>IF(J220&lt;&gt;1,"",IF(I220="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I220" s="26" t="str">
+        <f>IF(OR(E220="",E220="!!!",F220="NEW"),"",INDEX(B219:B$2,-1+SUMPRODUCT(MAX(ROW(E219:E$2)*(E220=E219:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J220" s="26" t="str">
+        <f>IF(OR(E220="",E220="!!!",F220="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E220)*(E220=E$2:E220)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E219)*(E2=E$1:E219))))))</f>
+        <v> </v>
+      </c>
+      <c r="K220" s="26" t="str">
+        <f>IF(OR(E220="",E220="!!!",F220="NEW"),"",INDEX(J$1:J219,SUMPRODUCT(MAX(ROW(E$1:E219)*(E220=E$1:E219)))))</f>
+        <v> </v>
+      </c>
+      <c r="L220" s="27"/>
     </row>
     <row r="221" spans="1:12">
-      <c r="A221" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="E221" s="22">
-        <f>IF(D221="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F221" s="23" t="str">
-        <f>IF(OR(E221="",E221="!!!"),"",IF(NOT(ISNA(VLOOKUP(E221,E$1:E220,1,FALSE()))),"OLD",IF(AND(E221&lt;&gt;"",E221&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G221" s="24" t="str">
-        <f>IF(OR(E221="",E221="!!!"),"",IF(OR(J221=0,AND(J221=1,K221=1),AND(J221=1,I221="SBJ"),AND(J221=1,I221=0)),"?IN_FOCUS",IF(J221&lt;=2,"?ACTIVATED",IF(J221&lt;&gt;"","?FAMILIAR",IF(F221="NEW",IF(ISNA(VLOOKUP(E221,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H221" s="25" t="str">
-        <f>IF(J221&lt;&gt;1,"",IF(I221="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I221" s="26" t="str">
-        <f>IF(OR(E221="",E221="!!!",F221="NEW"),"",INDEX(B220:B$2,-1+SUMPRODUCT(MAX(ROW(E220:E$2)*(E221=E220:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J221" s="26" t="str">
-        <f>IF(OR(E221="",E221="!!!",F221="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E221)*(E221=E$2:E221)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E220)*(E2=E$1:E220))))))</f>
-        <v> </v>
-      </c>
-      <c r="K221" s="26" t="str">
-        <f>IF(OR(E221="",E221="!!!",F221="NEW"),"",INDEX(J$1:J220,SUMPRODUCT(MAX(ROW(E$1:E220)*(E221=E$1:E220)))))</f>
-        <v> </v>
-      </c>
-      <c r="L221" s="27"/>
+      <c r="A221" s="20"/>
     </row>
     <row r="222" spans="1:12">
       <c r="A222" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="E222" s="22">
-        <f>IF(D222="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F222" s="23" t="str">
-        <f>IF(OR(E222="",E222="!!!"),"",IF(NOT(ISNA(VLOOKUP(E222,E$1:E221,1,FALSE()))),"OLD",IF(AND(E222&lt;&gt;"",E222&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G222" s="24" t="str">
-        <f>IF(OR(E222="",E222="!!!"),"",IF(OR(J222=0,AND(J222=1,K222=1),AND(J222=1,I222="SBJ"),AND(J222=1,I222=0)),"?IN_FOCUS",IF(J222&lt;=2,"?ACTIVATED",IF(J222&lt;&gt;"","?FAMILIAR",IF(F222="NEW",IF(ISNA(VLOOKUP(E222,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H222" s="25" t="str">
-        <f>IF(J222&lt;&gt;1,"",IF(I222="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I222" s="26" t="str">
-        <f>IF(OR(E222="",E222="!!!",F222="NEW"),"",INDEX(B221:B$2,-1+SUMPRODUCT(MAX(ROW(E221:E$2)*(E222=E221:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J222" s="26" t="str">
-        <f>IF(OR(E222="",E222="!!!",F222="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E222)*(E222=E$2:E222)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E221)*(E2=E$1:E221))))))</f>
-        <v> </v>
-      </c>
-      <c r="K222" s="26" t="str">
-        <f>IF(OR(E222="",E222="!!!",F222="NEW"),"",INDEX(J$1:J221,SUMPRODUCT(MAX(ROW(E$1:E221)*(E222=E$1:E221)))))</f>
-        <v> </v>
-      </c>
-      <c r="L222" s="27"/>
+        <v>239</v>
+      </c>
     </row>
     <row r="223" spans="1:12">
       <c r="A223" s="20" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E223" s="22">
         <f>IF(D223="?OLD","!!!","")</f>
@@ -9663,7 +9646,7 @@
     </row>
     <row r="224" spans="1:12">
       <c r="A224" s="20" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="E224" s="22">
         <f>IF(D224="?OLD","!!!","")</f>
@@ -9697,7 +9680,7 @@
     </row>
     <row r="225" spans="1:12">
       <c r="A225" s="20" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E225" s="22">
         <f>IF(D225="?OLD","!!!","")</f>
@@ -9731,13 +9714,7 @@
     </row>
     <row r="226" spans="1:12">
       <c r="A226" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="B226" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C226" s="21" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E226" s="22">
         <f>IF(D226="?OLD","!!!","")</f>
@@ -9771,7 +9748,7 @@
     </row>
     <row r="227" spans="1:12">
       <c r="A227" s="20" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E227" s="22">
         <f>IF(D227="?OLD","!!!","")</f>
@@ -9805,7 +9782,13 @@
     </row>
     <row r="228" spans="1:12">
       <c r="A228" s="20" t="s">
-        <v>133</v>
+        <v>243</v>
+      </c>
+      <c r="B228" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C228" s="21" t="s">
+        <v>91</v>
       </c>
       <c r="E228" s="22">
         <f>IF(D228="?OLD","!!!","")</f>
@@ -9839,7 +9822,7 @@
     </row>
     <row r="229" spans="1:12">
       <c r="A229" s="20" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="E229" s="22">
         <f>IF(D229="?OLD","!!!","")</f>
@@ -9873,13 +9856,7 @@
     </row>
     <row r="230" spans="1:12">
       <c r="A230" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="B230" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C230" s="21" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="E230" s="22">
         <f>IF(D230="?OLD","!!!","")</f>
@@ -9913,7 +9890,7 @@
     </row>
     <row r="231" spans="1:12">
       <c r="A231" s="20" t="s">
-        <v>93</v>
+        <v>235</v>
       </c>
       <c r="E231" s="22">
         <f>IF(D231="?OLD","!!!","")</f>
@@ -9947,7 +9924,13 @@
     </row>
     <row r="232" spans="1:12">
       <c r="A232" s="20" t="s">
-        <v>242</v>
+        <v>245</v>
+      </c>
+      <c r="B232" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C232" s="21" t="s">
+        <v>95</v>
       </c>
       <c r="E232" s="22">
         <f>IF(D232="?OLD","!!!","")</f>
@@ -9981,13 +9964,7 @@
     </row>
     <row r="233" spans="1:12">
       <c r="A233" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="B233" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C233" s="21" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E233" s="22">
         <f>IF(D233="?OLD","!!!","")</f>
@@ -10021,7 +9998,7 @@
     </row>
     <row r="234" spans="1:12">
       <c r="A234" s="20" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E234" s="22">
         <f>IF(D234="?OLD","!!!","")</f>
@@ -10055,13 +10032,13 @@
     </row>
     <row r="235" spans="1:12">
       <c r="A235" s="20" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B235" s="21" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="C235" s="21" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E235" s="22">
         <f>IF(D235="?OLD","!!!","")</f>
@@ -10095,7 +10072,7 @@
     </row>
     <row r="236" spans="1:12">
       <c r="A236" s="20" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E236" s="22">
         <f>IF(D236="?OLD","!!!","")</f>
@@ -10129,7 +10106,13 @@
     </row>
     <row r="237" spans="1:12">
       <c r="A237" s="20" t="s">
-        <v>118</v>
+        <v>248</v>
+      </c>
+      <c r="B237" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C237" s="21" t="s">
+        <v>95</v>
       </c>
       <c r="E237" s="22">
         <f>IF(D237="?OLD","!!!","")</f>
@@ -10163,7 +10146,7 @@
     </row>
     <row r="238" spans="1:12">
       <c r="A238" s="20" t="s">
-        <v>115</v>
+        <v>249</v>
       </c>
       <c r="E238" s="22">
         <f>IF(D238="?OLD","!!!","")</f>
@@ -10197,7 +10180,7 @@
     </row>
     <row r="239" spans="1:12">
       <c r="A239" s="20" t="s">
-        <v>246</v>
+        <v>122</v>
       </c>
       <c r="E239" s="22">
         <f>IF(D239="?OLD","!!!","")</f>
@@ -10231,7 +10214,7 @@
     </row>
     <row r="240" spans="1:12">
       <c r="A240" s="20" t="s">
-        <v>247</v>
+        <v>120</v>
       </c>
       <c r="E240" s="22">
         <f>IF(D240="?OLD","!!!","")</f>
@@ -10265,7 +10248,7 @@
     </row>
     <row r="241" spans="1:12">
       <c r="A241" s="20" t="s">
-        <v>147</v>
+        <v>250</v>
       </c>
       <c r="E241" s="22">
         <f>IF(D241="?OLD","!!!","")</f>
@@ -10298,11 +10281,42 @@
       <c r="L241" s="27"/>
     </row>
     <row r="242" spans="1:12">
-      <c r="A242" s="20"/>
+      <c r="A242" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="E242" s="22">
+        <f>IF(D242="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F242" s="23" t="str">
+        <f>IF(OR(E242="",E242="!!!"),"",IF(NOT(ISNA(VLOOKUP(E242,E$1:E241,1,FALSE()))),"OLD",IF(AND(E242&lt;&gt;"",E242&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G242" s="24" t="str">
+        <f>IF(OR(E242="",E242="!!!"),"",IF(OR(J242=0,AND(J242=1,K242=1),AND(J242=1,I242="SBJ"),AND(J242=1,I242=0)),"?IN_FOCUS",IF(J242&lt;=2,"?ACTIVATED",IF(J242&lt;&gt;"","?FAMILIAR",IF(F242="NEW",IF(ISNA(VLOOKUP(E242,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H242" s="25" t="str">
+        <f>IF(J242&lt;&gt;1,"",IF(I242="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I242" s="26" t="str">
+        <f>IF(OR(E242="",E242="!!!",F242="NEW"),"",INDEX(B241:B$2,-1+SUMPRODUCT(MAX(ROW(E241:E$2)*(E242=E241:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J242" s="26" t="str">
+        <f>IF(OR(E242="",E242="!!!",F242="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E242)*(E242=E$2:E242)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E241)*(E2=E$1:E241))))))</f>
+        <v> </v>
+      </c>
+      <c r="K242" s="26" t="str">
+        <f>IF(OR(E242="",E242="!!!",F242="NEW"),"",INDEX(J$1:J241,SUMPRODUCT(MAX(ROW(E$1:E241)*(E242=E$1:E241)))))</f>
+        <v> </v>
+      </c>
+      <c r="L242" s="27"/>
     </row>
     <row r="243" spans="1:12">
       <c r="A243" s="20" t="s">
-        <v>248</v>
+        <v>150</v>
       </c>
       <c r="E243" s="22">
         <f>IF(D243="?OLD","!!!","")</f>
@@ -10335,13 +10349,11 @@
       <c r="L243" s="27"/>
     </row>
     <row r="244" spans="1:12">
-      <c r="A244" s="20" t="s">
-        <v>249</v>
-      </c>
+      <c r="A244" s="20"/>
     </row>
     <row r="245" spans="1:12">
       <c r="A245" s="20" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E245" s="22">
         <f>IF(D245="?OLD","!!!","")</f>
@@ -10375,50 +10387,12 @@
     </row>
     <row r="246" spans="1:12">
       <c r="A246" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="B246" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C246" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="D246" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="E246" s="22">
-        <f>IF(D246="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F246" s="23" t="str">
-        <f>IF(OR(E246="",E246="!!!"),"",IF(NOT(ISNA(VLOOKUP(E246,E$1:E245,1,FALSE()))),"OLD",IF(AND(E246&lt;&gt;"",E246&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G246" s="24" t="str">
-        <f>IF(OR(E246="",E246="!!!"),"",IF(OR(J246=0,AND(J246=1,K246=1),AND(J246=1,I246="SBJ"),AND(J246=1,I246=0)),"?IN_FOCUS",IF(J246&lt;=2,"?ACTIVATED",IF(J246&lt;&gt;"","?FAMILIAR",IF(F246="NEW",IF(ISNA(VLOOKUP(E246,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H246" s="25" t="str">
-        <f>IF(J246&lt;&gt;1,"",IF(I246="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I246" s="26" t="str">
-        <f>IF(OR(E246="",E246="!!!",F246="NEW"),"",INDEX(B245:B$2,-1+SUMPRODUCT(MAX(ROW(E245:E$2)*(E246=E245:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J246" s="26" t="str">
-        <f>IF(OR(E246="",E246="!!!",F246="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E246)*(E246=E$2:E246)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E245)*(E2=E$1:E245))))))</f>
-        <v> </v>
-      </c>
-      <c r="K246" s="26" t="str">
-        <f>IF(OR(E246="",E246="!!!",F246="NEW"),"",INDEX(J$1:J245,SUMPRODUCT(MAX(ROW(E$1:E245)*(E246=E$1:E245)))))</f>
-        <v> </v>
-      </c>
-      <c r="L246" s="27"/>
+        <v>253</v>
+      </c>
     </row>
     <row r="247" spans="1:12">
       <c r="A247" s="20" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E247" s="22">
         <f>IF(D247="?OLD","!!!","")</f>
@@ -10452,7 +10426,16 @@
     </row>
     <row r="248" spans="1:12">
       <c r="A248" s="20" t="s">
-        <v>93</v>
+        <v>255</v>
+      </c>
+      <c r="B248" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C248" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="D248" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E248" s="22">
         <f>IF(D248="?OLD","!!!","")</f>
@@ -10486,7 +10469,7 @@
     </row>
     <row r="249" spans="1:12">
       <c r="A249" s="20" t="s">
-        <v>161</v>
+        <v>256</v>
       </c>
       <c r="E249" s="22">
         <f>IF(D249="?OLD","!!!","")</f>
@@ -10520,13 +10503,7 @@
     </row>
     <row r="250" spans="1:12">
       <c r="A250" s="20" t="s">
-        <v>253</v>
-      </c>
-      <c r="B250" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C250" s="21" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="E250" s="22">
         <f>IF(D250="?OLD","!!!","")</f>
@@ -10560,7 +10537,7 @@
     </row>
     <row r="251" spans="1:12">
       <c r="A251" s="20" t="s">
-        <v>254</v>
+        <v>165</v>
       </c>
       <c r="E251" s="22">
         <f>IF(D251="?OLD","!!!","")</f>
@@ -10594,7 +10571,13 @@
     </row>
     <row r="252" spans="1:12">
       <c r="A252" s="20" t="s">
-        <v>125</v>
+        <v>257</v>
+      </c>
+      <c r="B252" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C252" s="21" t="s">
+        <v>127</v>
       </c>
       <c r="E252" s="22">
         <f>IF(D252="?OLD","!!!","")</f>
@@ -10628,13 +10611,7 @@
     </row>
     <row r="253" spans="1:12">
       <c r="A253" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="B253" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C253" s="21" t="s">
-        <v>123</v>
+        <v>258</v>
       </c>
       <c r="E253" s="22">
         <f>IF(D253="?OLD","!!!","")</f>
@@ -10668,7 +10645,7 @@
     </row>
     <row r="254" spans="1:12">
       <c r="A254" s="20" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="E254" s="22">
         <f>IF(D254="?OLD","!!!","")</f>
@@ -10702,7 +10679,13 @@
     </row>
     <row r="255" spans="1:12">
       <c r="A255" s="20" t="s">
-        <v>250</v>
+        <v>259</v>
+      </c>
+      <c r="B255" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C255" s="21" t="s">
+        <v>127</v>
       </c>
       <c r="E255" s="22">
         <f>IF(D255="?OLD","!!!","")</f>
@@ -10736,7 +10719,7 @@
     </row>
     <row r="256" spans="1:12">
       <c r="A256" s="20" t="s">
-        <v>193</v>
+        <v>112</v>
       </c>
       <c r="E256" s="22">
         <f>IF(D256="?OLD","!!!","")</f>
@@ -10770,16 +10753,7 @@
     </row>
     <row r="257" spans="1:12">
       <c r="A257" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="B257" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="C257" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D257" s="21" t="s">
-        <v>100</v>
+        <v>254</v>
       </c>
       <c r="E257" s="22">
         <f>IF(D257="?OLD","!!!","")</f>
@@ -10813,7 +10787,7 @@
     </row>
     <row r="258" spans="1:12">
       <c r="A258" s="20" t="s">
-        <v>127</v>
+        <v>197</v>
       </c>
       <c r="E258" s="22">
         <f>IF(D258="?OLD","!!!","")</f>
@@ -10847,16 +10821,16 @@
     </row>
     <row r="259" spans="1:12">
       <c r="A259" s="20" t="s">
-        <v>256</v>
+        <v>224</v>
       </c>
       <c r="B259" s="21" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="C259" s="21" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D259" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E259" s="22">
         <f>IF(D259="?OLD","!!!","")</f>
@@ -10890,7 +10864,7 @@
     </row>
     <row r="260" spans="1:12">
       <c r="A260" s="20" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="E260" s="22">
         <f>IF(D260="?OLD","!!!","")</f>
@@ -10924,7 +10898,16 @@
     </row>
     <row r="261" spans="1:12">
       <c r="A261" s="20" t="s">
-        <v>161</v>
+        <v>260</v>
+      </c>
+      <c r="B261" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C261" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D261" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E261" s="22">
         <f>IF(D261="?OLD","!!!","")</f>
@@ -10958,13 +10941,7 @@
     </row>
     <row r="262" spans="1:12">
       <c r="A262" s="20" t="s">
-        <v>257</v>
-      </c>
-      <c r="B262" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C262" s="21" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E262" s="22">
         <f>IF(D262="?OLD","!!!","")</f>
@@ -10998,7 +10975,7 @@
     </row>
     <row r="263" spans="1:12">
       <c r="A263" s="20" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="E263" s="22">
         <f>IF(D263="?OLD","!!!","")</f>
@@ -11032,16 +11009,13 @@
     </row>
     <row r="264" spans="1:12">
       <c r="A264" s="20" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B264" s="21" t="s">
-        <v>259</v>
+        <v>106</v>
       </c>
       <c r="C264" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D264" s="21" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="E264" s="22">
         <f>IF(D264="?OLD","!!!","")</f>
@@ -11075,7 +11049,7 @@
     </row>
     <row r="265" spans="1:12">
       <c r="A265" s="20" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="E265" s="22">
         <f>IF(D265="?OLD","!!!","")</f>
@@ -11109,13 +11083,16 @@
     </row>
     <row r="266" spans="1:12">
       <c r="A266" s="20" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B266" s="21" t="s">
-        <v>111</v>
+        <v>263</v>
       </c>
       <c r="C266" s="21" t="s">
-        <v>88</v>
+        <v>117</v>
+      </c>
+      <c r="D266" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E266" s="22">
         <f>IF(D266="?OLD","!!!","")</f>
@@ -11149,7 +11126,7 @@
     </row>
     <row r="267" spans="1:12">
       <c r="A267" s="20" t="s">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="E267" s="22">
         <f>IF(D267="?OLD","!!!","")</f>
@@ -11183,16 +11160,13 @@
     </row>
     <row r="268" spans="1:12">
       <c r="A268" s="20" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B268" s="21" t="s">
-        <v>259</v>
+        <v>106</v>
       </c>
       <c r="C268" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D268" s="21" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E268" s="22">
         <f>IF(D268="?OLD","!!!","")</f>
@@ -11226,7 +11200,7 @@
     </row>
     <row r="269" spans="1:12">
       <c r="A269" s="20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E269" s="22">
         <f>IF(D269="?OLD","!!!","")</f>
@@ -11260,7 +11234,16 @@
     </row>
     <row r="270" spans="1:12">
       <c r="A270" s="20" t="s">
-        <v>147</v>
+        <v>265</v>
+      </c>
+      <c r="B270" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="C270" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D270" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E270" s="22">
         <f>IF(D270="?OLD","!!!","")</f>
@@ -11293,84 +11276,84 @@
       <c r="L270" s="27"/>
     </row>
     <row r="271" spans="1:12">
-      <c r="A271" s="20"/>
+      <c r="A271" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="E271" s="22">
+        <f>IF(D271="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F271" s="23" t="str">
+        <f>IF(OR(E271="",E271="!!!"),"",IF(NOT(ISNA(VLOOKUP(E271,E$1:E270,1,FALSE()))),"OLD",IF(AND(E271&lt;&gt;"",E271&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G271" s="24" t="str">
+        <f>IF(OR(E271="",E271="!!!"),"",IF(OR(J271=0,AND(J271=1,K271=1),AND(J271=1,I271="SBJ"),AND(J271=1,I271=0)),"?IN_FOCUS",IF(J271&lt;=2,"?ACTIVATED",IF(J271&lt;&gt;"","?FAMILIAR",IF(F271="NEW",IF(ISNA(VLOOKUP(E271,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H271" s="25" t="str">
+        <f>IF(J271&lt;&gt;1,"",IF(I271="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I271" s="26" t="str">
+        <f>IF(OR(E271="",E271="!!!",F271="NEW"),"",INDEX(B270:B$2,-1+SUMPRODUCT(MAX(ROW(E270:E$2)*(E271=E270:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J271" s="26" t="str">
+        <f>IF(OR(E271="",E271="!!!",F271="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E271)*(E271=E$2:E271)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E270)*(E2=E$1:E270))))))</f>
+        <v> </v>
+      </c>
+      <c r="K271" s="26" t="str">
+        <f>IF(OR(E271="",E271="!!!",F271="NEW"),"",INDEX(J$1:J270,SUMPRODUCT(MAX(ROW(E$1:E270)*(E271=E$1:E270)))))</f>
+        <v> </v>
+      </c>
+      <c r="L271" s="27"/>
     </row>
     <row r="272" spans="1:12">
       <c r="A272" s="20" t="s">
-        <v>262</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E272" s="22">
+        <f>IF(D272="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F272" s="23" t="str">
+        <f>IF(OR(E272="",E272="!!!"),"",IF(NOT(ISNA(VLOOKUP(E272,E$1:E271,1,FALSE()))),"OLD",IF(AND(E272&lt;&gt;"",E272&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G272" s="24" t="str">
+        <f>IF(OR(E272="",E272="!!!"),"",IF(OR(J272=0,AND(J272=1,K272=1),AND(J272=1,I272="SBJ"),AND(J272=1,I272=0)),"?IN_FOCUS",IF(J272&lt;=2,"?ACTIVATED",IF(J272&lt;&gt;"","?FAMILIAR",IF(F272="NEW",IF(ISNA(VLOOKUP(E272,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H272" s="25" t="str">
+        <f>IF(J272&lt;&gt;1,"",IF(I272="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I272" s="26" t="str">
+        <f>IF(OR(E272="",E272="!!!",F272="NEW"),"",INDEX(B271:B$2,-1+SUMPRODUCT(MAX(ROW(E271:E$2)*(E272=E271:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J272" s="26" t="str">
+        <f>IF(OR(E272="",E272="!!!",F272="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E272)*(E272=E$2:E272)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E271)*(E2=E$1:E271))))))</f>
+        <v> </v>
+      </c>
+      <c r="K272" s="26" t="str">
+        <f>IF(OR(E272="",E272="!!!",F272="NEW"),"",INDEX(J$1:J271,SUMPRODUCT(MAX(ROW(E$1:E271)*(E272=E$1:E271)))))</f>
+        <v> </v>
+      </c>
+      <c r="L272" s="27"/>
     </row>
     <row r="273" spans="1:12">
-      <c r="A273" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="E273" s="22">
-        <f>IF(D273="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F273" s="23" t="str">
-        <f>IF(OR(E273="",E273="!!!"),"",IF(NOT(ISNA(VLOOKUP(E273,E$1:E272,1,FALSE()))),"OLD",IF(AND(E273&lt;&gt;"",E273&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G273" s="24" t="str">
-        <f>IF(OR(E273="",E273="!!!"),"",IF(OR(J273=0,AND(J273=1,K273=1),AND(J273=1,I273="SBJ"),AND(J273=1,I273=0)),"?IN_FOCUS",IF(J273&lt;=2,"?ACTIVATED",IF(J273&lt;&gt;"","?FAMILIAR",IF(F273="NEW",IF(ISNA(VLOOKUP(E273,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H273" s="25" t="str">
-        <f>IF(J273&lt;&gt;1,"",IF(I273="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I273" s="26" t="str">
-        <f>IF(OR(E273="",E273="!!!",F273="NEW"),"",INDEX(B272:B$2,-1+SUMPRODUCT(MAX(ROW(E272:E$2)*(E273=E272:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J273" s="26" t="str">
-        <f>IF(OR(E273="",E273="!!!",F273="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E273)*(E273=E$2:E273)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E272)*(E2=E$1:E272))))))</f>
-        <v> </v>
-      </c>
-      <c r="K273" s="26" t="str">
-        <f>IF(OR(E273="",E273="!!!",F273="NEW"),"",INDEX(J$1:J272,SUMPRODUCT(MAX(ROW(E$1:E272)*(E273=E$1:E272)))))</f>
-        <v> </v>
-      </c>
-      <c r="L273" s="27"/>
+      <c r="A273" s="20"/>
     </row>
     <row r="274" spans="1:12">
       <c r="A274" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="E274" s="22">
-        <f>IF(D274="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F274" s="23" t="str">
-        <f>IF(OR(E274="",E274="!!!"),"",IF(NOT(ISNA(VLOOKUP(E274,E$1:E273,1,FALSE()))),"OLD",IF(AND(E274&lt;&gt;"",E274&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G274" s="24" t="str">
-        <f>IF(OR(E274="",E274="!!!"),"",IF(OR(J274=0,AND(J274=1,K274=1),AND(J274=1,I274="SBJ"),AND(J274=1,I274=0)),"?IN_FOCUS",IF(J274&lt;=2,"?ACTIVATED",IF(J274&lt;&gt;"","?FAMILIAR",IF(F274="NEW",IF(ISNA(VLOOKUP(E274,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H274" s="25" t="str">
-        <f>IF(J274&lt;&gt;1,"",IF(I274="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I274" s="26" t="str">
-        <f>IF(OR(E274="",E274="!!!",F274="NEW"),"",INDEX(B273:B$2,-1+SUMPRODUCT(MAX(ROW(E273:E$2)*(E274=E273:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J274" s="26" t="str">
-        <f>IF(OR(E274="",E274="!!!",F274="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E274)*(E274=E$2:E274)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E273)*(E2=E$1:E273))))))</f>
-        <v> </v>
-      </c>
-      <c r="K274" s="26" t="str">
-        <f>IF(OR(E274="",E274="!!!",F274="NEW"),"",INDEX(J$1:J273,SUMPRODUCT(MAX(ROW(E$1:E273)*(E274=E$1:E273)))))</f>
-        <v> </v>
-      </c>
-      <c r="L274" s="27"/>
+        <v>266</v>
+      </c>
     </row>
     <row r="275" spans="1:12">
       <c r="A275" s="20" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="E275" s="22">
         <f>IF(D275="?OLD","!!!","")</f>
@@ -11404,7 +11387,7 @@
     </row>
     <row r="276" spans="1:12">
       <c r="A276" s="20" t="s">
-        <v>106</v>
+        <v>267</v>
       </c>
       <c r="E276" s="22">
         <f>IF(D276="?OLD","!!!","")</f>
@@ -11438,7 +11421,7 @@
     </row>
     <row r="277" spans="1:12">
       <c r="A277" s="20" t="s">
-        <v>194</v>
+        <v>268</v>
       </c>
       <c r="E277" s="22">
         <f>IF(D277="?OLD","!!!","")</f>
@@ -11472,7 +11455,7 @@
     </row>
     <row r="278" spans="1:12">
       <c r="A278" s="20" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="E278" s="22">
         <f>IF(D278="?OLD","!!!","")</f>
@@ -11506,16 +11489,7 @@
     </row>
     <row r="279" spans="1:12">
       <c r="A279" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="B279" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="C279" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D279" s="21" t="s">
-        <v>100</v>
+        <v>198</v>
       </c>
       <c r="E279" s="22">
         <f>IF(D279="?OLD","!!!","")</f>
@@ -11549,13 +11523,7 @@
     </row>
     <row r="280" spans="1:12">
       <c r="A280" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="B280" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C280" s="21" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E280" s="22">
         <f>IF(D280="?OLD","!!!","")</f>
@@ -11589,13 +11557,16 @@
     </row>
     <row r="281" spans="1:12">
       <c r="A281" s="20" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B281" s="21" t="s">
-        <v>214</v>
+        <v>128</v>
       </c>
       <c r="C281" s="21" t="s">
-        <v>88</v>
+        <v>103</v>
+      </c>
+      <c r="D281" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E281" s="22">
         <f>IF(D281="?OLD","!!!","")</f>
@@ -11629,7 +11600,13 @@
     </row>
     <row r="282" spans="1:12">
       <c r="A282" s="20" t="s">
-        <v>268</v>
+        <v>270</v>
+      </c>
+      <c r="B282" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C282" s="21" t="s">
+        <v>130</v>
       </c>
       <c r="E282" s="22">
         <f>IF(D282="?OLD","!!!","")</f>
@@ -11663,7 +11640,13 @@
     </row>
     <row r="283" spans="1:12">
       <c r="A283" s="20" t="s">
-        <v>269</v>
+        <v>271</v>
+      </c>
+      <c r="B283" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="C283" s="21" t="s">
+        <v>91</v>
       </c>
       <c r="E283" s="22">
         <f>IF(D283="?OLD","!!!","")</f>
@@ -11697,7 +11680,7 @@
     </row>
     <row r="284" spans="1:12">
       <c r="A284" s="20" t="s">
-        <v>106</v>
+        <v>272</v>
       </c>
       <c r="E284" s="22">
         <f>IF(D284="?OLD","!!!","")</f>
@@ -11731,7 +11714,7 @@
     </row>
     <row r="285" spans="1:12">
       <c r="A285" s="20" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E285" s="22">
         <f>IF(D285="?OLD","!!!","")</f>
@@ -11765,7 +11748,7 @@
     </row>
     <row r="286" spans="1:12">
       <c r="A286" s="20" t="s">
-        <v>199</v>
+        <v>112</v>
       </c>
       <c r="E286" s="22">
         <f>IF(D286="?OLD","!!!","")</f>
@@ -11799,7 +11782,7 @@
     </row>
     <row r="287" spans="1:12">
       <c r="A287" s="20" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E287" s="22">
         <f>IF(D287="?OLD","!!!","")</f>
@@ -11833,13 +11816,7 @@
     </row>
     <row r="288" spans="1:12">
       <c r="A288" s="20" t="s">
-        <v>272</v>
-      </c>
-      <c r="B288" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C288" s="21" t="s">
-        <v>123</v>
+        <v>203</v>
       </c>
       <c r="E288" s="22">
         <f>IF(D288="?OLD","!!!","")</f>
@@ -11873,7 +11850,7 @@
     </row>
     <row r="289" spans="1:12">
       <c r="A289" s="20" t="s">
-        <v>173</v>
+        <v>275</v>
       </c>
       <c r="E289" s="22">
         <f>IF(D289="?OLD","!!!","")</f>
@@ -11907,7 +11884,13 @@
     </row>
     <row r="290" spans="1:12">
       <c r="A290" s="20" t="s">
-        <v>273</v>
+        <v>276</v>
+      </c>
+      <c r="B290" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C290" s="21" t="s">
+        <v>127</v>
       </c>
       <c r="E290" s="22">
         <f>IF(D290="?OLD","!!!","")</f>
@@ -11941,7 +11924,7 @@
     </row>
     <row r="291" spans="1:12">
       <c r="A291" s="20" t="s">
-        <v>274</v>
+        <v>177</v>
       </c>
       <c r="E291" s="22">
         <f>IF(D291="?OLD","!!!","")</f>
@@ -11975,16 +11958,7 @@
     </row>
     <row r="292" spans="1:12">
       <c r="A292" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="B292" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C292" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D292" s="21" t="s">
-        <v>100</v>
+        <v>277</v>
       </c>
       <c r="E292" s="22">
         <f>IF(D292="?OLD","!!!","")</f>
@@ -12018,7 +11992,7 @@
     </row>
     <row r="293" spans="1:12">
       <c r="A293" s="20" t="s">
-        <v>106</v>
+        <v>278</v>
       </c>
       <c r="E293" s="22">
         <f>IF(D293="?OLD","!!!","")</f>
@@ -12052,7 +12026,16 @@
     </row>
     <row r="294" spans="1:12">
       <c r="A294" s="20" t="s">
-        <v>125</v>
+        <v>279</v>
+      </c>
+      <c r="B294" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C294" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D294" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E294" s="22">
         <f>IF(D294="?OLD","!!!","")</f>
@@ -12086,7 +12069,7 @@
     </row>
     <row r="295" spans="1:12">
       <c r="A295" s="20" t="s">
-        <v>276</v>
+        <v>112</v>
       </c>
       <c r="E295" s="22">
         <f>IF(D295="?OLD","!!!","")</f>
@@ -12120,13 +12103,7 @@
     </row>
     <row r="296" spans="1:12">
       <c r="A296" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="B296" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C296" s="21" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E296" s="22">
         <f>IF(D296="?OLD","!!!","")</f>
@@ -12160,7 +12137,7 @@
     </row>
     <row r="297" spans="1:12">
       <c r="A297" s="20" t="s">
-        <v>173</v>
+        <v>280</v>
       </c>
       <c r="E297" s="22">
         <f>IF(D297="?OLD","!!!","")</f>
@@ -12194,7 +12171,13 @@
     </row>
     <row r="298" spans="1:12">
       <c r="A298" s="20" t="s">
-        <v>273</v>
+        <v>281</v>
+      </c>
+      <c r="B298" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C298" s="21" t="s">
+        <v>127</v>
       </c>
       <c r="E298" s="22">
         <f>IF(D298="?OLD","!!!","")</f>
@@ -12228,7 +12211,7 @@
     </row>
     <row r="299" spans="1:12">
       <c r="A299" s="20" t="s">
-        <v>274</v>
+        <v>177</v>
       </c>
       <c r="E299" s="22">
         <f>IF(D299="?OLD","!!!","")</f>
@@ -12262,16 +12245,7 @@
     </row>
     <row r="300" spans="1:12">
       <c r="A300" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="B300" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="C300" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D300" s="21" t="s">
-        <v>100</v>
+        <v>277</v>
       </c>
       <c r="E300" s="22">
         <f>IF(D300="?OLD","!!!","")</f>
@@ -12305,7 +12279,7 @@
     </row>
     <row r="301" spans="1:12">
       <c r="A301" s="20" t="s">
-        <v>118</v>
+        <v>278</v>
       </c>
       <c r="E301" s="22">
         <f>IF(D301="?OLD","!!!","")</f>
@@ -12339,7 +12313,16 @@
     </row>
     <row r="302" spans="1:12">
       <c r="A302" s="20" t="s">
-        <v>125</v>
+        <v>279</v>
+      </c>
+      <c r="B302" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="C302" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D302" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E302" s="22">
         <f>IF(D302="?OLD","!!!","")</f>
@@ -12373,7 +12356,7 @@
     </row>
     <row r="303" spans="1:12">
       <c r="A303" s="20" t="s">
-        <v>278</v>
+        <v>122</v>
       </c>
       <c r="E303" s="22">
         <f>IF(D303="?OLD","!!!","")</f>
@@ -12407,13 +12390,7 @@
     </row>
     <row r="304" spans="1:12">
       <c r="A304" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="B304" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="C304" s="21" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E304" s="22">
         <f>IF(D304="?OLD","!!!","")</f>
@@ -12447,7 +12424,7 @@
     </row>
     <row r="305" spans="1:12">
       <c r="A305" s="20" t="s">
-        <v>207</v>
+        <v>282</v>
       </c>
       <c r="E305" s="22">
         <f>IF(D305="?OLD","!!!","")</f>
@@ -12481,13 +12458,13 @@
     </row>
     <row r="306" spans="1:12">
       <c r="A306" s="20" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B306" s="21" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C306" s="21" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="E306" s="22">
         <f>IF(D306="?OLD","!!!","")</f>
@@ -12521,7 +12498,7 @@
     </row>
     <row r="307" spans="1:12">
       <c r="A307" s="20" t="s">
-        <v>147</v>
+        <v>211</v>
       </c>
       <c r="E307" s="22">
         <f>IF(D307="?OLD","!!!","")</f>
@@ -12554,93 +12531,90 @@
       <c r="L307" s="27"/>
     </row>
     <row r="308" spans="1:12">
-      <c r="A308" s="20"/>
+      <c r="A308" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="B308" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="C308" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="E308" s="22">
+        <f>IF(D308="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F308" s="23" t="str">
+        <f>IF(OR(E308="",E308="!!!"),"",IF(NOT(ISNA(VLOOKUP(E308,E$1:E307,1,FALSE()))),"OLD",IF(AND(E308&lt;&gt;"",E308&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G308" s="24" t="str">
+        <f>IF(OR(E308="",E308="!!!"),"",IF(OR(J308=0,AND(J308=1,K308=1),AND(J308=1,I308="SBJ"),AND(J308=1,I308=0)),"?IN_FOCUS",IF(J308&lt;=2,"?ACTIVATED",IF(J308&lt;&gt;"","?FAMILIAR",IF(F308="NEW",IF(ISNA(VLOOKUP(E308,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H308" s="25" t="str">
+        <f>IF(J308&lt;&gt;1,"",IF(I308="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I308" s="26" t="str">
+        <f>IF(OR(E308="",E308="!!!",F308="NEW"),"",INDEX(B307:B$2,-1+SUMPRODUCT(MAX(ROW(E307:E$2)*(E308=E307:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J308" s="26" t="str">
+        <f>IF(OR(E308="",E308="!!!",F308="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E308)*(E308=E$2:E308)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E307)*(E2=E$1:E307))))))</f>
+        <v> </v>
+      </c>
+      <c r="K308" s="26" t="str">
+        <f>IF(OR(E308="",E308="!!!",F308="NEW"),"",INDEX(J$1:J307,SUMPRODUCT(MAX(ROW(E$1:E307)*(E308=E$1:E307)))))</f>
+        <v> </v>
+      </c>
+      <c r="L308" s="27"/>
     </row>
     <row r="309" spans="1:12">
       <c r="A309" s="20" t="s">
-        <v>283</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E309" s="22">
+        <f>IF(D309="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F309" s="23" t="str">
+        <f>IF(OR(E309="",E309="!!!"),"",IF(NOT(ISNA(VLOOKUP(E309,E$1:E308,1,FALSE()))),"OLD",IF(AND(E309&lt;&gt;"",E309&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G309" s="24" t="str">
+        <f>IF(OR(E309="",E309="!!!"),"",IF(OR(J309=0,AND(J309=1,K309=1),AND(J309=1,I309="SBJ"),AND(J309=1,I309=0)),"?IN_FOCUS",IF(J309&lt;=2,"?ACTIVATED",IF(J309&lt;&gt;"","?FAMILIAR",IF(F309="NEW",IF(ISNA(VLOOKUP(E309,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H309" s="25" t="str">
+        <f>IF(J309&lt;&gt;1,"",IF(I309="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I309" s="26" t="str">
+        <f>IF(OR(E309="",E309="!!!",F309="NEW"),"",INDEX(B308:B$2,-1+SUMPRODUCT(MAX(ROW(E308:E$2)*(E309=E308:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J309" s="26" t="str">
+        <f>IF(OR(E309="",E309="!!!",F309="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E309)*(E309=E$2:E309)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E308)*(E2=E$1:E308))))))</f>
+        <v> </v>
+      </c>
+      <c r="K309" s="26" t="str">
+        <f>IF(OR(E309="",E309="!!!",F309="NEW"),"",INDEX(J$1:J308,SUMPRODUCT(MAX(ROW(E$1:E308)*(E309=E$1:E308)))))</f>
+        <v> </v>
+      </c>
+      <c r="L309" s="27"/>
     </row>
     <row r="310" spans="1:12">
-      <c r="A310" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="E310" s="22">
-        <f>IF(D310="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F310" s="23" t="str">
-        <f>IF(OR(E310="",E310="!!!"),"",IF(NOT(ISNA(VLOOKUP(E310,E$1:E309,1,FALSE()))),"OLD",IF(AND(E310&lt;&gt;"",E310&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G310" s="24" t="str">
-        <f>IF(OR(E310="",E310="!!!"),"",IF(OR(J310=0,AND(J310=1,K310=1),AND(J310=1,I310="SBJ"),AND(J310=1,I310=0)),"?IN_FOCUS",IF(J310&lt;=2,"?ACTIVATED",IF(J310&lt;&gt;"","?FAMILIAR",IF(F310="NEW",IF(ISNA(VLOOKUP(E310,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H310" s="25" t="str">
-        <f>IF(J310&lt;&gt;1,"",IF(I310="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I310" s="26" t="str">
-        <f>IF(OR(E310="",E310="!!!",F310="NEW"),"",INDEX(B309:B$2,-1+SUMPRODUCT(MAX(ROW(E309:E$2)*(E310=E309:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J310" s="26" t="str">
-        <f>IF(OR(E310="",E310="!!!",F310="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E310)*(E310=E$2:E310)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E309)*(E2=E$1:E309))))))</f>
-        <v> </v>
-      </c>
-      <c r="K310" s="26" t="str">
-        <f>IF(OR(E310="",E310="!!!",F310="NEW"),"",INDEX(J$1:J309,SUMPRODUCT(MAX(ROW(E$1:E309)*(E310=E$1:E309)))))</f>
-        <v> </v>
-      </c>
-      <c r="L310" s="27"/>
+      <c r="A310" s="20"/>
     </row>
     <row r="311" spans="1:12">
       <c r="A311" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="B311" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C311" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D311" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="E311" s="22">
-        <f>IF(D311="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F311" s="23" t="str">
-        <f>IF(OR(E311="",E311="!!!"),"",IF(NOT(ISNA(VLOOKUP(E311,E$1:E310,1,FALSE()))),"OLD",IF(AND(E311&lt;&gt;"",E311&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G311" s="24" t="str">
-        <f>IF(OR(E311="",E311="!!!"),"",IF(OR(J311=0,AND(J311=1,K311=1),AND(J311=1,I311="SBJ"),AND(J311=1,I311=0)),"?IN_FOCUS",IF(J311&lt;=2,"?ACTIVATED",IF(J311&lt;&gt;"","?FAMILIAR",IF(F311="NEW",IF(ISNA(VLOOKUP(E311,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H311" s="25" t="str">
-        <f>IF(J311&lt;&gt;1,"",IF(I311="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I311" s="26" t="str">
-        <f>IF(OR(E311="",E311="!!!",F311="NEW"),"",INDEX(B310:B$2,-1+SUMPRODUCT(MAX(ROW(E310:E$2)*(E311=E310:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J311" s="26" t="str">
-        <f>IF(OR(E311="",E311="!!!",F311="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E311)*(E311=E$2:E311)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E310)*(E2=E$1:E310))))))</f>
-        <v> </v>
-      </c>
-      <c r="K311" s="26" t="str">
-        <f>IF(OR(E311="",E311="!!!",F311="NEW"),"",INDEX(J$1:J310,SUMPRODUCT(MAX(ROW(E$1:E310)*(E311=E$1:E310)))))</f>
-        <v> </v>
-      </c>
-      <c r="L311" s="27"/>
+        <v>287</v>
+      </c>
     </row>
     <row r="312" spans="1:12">
       <c r="A312" s="20" t="s">
-        <v>284</v>
+        <v>196</v>
       </c>
       <c r="E312" s="22">
         <f>IF(D312="?OLD","!!!","")</f>
@@ -12674,10 +12648,16 @@
     </row>
     <row r="313" spans="1:12">
       <c r="A313" s="20" t="s">
-        <v>141</v>
+        <v>227</v>
       </c>
       <c r="B313" s="21" t="s">
-        <v>117</v>
+        <v>90</v>
+      </c>
+      <c r="C313" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D313" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E313" s="22">
         <f>IF(D313="?OLD","!!!","")</f>
@@ -12711,7 +12691,7 @@
     </row>
     <row r="314" spans="1:12">
       <c r="A314" s="20" t="s">
-        <v>106</v>
+        <v>288</v>
       </c>
       <c r="E314" s="22">
         <f>IF(D314="?OLD","!!!","")</f>
@@ -12745,7 +12725,10 @@
     </row>
     <row r="315" spans="1:12">
       <c r="A315" s="20" t="s">
-        <v>107</v>
+        <v>144</v>
+      </c>
+      <c r="B315" s="21" t="s">
+        <v>94</v>
       </c>
       <c r="E315" s="22">
         <f>IF(D315="?OLD","!!!","")</f>
@@ -12779,16 +12762,7 @@
     </row>
     <row r="316" spans="1:12">
       <c r="A316" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="B316" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="C316" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D316" s="21" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E316" s="22">
         <f>IF(D316="?OLD","!!!","")</f>
@@ -12822,7 +12796,7 @@
     </row>
     <row r="317" spans="1:12">
       <c r="A317" s="20" t="s">
-        <v>286</v>
+        <v>113</v>
       </c>
       <c r="E317" s="22">
         <f>IF(D317="?OLD","!!!","")</f>
@@ -12856,7 +12830,16 @@
     </row>
     <row r="318" spans="1:12">
       <c r="A318" s="20" t="s">
-        <v>106</v>
+        <v>289</v>
+      </c>
+      <c r="B318" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C318" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D318" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E318" s="22">
         <f>IF(D318="?OLD","!!!","")</f>
@@ -12890,16 +12873,7 @@
     </row>
     <row r="319" spans="1:12">
       <c r="A319" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="B319" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C319" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="D319" s="21" t="s">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="E319" s="22">
         <f>IF(D319="?OLD","!!!","")</f>
@@ -12933,16 +12907,7 @@
     </row>
     <row r="320" spans="1:12">
       <c r="A320" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="B320" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="C320" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="D320" s="21" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E320" s="22">
         <f>IF(D320="?OLD","!!!","")</f>
@@ -12976,7 +12941,16 @@
     </row>
     <row r="321" spans="1:12">
       <c r="A321" s="20" t="s">
-        <v>189</v>
+        <v>113</v>
+      </c>
+      <c r="B321" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C321" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D321" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E321" s="22">
         <f>IF(D321="?OLD","!!!","")</f>
@@ -13010,7 +12984,16 @@
     </row>
     <row r="322" spans="1:12">
       <c r="A322" s="20" t="s">
-        <v>127</v>
+        <v>142</v>
+      </c>
+      <c r="B322" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C322" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D322" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E322" s="22">
         <f>IF(D322="?OLD","!!!","")</f>
@@ -13044,16 +13027,7 @@
     </row>
     <row r="323" spans="1:12">
       <c r="A323" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="B323" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C323" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D323" s="21" t="s">
-        <v>100</v>
+        <v>193</v>
       </c>
       <c r="E323" s="22">
         <f>IF(D323="?OLD","!!!","")</f>
@@ -13087,7 +13061,7 @@
     </row>
     <row r="324" spans="1:12">
       <c r="A324" s="20" t="s">
-        <v>288</v>
+        <v>131</v>
       </c>
       <c r="E324" s="22">
         <f>IF(D324="?OLD","!!!","")</f>
@@ -13121,7 +13095,16 @@
     </row>
     <row r="325" spans="1:12">
       <c r="A325" s="20" t="s">
-        <v>289</v>
+        <v>291</v>
+      </c>
+      <c r="B325" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C325" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D325" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E325" s="22">
         <f>IF(D325="?OLD","!!!","")</f>
@@ -13155,7 +13138,7 @@
     </row>
     <row r="326" spans="1:12">
       <c r="A326" s="20" t="s">
-        <v>106</v>
+        <v>292</v>
       </c>
       <c r="E326" s="22">
         <f>IF(D326="?OLD","!!!","")</f>
@@ -13189,7 +13172,7 @@
     </row>
     <row r="327" spans="1:12">
       <c r="A327" s="20" t="s">
-        <v>194</v>
+        <v>293</v>
       </c>
       <c r="E327" s="22">
         <f>IF(D327="?OLD","!!!","")</f>
@@ -13223,7 +13206,7 @@
     </row>
     <row r="328" spans="1:12">
       <c r="A328" s="20" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E328" s="22">
         <f>IF(D328="?OLD","!!!","")</f>
@@ -13257,16 +13240,7 @@
     </row>
     <row r="329" spans="1:12">
       <c r="A329" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="B329" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="C329" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D329" s="21" t="s">
-        <v>100</v>
+        <v>198</v>
       </c>
       <c r="E329" s="22">
         <f>IF(D329="?OLD","!!!","")</f>
@@ -13300,7 +13274,7 @@
     </row>
     <row r="330" spans="1:12">
       <c r="A330" s="20" t="s">
-        <v>290</v>
+        <v>113</v>
       </c>
       <c r="E330" s="22">
         <f>IF(D330="?OLD","!!!","")</f>
@@ -13334,7 +13308,16 @@
     </row>
     <row r="331" spans="1:12">
       <c r="A331" s="20" t="s">
-        <v>136</v>
+        <v>133</v>
+      </c>
+      <c r="B331" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C331" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D331" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E331" s="22">
         <f>IF(D331="?OLD","!!!","")</f>
@@ -13368,7 +13351,7 @@
     </row>
     <row r="332" spans="1:12">
       <c r="A332" s="20" t="s">
-        <v>118</v>
+        <v>294</v>
       </c>
       <c r="E332" s="22">
         <f>IF(D332="?OLD","!!!","")</f>
@@ -13402,7 +13385,7 @@
     </row>
     <row r="333" spans="1:12">
       <c r="A333" s="20" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E333" s="22">
         <f>IF(D333="?OLD","!!!","")</f>
@@ -13436,7 +13419,7 @@
     </row>
     <row r="334" spans="1:12">
       <c r="A334" s="20" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="E334" s="22">
         <f>IF(D334="?OLD","!!!","")</f>
@@ -13470,7 +13453,7 @@
     </row>
     <row r="335" spans="1:12">
       <c r="A335" s="20" t="s">
-        <v>291</v>
+        <v>137</v>
       </c>
       <c r="E335" s="22">
         <f>IF(D335="?OLD","!!!","")</f>
@@ -13504,15 +13487,6 @@
     </row>
     <row r="336" spans="1:12">
       <c r="A336" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="B336" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C336" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D336" s="21" t="s">
         <v>100</v>
       </c>
       <c r="E336" s="22">
@@ -13547,7 +13521,7 @@
     </row>
     <row r="337" spans="1:12">
       <c r="A337" s="20" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E337" s="22">
         <f>IF(D337="?OLD","!!!","")</f>
@@ -13581,7 +13555,16 @@
     </row>
     <row r="338" spans="1:12">
       <c r="A338" s="20" t="s">
-        <v>114</v>
+        <v>296</v>
+      </c>
+      <c r="B338" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C338" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D338" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E338" s="22">
         <f>IF(D338="?OLD","!!!","")</f>
@@ -13615,7 +13598,7 @@
     </row>
     <row r="339" spans="1:12">
       <c r="A339" s="20" t="s">
-        <v>147</v>
+        <v>297</v>
       </c>
       <c r="E339" s="22">
         <f>IF(D339="?OLD","!!!","")</f>
@@ -13648,93 +13631,93 @@
       <c r="L339" s="27"/>
     </row>
     <row r="340" spans="1:12">
-      <c r="A340" s="20"/>
+      <c r="A340" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="E340" s="22">
+        <f>IF(D340="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F340" s="23" t="str">
+        <f>IF(OR(E340="",E340="!!!"),"",IF(NOT(ISNA(VLOOKUP(E340,E$1:E339,1,FALSE()))),"OLD",IF(AND(E340&lt;&gt;"",E340&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G340" s="24" t="str">
+        <f>IF(OR(E340="",E340="!!!"),"",IF(OR(J340=0,AND(J340=1,K340=1),AND(J340=1,I340="SBJ"),AND(J340=1,I340=0)),"?IN_FOCUS",IF(J340&lt;=2,"?ACTIVATED",IF(J340&lt;&gt;"","?FAMILIAR",IF(F340="NEW",IF(ISNA(VLOOKUP(E340,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H340" s="25" t="str">
+        <f>IF(J340&lt;&gt;1,"",IF(I340="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I340" s="26" t="str">
+        <f>IF(OR(E340="",E340="!!!",F340="NEW"),"",INDEX(B339:B$2,-1+SUMPRODUCT(MAX(ROW(E339:E$2)*(E340=E339:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J340" s="26" t="str">
+        <f>IF(OR(E340="",E340="!!!",F340="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E340)*(E340=E$2:E340)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E339)*(E2=E$1:E339))))))</f>
+        <v> </v>
+      </c>
+      <c r="K340" s="26" t="str">
+        <f>IF(OR(E340="",E340="!!!",F340="NEW"),"",INDEX(J$1:J339,SUMPRODUCT(MAX(ROW(E$1:E339)*(E340=E$1:E339)))))</f>
+        <v> </v>
+      </c>
+      <c r="L340" s="27"/>
     </row>
     <row r="341" spans="1:12">
       <c r="A341" s="20" t="s">
-        <v>294</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E341" s="22">
+        <f>IF(D341="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F341" s="23" t="str">
+        <f>IF(OR(E341="",E341="!!!"),"",IF(NOT(ISNA(VLOOKUP(E341,E$1:E340,1,FALSE()))),"OLD",IF(AND(E341&lt;&gt;"",E341&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G341" s="24" t="str">
+        <f>IF(OR(E341="",E341="!!!"),"",IF(OR(J341=0,AND(J341=1,K341=1),AND(J341=1,I341="SBJ"),AND(J341=1,I341=0)),"?IN_FOCUS",IF(J341&lt;=2,"?ACTIVATED",IF(J341&lt;&gt;"","?FAMILIAR",IF(F341="NEW",IF(ISNA(VLOOKUP(E341,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H341" s="25" t="str">
+        <f>IF(J341&lt;&gt;1,"",IF(I341="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I341" s="26" t="str">
+        <f>IF(OR(E341="",E341="!!!",F341="NEW"),"",INDEX(B340:B$2,-1+SUMPRODUCT(MAX(ROW(E340:E$2)*(E341=E340:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J341" s="26" t="str">
+        <f>IF(OR(E341="",E341="!!!",F341="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E341)*(E341=E$2:E341)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E340)*(E2=E$1:E340))))))</f>
+        <v> </v>
+      </c>
+      <c r="K341" s="26" t="str">
+        <f>IF(OR(E341="",E341="!!!",F341="NEW"),"",INDEX(J$1:J340,SUMPRODUCT(MAX(ROW(E$1:E340)*(E341=E$1:E340)))))</f>
+        <v> </v>
+      </c>
+      <c r="L341" s="27"/>
     </row>
     <row r="342" spans="1:12">
-      <c r="A342" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="B342" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C342" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D342" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="E342" s="22">
-        <f>IF(D342="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F342" s="23" t="str">
-        <f>IF(OR(E342="",E342="!!!"),"",IF(NOT(ISNA(VLOOKUP(E342,E$1:E341,1,FALSE()))),"OLD",IF(AND(E342&lt;&gt;"",E342&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G342" s="24" t="str">
-        <f>IF(OR(E342="",E342="!!!"),"",IF(OR(J342=0,AND(J342=1,K342=1),AND(J342=1,I342="SBJ"),AND(J342=1,I342=0)),"?IN_FOCUS",IF(J342&lt;=2,"?ACTIVATED",IF(J342&lt;&gt;"","?FAMILIAR",IF(F342="NEW",IF(ISNA(VLOOKUP(E342,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H342" s="25" t="str">
-        <f>IF(J342&lt;&gt;1,"",IF(I342="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I342" s="26" t="str">
-        <f>IF(OR(E342="",E342="!!!",F342="NEW"),"",INDEX(B341:B$2,-1+SUMPRODUCT(MAX(ROW(E341:E$2)*(E342=E341:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J342" s="26" t="str">
-        <f>IF(OR(E342="",E342="!!!",F342="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E342)*(E342=E$2:E342)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E341)*(E2=E$1:E341))))))</f>
-        <v> </v>
-      </c>
-      <c r="K342" s="26" t="str">
-        <f>IF(OR(E342="",E342="!!!",F342="NEW"),"",INDEX(J$1:J341,SUMPRODUCT(MAX(ROW(E$1:E341)*(E342=E$1:E341)))))</f>
-        <v> </v>
-      </c>
-      <c r="L342" s="27"/>
+      <c r="A342" s="20"/>
     </row>
     <row r="343" spans="1:12">
       <c r="A343" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E343" s="22">
-        <f>IF(D343="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F343" s="23" t="str">
-        <f>IF(OR(E343="",E343="!!!"),"",IF(NOT(ISNA(VLOOKUP(E343,E$1:E342,1,FALSE()))),"OLD",IF(AND(E343&lt;&gt;"",E343&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G343" s="24" t="str">
-        <f>IF(OR(E343="",E343="!!!"),"",IF(OR(J343=0,AND(J343=1,K343=1),AND(J343=1,I343="SBJ"),AND(J343=1,I343=0)),"?IN_FOCUS",IF(J343&lt;=2,"?ACTIVATED",IF(J343&lt;&gt;"","?FAMILIAR",IF(F343="NEW",IF(ISNA(VLOOKUP(E343,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H343" s="25" t="str">
-        <f>IF(J343&lt;&gt;1,"",IF(I343="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I343" s="26" t="str">
-        <f>IF(OR(E343="",E343="!!!",F343="NEW"),"",INDEX(B342:B$2,-1+SUMPRODUCT(MAX(ROW(E342:E$2)*(E343=E342:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J343" s="26" t="str">
-        <f>IF(OR(E343="",E343="!!!",F343="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E343)*(E343=E$2:E343)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E342)*(E2=E$1:E342))))))</f>
-        <v> </v>
-      </c>
-      <c r="K343" s="26" t="str">
-        <f>IF(OR(E343="",E343="!!!",F343="NEW"),"",INDEX(J$1:J342,SUMPRODUCT(MAX(ROW(E$1:E342)*(E343=E$1:E342)))))</f>
-        <v> </v>
-      </c>
-      <c r="L343" s="27"/>
+        <v>298</v>
+      </c>
     </row>
     <row r="344" spans="1:12">
       <c r="A344" s="20" t="s">
-        <v>295</v>
+        <v>157</v>
+      </c>
+      <c r="B344" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C344" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D344" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E344" s="22">
         <f>IF(D344="?OLD","!!!","")</f>
@@ -13768,7 +13751,7 @@
     </row>
     <row r="345" spans="1:12">
       <c r="A345" s="20" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E345" s="22">
         <f>IF(D345="?OLD","!!!","")</f>
@@ -13802,7 +13785,7 @@
     </row>
     <row r="346" spans="1:12">
       <c r="A346" s="20" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E346" s="22">
         <f>IF(D346="?OLD","!!!","")</f>
@@ -13836,7 +13819,7 @@
     </row>
     <row r="347" spans="1:12">
       <c r="A347" s="20" t="s">
-        <v>297</v>
+        <v>112</v>
       </c>
       <c r="E347" s="22">
         <f>IF(D347="?OLD","!!!","")</f>
@@ -13870,7 +13853,7 @@
     </row>
     <row r="348" spans="1:12">
       <c r="A348" s="20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E348" s="22">
         <f>IF(D348="?OLD","!!!","")</f>
@@ -13904,13 +13887,7 @@
     </row>
     <row r="349" spans="1:12">
       <c r="A349" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="B349" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C349" s="21" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E349" s="22">
         <f>IF(D349="?OLD","!!!","")</f>
@@ -13944,7 +13921,7 @@
     </row>
     <row r="350" spans="1:12">
       <c r="A350" s="20" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E350" s="22">
         <f>IF(D350="?OLD","!!!","")</f>
@@ -13978,7 +13955,13 @@
     </row>
     <row r="351" spans="1:12">
       <c r="A351" s="20" t="s">
-        <v>118</v>
+        <v>303</v>
+      </c>
+      <c r="B351" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C351" s="21" t="s">
+        <v>304</v>
       </c>
       <c r="E351" s="22">
         <f>IF(D351="?OLD","!!!","")</f>
@@ -14012,7 +13995,7 @@
     </row>
     <row r="352" spans="1:12">
       <c r="A352" s="20" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E352" s="22">
         <f>IF(D352="?OLD","!!!","")</f>
@@ -14046,7 +14029,7 @@
     </row>
     <row r="353" spans="1:12">
       <c r="A353" s="20" t="s">
-        <v>303</v>
+        <v>122</v>
       </c>
       <c r="E353" s="22">
         <f>IF(D353="?OLD","!!!","")</f>
@@ -14080,7 +14063,7 @@
     </row>
     <row r="354" spans="1:12">
       <c r="A354" s="20" t="s">
-        <v>147</v>
+        <v>306</v>
       </c>
       <c r="E354" s="22">
         <f>IF(D354="?OLD","!!!","")</f>
@@ -14113,87 +14096,87 @@
       <c r="L354" s="27"/>
     </row>
     <row r="355" spans="1:12">
-      <c r="A355" s="20"/>
+      <c r="A355" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="E355" s="22">
+        <f>IF(D355="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F355" s="23" t="str">
+        <f>IF(OR(E355="",E355="!!!"),"",IF(NOT(ISNA(VLOOKUP(E355,E$1:E354,1,FALSE()))),"OLD",IF(AND(E355&lt;&gt;"",E355&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G355" s="24" t="str">
+        <f>IF(OR(E355="",E355="!!!"),"",IF(OR(J355=0,AND(J355=1,K355=1),AND(J355=1,I355="SBJ"),AND(J355=1,I355=0)),"?IN_FOCUS",IF(J355&lt;=2,"?ACTIVATED",IF(J355&lt;&gt;"","?FAMILIAR",IF(F355="NEW",IF(ISNA(VLOOKUP(E355,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H355" s="25" t="str">
+        <f>IF(J355&lt;&gt;1,"",IF(I355="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I355" s="26" t="str">
+        <f>IF(OR(E355="",E355="!!!",F355="NEW"),"",INDEX(B354:B$2,-1+SUMPRODUCT(MAX(ROW(E354:E$2)*(E355=E354:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J355" s="26" t="str">
+        <f>IF(OR(E355="",E355="!!!",F355="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E355)*(E355=E$2:E355)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E354)*(E2=E$1:E354))))))</f>
+        <v> </v>
+      </c>
+      <c r="K355" s="26" t="str">
+        <f>IF(OR(E355="",E355="!!!",F355="NEW"),"",INDEX(J$1:J354,SUMPRODUCT(MAX(ROW(E$1:E354)*(E355=E$1:E354)))))</f>
+        <v> </v>
+      </c>
+      <c r="L355" s="27"/>
     </row>
     <row r="356" spans="1:12">
       <c r="A356" s="20" t="s">
-        <v>304</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E356" s="22">
+        <f>IF(D356="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F356" s="23" t="str">
+        <f>IF(OR(E356="",E356="!!!"),"",IF(NOT(ISNA(VLOOKUP(E356,E$1:E355,1,FALSE()))),"OLD",IF(AND(E356&lt;&gt;"",E356&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G356" s="24" t="str">
+        <f>IF(OR(E356="",E356="!!!"),"",IF(OR(J356=0,AND(J356=1,K356=1),AND(J356=1,I356="SBJ"),AND(J356=1,I356=0)),"?IN_FOCUS",IF(J356&lt;=2,"?ACTIVATED",IF(J356&lt;&gt;"","?FAMILIAR",IF(F356="NEW",IF(ISNA(VLOOKUP(E356,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H356" s="25" t="str">
+        <f>IF(J356&lt;&gt;1,"",IF(I356="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I356" s="26" t="str">
+        <f>IF(OR(E356="",E356="!!!",F356="NEW"),"",INDEX(B355:B$2,-1+SUMPRODUCT(MAX(ROW(E355:E$2)*(E356=E355:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J356" s="26" t="str">
+        <f>IF(OR(E356="",E356="!!!",F356="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E356)*(E356=E$2:E356)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E355)*(E2=E$1:E355))))))</f>
+        <v> </v>
+      </c>
+      <c r="K356" s="26" t="str">
+        <f>IF(OR(E356="",E356="!!!",F356="NEW"),"",INDEX(J$1:J355,SUMPRODUCT(MAX(ROW(E$1:E355)*(E356=E$1:E355)))))</f>
+        <v> </v>
+      </c>
+      <c r="L356" s="27"/>
     </row>
     <row r="357" spans="1:12">
-      <c r="A357" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="B357" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="E357" s="22">
-        <f>IF(D357="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F357" s="23" t="str">
-        <f>IF(OR(E357="",E357="!!!"),"",IF(NOT(ISNA(VLOOKUP(E357,E$1:E356,1,FALSE()))),"OLD",IF(AND(E357&lt;&gt;"",E357&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G357" s="24" t="str">
-        <f>IF(OR(E357="",E357="!!!"),"",IF(OR(J357=0,AND(J357=1,K357=1),AND(J357=1,I357="SBJ"),AND(J357=1,I357=0)),"?IN_FOCUS",IF(J357&lt;=2,"?ACTIVATED",IF(J357&lt;&gt;"","?FAMILIAR",IF(F357="NEW",IF(ISNA(VLOOKUP(E357,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H357" s="25" t="str">
-        <f>IF(J357&lt;&gt;1,"",IF(I357="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I357" s="26" t="str">
-        <f>IF(OR(E357="",E357="!!!",F357="NEW"),"",INDEX(B356:B$2,-1+SUMPRODUCT(MAX(ROW(E356:E$2)*(E357=E356:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J357" s="26" t="str">
-        <f>IF(OR(E357="",E357="!!!",F357="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E357)*(E357=E$2:E357)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E356)*(E2=E$1:E356))))))</f>
-        <v> </v>
-      </c>
-      <c r="K357" s="26" t="str">
-        <f>IF(OR(E357="",E357="!!!",F357="NEW"),"",INDEX(J$1:J356,SUMPRODUCT(MAX(ROW(E$1:E356)*(E357=E$1:E356)))))</f>
-        <v> </v>
-      </c>
-      <c r="L357" s="27"/>
+      <c r="A357" s="20"/>
     </row>
     <row r="358" spans="1:12">
       <c r="A358" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E358" s="22">
-        <f>IF(D358="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F358" s="23" t="str">
-        <f>IF(OR(E358="",E358="!!!"),"",IF(NOT(ISNA(VLOOKUP(E358,E$1:E357,1,FALSE()))),"OLD",IF(AND(E358&lt;&gt;"",E358&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G358" s="24" t="str">
-        <f>IF(OR(E358="",E358="!!!"),"",IF(OR(J358=0,AND(J358=1,K358=1),AND(J358=1,I358="SBJ"),AND(J358=1,I358=0)),"?IN_FOCUS",IF(J358&lt;=2,"?ACTIVATED",IF(J358&lt;&gt;"","?FAMILIAR",IF(F358="NEW",IF(ISNA(VLOOKUP(E358,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H358" s="25" t="str">
-        <f>IF(J358&lt;&gt;1,"",IF(I358="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I358" s="26" t="str">
-        <f>IF(OR(E358="",E358="!!!",F358="NEW"),"",INDEX(B357:B$2,-1+SUMPRODUCT(MAX(ROW(E357:E$2)*(E358=E357:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J358" s="26" t="str">
-        <f>IF(OR(E358="",E358="!!!",F358="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E358)*(E358=E$2:E358)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E357)*(E2=E$1:E357))))))</f>
-        <v> </v>
-      </c>
-      <c r="K358" s="26" t="str">
-        <f>IF(OR(E358="",E358="!!!",F358="NEW"),"",INDEX(J$1:J357,SUMPRODUCT(MAX(ROW(E$1:E357)*(E358=E$1:E357)))))</f>
-        <v> </v>
-      </c>
-      <c r="L358" s="27"/>
+        <v>308</v>
+      </c>
     </row>
     <row r="359" spans="1:12">
       <c r="A359" s="20" t="s">
-        <v>305</v>
+        <v>154</v>
+      </c>
+      <c r="B359" s="21" t="s">
+        <v>90</v>
       </c>
       <c r="E359" s="22">
         <f>IF(D359="?OLD","!!!","")</f>
@@ -14227,7 +14210,7 @@
     </row>
     <row r="360" spans="1:12">
       <c r="A360" s="20" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E360" s="22">
         <f>IF(D360="?OLD","!!!","")</f>
@@ -14261,7 +14244,7 @@
     </row>
     <row r="361" spans="1:12">
       <c r="A361" s="20" t="s">
-        <v>118</v>
+        <v>309</v>
       </c>
       <c r="E361" s="22">
         <f>IF(D361="?OLD","!!!","")</f>
@@ -14295,16 +14278,7 @@
     </row>
     <row r="362" spans="1:12">
       <c r="A362" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="B362" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C362" s="21" t="s">
         <v>112</v>
-      </c>
-      <c r="D362" s="21" t="s">
-        <v>100</v>
       </c>
       <c r="E362" s="22">
         <f>IF(D362="?OLD","!!!","")</f>
@@ -14338,16 +14312,7 @@
     </row>
     <row r="363" spans="1:12">
       <c r="A363" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="B363" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C363" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="D363" s="21" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E363" s="22">
         <f>IF(D363="?OLD","!!!","")</f>
@@ -14383,6 +14348,15 @@
       <c r="A364" s="20" t="s">
         <v>157</v>
       </c>
+      <c r="B364" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C364" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D364" s="21" t="s">
+        <v>104</v>
+      </c>
       <c r="E364" s="22">
         <f>IF(D364="?OLD","!!!","")</f>
         <v/>
@@ -14415,7 +14389,16 @@
     </row>
     <row r="365" spans="1:12">
       <c r="A365" s="20" t="s">
-        <v>61</v>
+        <v>159</v>
+      </c>
+      <c r="B365" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C365" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D365" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E365" s="22">
         <f>IF(D365="?OLD","!!!","")</f>
@@ -14449,7 +14432,7 @@
     </row>
     <row r="366" spans="1:12">
       <c r="A366" s="20" t="s">
-        <v>306</v>
+        <v>160</v>
       </c>
       <c r="E366" s="22">
         <f>IF(D366="?OLD","!!!","")</f>
@@ -14483,7 +14466,7 @@
     </row>
     <row r="367" spans="1:12">
       <c r="A367" s="20" t="s">
-        <v>254</v>
+        <v>64</v>
       </c>
       <c r="E367" s="22">
         <f>IF(D367="?OLD","!!!","")</f>
@@ -14517,13 +14500,7 @@
     </row>
     <row r="368" spans="1:12">
       <c r="A368" s="20" t="s">
-        <v>307</v>
-      </c>
-      <c r="B368" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C368" s="21" t="s">
-        <v>88</v>
+        <v>310</v>
       </c>
       <c r="E368" s="22">
         <f>IF(D368="?OLD","!!!","")</f>
@@ -14557,7 +14534,7 @@
     </row>
     <row r="369" spans="1:12">
       <c r="A369" s="20" t="s">
-        <v>147</v>
+        <v>258</v>
       </c>
       <c r="E369" s="22">
         <f>IF(D369="?OLD","!!!","")</f>
@@ -14590,90 +14567,90 @@
       <c r="L369" s="27"/>
     </row>
     <row r="370" spans="1:12">
-      <c r="A370" s="20"/>
+      <c r="A370" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="B370" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C370" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="E370" s="22">
+        <f>IF(D370="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F370" s="23" t="str">
+        <f>IF(OR(E370="",E370="!!!"),"",IF(NOT(ISNA(VLOOKUP(E370,E$1:E369,1,FALSE()))),"OLD",IF(AND(E370&lt;&gt;"",E370&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G370" s="24" t="str">
+        <f>IF(OR(E370="",E370="!!!"),"",IF(OR(J370=0,AND(J370=1,K370=1),AND(J370=1,I370="SBJ"),AND(J370=1,I370=0)),"?IN_FOCUS",IF(J370&lt;=2,"?ACTIVATED",IF(J370&lt;&gt;"","?FAMILIAR",IF(F370="NEW",IF(ISNA(VLOOKUP(E370,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H370" s="25" t="str">
+        <f>IF(J370&lt;&gt;1,"",IF(I370="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I370" s="26" t="str">
+        <f>IF(OR(E370="",E370="!!!",F370="NEW"),"",INDEX(B369:B$2,-1+SUMPRODUCT(MAX(ROW(E369:E$2)*(E370=E369:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J370" s="26" t="str">
+        <f>IF(OR(E370="",E370="!!!",F370="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E370)*(E370=E$2:E370)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E369)*(E2=E$1:E369))))))</f>
+        <v> </v>
+      </c>
+      <c r="K370" s="26" t="str">
+        <f>IF(OR(E370="",E370="!!!",F370="NEW"),"",INDEX(J$1:J369,SUMPRODUCT(MAX(ROW(E$1:E369)*(E370=E$1:E369)))))</f>
+        <v> </v>
+      </c>
+      <c r="L370" s="27"/>
     </row>
     <row r="371" spans="1:12">
       <c r="A371" s="20" t="s">
-        <v>308</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E371" s="22">
+        <f>IF(D371="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F371" s="23" t="str">
+        <f>IF(OR(E371="",E371="!!!"),"",IF(NOT(ISNA(VLOOKUP(E371,E$1:E370,1,FALSE()))),"OLD",IF(AND(E371&lt;&gt;"",E371&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G371" s="24" t="str">
+        <f>IF(OR(E371="",E371="!!!"),"",IF(OR(J371=0,AND(J371=1,K371=1),AND(J371=1,I371="SBJ"),AND(J371=1,I371=0)),"?IN_FOCUS",IF(J371&lt;=2,"?ACTIVATED",IF(J371&lt;&gt;"","?FAMILIAR",IF(F371="NEW",IF(ISNA(VLOOKUP(E371,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H371" s="25" t="str">
+        <f>IF(J371&lt;&gt;1,"",IF(I371="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I371" s="26" t="str">
+        <f>IF(OR(E371="",E371="!!!",F371="NEW"),"",INDEX(B370:B$2,-1+SUMPRODUCT(MAX(ROW(E370:E$2)*(E371=E370:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J371" s="26" t="str">
+        <f>IF(OR(E371="",E371="!!!",F371="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E371)*(E371=E$2:E371)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E370)*(E2=E$1:E370))))))</f>
+        <v> </v>
+      </c>
+      <c r="K371" s="26" t="str">
+        <f>IF(OR(E371="",E371="!!!",F371="NEW"),"",INDEX(J$1:J370,SUMPRODUCT(MAX(ROW(E$1:E370)*(E371=E$1:E370)))))</f>
+        <v> </v>
+      </c>
+      <c r="L371" s="27"/>
     </row>
     <row r="372" spans="1:12">
-      <c r="A372" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="E372" s="22">
-        <f>IF(D372="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F372" s="23" t="str">
-        <f>IF(OR(E372="",E372="!!!"),"",IF(NOT(ISNA(VLOOKUP(E372,E$1:E371,1,FALSE()))),"OLD",IF(AND(E372&lt;&gt;"",E372&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G372" s="24" t="str">
-        <f>IF(OR(E372="",E372="!!!"),"",IF(OR(J372=0,AND(J372=1,K372=1),AND(J372=1,I372="SBJ"),AND(J372=1,I372=0)),"?IN_FOCUS",IF(J372&lt;=2,"?ACTIVATED",IF(J372&lt;&gt;"","?FAMILIAR",IF(F372="NEW",IF(ISNA(VLOOKUP(E372,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H372" s="25" t="str">
-        <f>IF(J372&lt;&gt;1,"",IF(I372="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I372" s="26" t="str">
-        <f>IF(OR(E372="",E372="!!!",F372="NEW"),"",INDEX(B371:B$2,-1+SUMPRODUCT(MAX(ROW(E371:E$2)*(E372=E371:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J372" s="26" t="str">
-        <f>IF(OR(E372="",E372="!!!",F372="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E372)*(E372=E$2:E372)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E371)*(E2=E$1:E371))))))</f>
-        <v> </v>
-      </c>
-      <c r="K372" s="26" t="str">
-        <f>IF(OR(E372="",E372="!!!",F372="NEW"),"",INDEX(J$1:J371,SUMPRODUCT(MAX(ROW(E$1:E371)*(E372=E$1:E371)))))</f>
-        <v> </v>
-      </c>
-      <c r="L372" s="27"/>
+      <c r="A372" s="20"/>
     </row>
     <row r="373" spans="1:12">
       <c r="A373" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="B373" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C373" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="E373" s="22">
-        <f>IF(D373="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F373" s="23" t="str">
-        <f>IF(OR(E373="",E373="!!!"),"",IF(NOT(ISNA(VLOOKUP(E373,E$1:E372,1,FALSE()))),"OLD",IF(AND(E373&lt;&gt;"",E373&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G373" s="24" t="str">
-        <f>IF(OR(E373="",E373="!!!"),"",IF(OR(J373=0,AND(J373=1,K373=1),AND(J373=1,I373="SBJ"),AND(J373=1,I373=0)),"?IN_FOCUS",IF(J373&lt;=2,"?ACTIVATED",IF(J373&lt;&gt;"","?FAMILIAR",IF(F373="NEW",IF(ISNA(VLOOKUP(E373,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H373" s="25" t="str">
-        <f>IF(J373&lt;&gt;1,"",IF(I373="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I373" s="26" t="str">
-        <f>IF(OR(E373="",E373="!!!",F373="NEW"),"",INDEX(B372:B$2,-1+SUMPRODUCT(MAX(ROW(E372:E$2)*(E373=E372:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J373" s="26" t="str">
-        <f>IF(OR(E373="",E373="!!!",F373="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E373)*(E373=E$2:E373)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E372)*(E2=E$1:E372))))))</f>
-        <v> </v>
-      </c>
-      <c r="K373" s="26" t="str">
-        <f>IF(OR(E373="",E373="!!!",F373="NEW"),"",INDEX(J$1:J372,SUMPRODUCT(MAX(ROW(E$1:E372)*(E373=E$1:E372)))))</f>
-        <v> </v>
-      </c>
-      <c r="L373" s="27"/>
+        <v>312</v>
+      </c>
     </row>
     <row r="374" spans="1:12">
       <c r="A374" s="20" t="s">
-        <v>193</v>
+        <v>313</v>
       </c>
       <c r="E374" s="22">
         <f>IF(D374="?OLD","!!!","")</f>
@@ -14707,6 +14684,12 @@
     </row>
     <row r="375" spans="1:12">
       <c r="A375" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="B375" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C375" s="21" t="s">
         <v>127</v>
       </c>
       <c r="E375" s="22">
@@ -14741,16 +14724,7 @@
     </row>
     <row r="376" spans="1:12">
       <c r="A376" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="B376" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="C376" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D376" s="21" t="s">
-        <v>100</v>
+        <v>197</v>
       </c>
       <c r="E376" s="22">
         <f>IF(D376="?OLD","!!!","")</f>
@@ -14784,7 +14758,7 @@
     </row>
     <row r="377" spans="1:12">
       <c r="A377" s="20" t="s">
-        <v>184</v>
+        <v>131</v>
       </c>
       <c r="E377" s="22">
         <f>IF(D377="?OLD","!!!","")</f>
@@ -14818,7 +14792,16 @@
     </row>
     <row r="378" spans="1:12">
       <c r="A378" s="20" t="s">
-        <v>106</v>
+        <v>89</v>
+      </c>
+      <c r="B378" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C378" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D378" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E378" s="22">
         <f>IF(D378="?OLD","!!!","")</f>
@@ -14852,7 +14835,7 @@
     </row>
     <row r="379" spans="1:12">
       <c r="A379" s="20" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E379" s="22">
         <f>IF(D379="?OLD","!!!","")</f>
@@ -14886,16 +14869,7 @@
     </row>
     <row r="380" spans="1:12">
       <c r="A380" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="B380" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="C380" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="D380" s="21" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E380" s="22">
         <f>IF(D380="?OLD","!!!","")</f>
@@ -14929,7 +14903,7 @@
     </row>
     <row r="381" spans="1:12">
       <c r="A381" s="20" t="s">
-        <v>312</v>
+        <v>198</v>
       </c>
       <c r="E381" s="22">
         <f>IF(D381="?OLD","!!!","")</f>
@@ -14963,16 +14937,16 @@
     </row>
     <row r="382" spans="1:12">
       <c r="A382" s="20" t="s">
-        <v>138</v>
+        <v>315</v>
       </c>
       <c r="B382" s="21" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="C382" s="21" t="s">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="D382" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E382" s="22">
         <f>IF(D382="?OLD","!!!","")</f>
@@ -15006,7 +14980,7 @@
     </row>
     <row r="383" spans="1:12">
       <c r="A383" s="20" t="s">
-        <v>197</v>
+        <v>316</v>
       </c>
       <c r="E383" s="22">
         <f>IF(D383="?OLD","!!!","")</f>
@@ -15040,7 +15014,16 @@
     </row>
     <row r="384" spans="1:12">
       <c r="A384" s="20" t="s">
-        <v>313</v>
+        <v>142</v>
+      </c>
+      <c r="B384" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C384" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D384" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E384" s="22">
         <f>IF(D384="?OLD","!!!","")</f>
@@ -15074,7 +15057,7 @@
     </row>
     <row r="385" spans="1:12">
       <c r="A385" s="20" t="s">
-        <v>164</v>
+        <v>201</v>
       </c>
       <c r="E385" s="22">
         <f>IF(D385="?OLD","!!!","")</f>
@@ -15108,7 +15091,7 @@
     </row>
     <row r="386" spans="1:12">
       <c r="A386" s="20" t="s">
-        <v>106</v>
+        <v>317</v>
       </c>
       <c r="E386" s="22">
         <f>IF(D386="?OLD","!!!","")</f>
@@ -15142,7 +15125,7 @@
     </row>
     <row r="387" spans="1:12">
       <c r="A387" s="20" t="s">
-        <v>93</v>
+        <v>168</v>
       </c>
       <c r="E387" s="22">
         <f>IF(D387="?OLD","!!!","")</f>
@@ -15176,7 +15159,7 @@
     </row>
     <row r="388" spans="1:12">
       <c r="A388" s="20" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="E388" s="22">
         <f>IF(D388="?OLD","!!!","")</f>
@@ -15210,7 +15193,7 @@
     </row>
     <row r="389" spans="1:12">
       <c r="A389" s="20" t="s">
-        <v>314</v>
+        <v>96</v>
       </c>
       <c r="E389" s="22">
         <f>IF(D389="?OLD","!!!","")</f>
@@ -15244,13 +15227,7 @@
     </row>
     <row r="390" spans="1:12">
       <c r="A390" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="B390" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C390" s="21" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E390" s="22">
         <f>IF(D390="?OLD","!!!","")</f>
@@ -15284,7 +15261,7 @@
     </row>
     <row r="391" spans="1:12">
       <c r="A391" s="20" t="s">
-        <v>189</v>
+        <v>318</v>
       </c>
       <c r="E391" s="22">
         <f>IF(D391="?OLD","!!!","")</f>
@@ -15318,7 +15295,13 @@
     </row>
     <row r="392" spans="1:12">
       <c r="A392" s="20" t="s">
-        <v>315</v>
+        <v>105</v>
+      </c>
+      <c r="B392" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="C392" s="21" t="s">
+        <v>127</v>
       </c>
       <c r="E392" s="22">
         <f>IF(D392="?OLD","!!!","")</f>
@@ -15352,7 +15335,7 @@
     </row>
     <row r="393" spans="1:12">
       <c r="A393" s="20" t="s">
-        <v>118</v>
+        <v>193</v>
       </c>
       <c r="E393" s="22">
         <f>IF(D393="?OLD","!!!","")</f>
@@ -15386,13 +15369,7 @@
     </row>
     <row r="394" spans="1:12">
       <c r="A394" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="B394" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="C394" s="21" t="s">
-        <v>88</v>
+        <v>319</v>
       </c>
       <c r="E394" s="22">
         <f>IF(D394="?OLD","!!!","")</f>
@@ -15426,7 +15403,7 @@
     </row>
     <row r="395" spans="1:12">
       <c r="A395" s="20" t="s">
-        <v>189</v>
+        <v>122</v>
       </c>
       <c r="E395" s="22">
         <f>IF(D395="?OLD","!!!","")</f>
@@ -15460,7 +15437,13 @@
     </row>
     <row r="396" spans="1:12">
       <c r="A396" s="20" t="s">
-        <v>316</v>
+        <v>147</v>
+      </c>
+      <c r="B396" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="C396" s="21" t="s">
+        <v>91</v>
       </c>
       <c r="E396" s="22">
         <f>IF(D396="?OLD","!!!","")</f>
@@ -15494,7 +15477,7 @@
     </row>
     <row r="397" spans="1:12">
       <c r="A397" s="20" t="s">
-        <v>147</v>
+        <v>193</v>
       </c>
       <c r="E397" s="22">
         <f>IF(D397="?OLD","!!!","")</f>
@@ -15527,93 +15510,84 @@
       <c r="L397" s="27"/>
     </row>
     <row r="398" spans="1:12">
-      <c r="A398" s="20"/>
+      <c r="A398" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="E398" s="22">
+        <f>IF(D398="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F398" s="23" t="str">
+        <f>IF(OR(E398="",E398="!!!"),"",IF(NOT(ISNA(VLOOKUP(E398,E$1:E397,1,FALSE()))),"OLD",IF(AND(E398&lt;&gt;"",E398&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G398" s="24" t="str">
+        <f>IF(OR(E398="",E398="!!!"),"",IF(OR(J398=0,AND(J398=1,K398=1),AND(J398=1,I398="SBJ"),AND(J398=1,I398=0)),"?IN_FOCUS",IF(J398&lt;=2,"?ACTIVATED",IF(J398&lt;&gt;"","?FAMILIAR",IF(F398="NEW",IF(ISNA(VLOOKUP(E398,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H398" s="25" t="str">
+        <f>IF(J398&lt;&gt;1,"",IF(I398="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I398" s="26" t="str">
+        <f>IF(OR(E398="",E398="!!!",F398="NEW"),"",INDEX(B397:B$2,-1+SUMPRODUCT(MAX(ROW(E397:E$2)*(E398=E397:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J398" s="26" t="str">
+        <f>IF(OR(E398="",E398="!!!",F398="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E398)*(E398=E$2:E398)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E397)*(E2=E$1:E397))))))</f>
+        <v> </v>
+      </c>
+      <c r="K398" s="26" t="str">
+        <f>IF(OR(E398="",E398="!!!",F398="NEW"),"",INDEX(J$1:J397,SUMPRODUCT(MAX(ROW(E$1:E397)*(E398=E$1:E397)))))</f>
+        <v> </v>
+      </c>
+      <c r="L398" s="27"/>
     </row>
     <row r="399" spans="1:12">
       <c r="A399" s="20" t="s">
-        <v>317</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E399" s="22">
+        <f>IF(D399="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F399" s="23" t="str">
+        <f>IF(OR(E399="",E399="!!!"),"",IF(NOT(ISNA(VLOOKUP(E399,E$1:E398,1,FALSE()))),"OLD",IF(AND(E399&lt;&gt;"",E399&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G399" s="24" t="str">
+        <f>IF(OR(E399="",E399="!!!"),"",IF(OR(J399=0,AND(J399=1,K399=1),AND(J399=1,I399="SBJ"),AND(J399=1,I399=0)),"?IN_FOCUS",IF(J399&lt;=2,"?ACTIVATED",IF(J399&lt;&gt;"","?FAMILIAR",IF(F399="NEW",IF(ISNA(VLOOKUP(E399,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H399" s="25" t="str">
+        <f>IF(J399&lt;&gt;1,"",IF(I399="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I399" s="26" t="str">
+        <f>IF(OR(E399="",E399="!!!",F399="NEW"),"",INDEX(B398:B$2,-1+SUMPRODUCT(MAX(ROW(E398:E$2)*(E399=E398:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J399" s="26" t="str">
+        <f>IF(OR(E399="",E399="!!!",F399="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E399)*(E399=E$2:E399)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E398)*(E2=E$1:E398))))))</f>
+        <v> </v>
+      </c>
+      <c r="K399" s="26" t="str">
+        <f>IF(OR(E399="",E399="!!!",F399="NEW"),"",INDEX(J$1:J398,SUMPRODUCT(MAX(ROW(E$1:E398)*(E399=E$1:E398)))))</f>
+        <v> </v>
+      </c>
+      <c r="L399" s="27"/>
     </row>
     <row r="400" spans="1:12">
-      <c r="A400" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="E400" s="22">
-        <f>IF(D400="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F400" s="23" t="str">
-        <f>IF(OR(E400="",E400="!!!"),"",IF(NOT(ISNA(VLOOKUP(E400,E$1:E399,1,FALSE()))),"OLD",IF(AND(E400&lt;&gt;"",E400&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G400" s="24" t="str">
-        <f>IF(OR(E400="",E400="!!!"),"",IF(OR(J400=0,AND(J400=1,K400=1),AND(J400=1,I400="SBJ"),AND(J400=1,I400=0)),"?IN_FOCUS",IF(J400&lt;=2,"?ACTIVATED",IF(J400&lt;&gt;"","?FAMILIAR",IF(F400="NEW",IF(ISNA(VLOOKUP(E400,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H400" s="25" t="str">
-        <f>IF(J400&lt;&gt;1,"",IF(I400="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I400" s="26" t="str">
-        <f>IF(OR(E400="",E400="!!!",F400="NEW"),"",INDEX(B399:B$2,-1+SUMPRODUCT(MAX(ROW(E399:E$2)*(E400=E399:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J400" s="26" t="str">
-        <f>IF(OR(E400="",E400="!!!",F400="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E400)*(E400=E$2:E400)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E399)*(E2=E$1:E399))))))</f>
-        <v> </v>
-      </c>
-      <c r="K400" s="26" t="str">
-        <f>IF(OR(E400="",E400="!!!",F400="NEW"),"",INDEX(J$1:J399,SUMPRODUCT(MAX(ROW(E$1:E399)*(E400=E$1:E399)))))</f>
-        <v> </v>
-      </c>
-      <c r="L400" s="27"/>
+      <c r="A400" s="20"/>
     </row>
     <row r="401" spans="1:12">
       <c r="A401" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="B401" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C401" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D401" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="E401" s="22">
-        <f>IF(D401="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F401" s="23" t="str">
-        <f>IF(OR(E401="",E401="!!!"),"",IF(NOT(ISNA(VLOOKUP(E401,E$1:E400,1,FALSE()))),"OLD",IF(AND(E401&lt;&gt;"",E401&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G401" s="24" t="str">
-        <f>IF(OR(E401="",E401="!!!"),"",IF(OR(J401=0,AND(J401=1,K401=1),AND(J401=1,I401="SBJ"),AND(J401=1,I401=0)),"?IN_FOCUS",IF(J401&lt;=2,"?ACTIVATED",IF(J401&lt;&gt;"","?FAMILIAR",IF(F401="NEW",IF(ISNA(VLOOKUP(E401,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H401" s="25" t="str">
-        <f>IF(J401&lt;&gt;1,"",IF(I401="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I401" s="26" t="str">
-        <f>IF(OR(E401="",E401="!!!",F401="NEW"),"",INDEX(B400:B$2,-1+SUMPRODUCT(MAX(ROW(E400:E$2)*(E401=E400:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J401" s="26" t="str">
-        <f>IF(OR(E401="",E401="!!!",F401="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E401)*(E401=E$2:E401)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E400)*(E2=E$1:E400))))))</f>
-        <v> </v>
-      </c>
-      <c r="K401" s="26" t="str">
-        <f>IF(OR(E401="",E401="!!!",F401="NEW"),"",INDEX(J$1:J400,SUMPRODUCT(MAX(ROW(E$1:E400)*(E401=E$1:E400)))))</f>
-        <v> </v>
-      </c>
-      <c r="L401" s="27"/>
+        <v>321</v>
+      </c>
     </row>
     <row r="402" spans="1:12">
       <c r="A402" s="20" t="s">
-        <v>318</v>
+        <v>196</v>
       </c>
       <c r="E402" s="22">
         <f>IF(D402="?OLD","!!!","")</f>
@@ -15647,7 +15621,16 @@
     </row>
     <row r="403" spans="1:12">
       <c r="A403" s="20" t="s">
-        <v>319</v>
+        <v>170</v>
+      </c>
+      <c r="B403" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C403" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D403" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E403" s="22">
         <f>IF(D403="?OLD","!!!","")</f>
@@ -15681,7 +15664,7 @@
     </row>
     <row r="404" spans="1:12">
       <c r="A404" s="20" t="s">
-        <v>226</v>
+        <v>322</v>
       </c>
       <c r="E404" s="22">
         <f>IF(D404="?OLD","!!!","")</f>
@@ -15715,13 +15698,7 @@
     </row>
     <row r="405" spans="1:12">
       <c r="A405" s="20" t="s">
-        <v>320</v>
-      </c>
-      <c r="B405" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="C405" s="21" t="s">
-        <v>123</v>
+        <v>323</v>
       </c>
       <c r="E405" s="22">
         <f>IF(D405="?OLD","!!!","")</f>
@@ -15755,7 +15732,7 @@
     </row>
     <row r="406" spans="1:12">
       <c r="A406" s="20" t="s">
-        <v>321</v>
+        <v>230</v>
       </c>
       <c r="E406" s="22">
         <f>IF(D406="?OLD","!!!","")</f>
@@ -15789,7 +15766,13 @@
     </row>
     <row r="407" spans="1:12">
       <c r="A407" s="20" t="s">
-        <v>107</v>
+        <v>324</v>
+      </c>
+      <c r="B407" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C407" s="21" t="s">
+        <v>127</v>
       </c>
       <c r="E407" s="22">
         <f>IF(D407="?OLD","!!!","")</f>
@@ -15823,16 +15806,7 @@
     </row>
     <row r="408" spans="1:12">
       <c r="A408" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="B408" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C408" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D408" s="21" t="s">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="E408" s="22">
         <f>IF(D408="?OLD","!!!","")</f>
@@ -15866,7 +15840,7 @@
     </row>
     <row r="409" spans="1:12">
       <c r="A409" s="20" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E409" s="22">
         <f>IF(D409="?OLD","!!!","")</f>
@@ -15900,10 +15874,16 @@
     </row>
     <row r="410" spans="1:12">
       <c r="A410" s="20" t="s">
-        <v>107</v>
+        <v>226</v>
       </c>
       <c r="B410" s="21" t="s">
-        <v>108</v>
+        <v>98</v>
+      </c>
+      <c r="C410" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D410" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E410" s="22">
         <f>IF(D410="?OLD","!!!","")</f>
@@ -15937,7 +15917,7 @@
     </row>
     <row r="411" spans="1:12">
       <c r="A411" s="20" t="s">
-        <v>177</v>
+        <v>112</v>
       </c>
       <c r="E411" s="22">
         <f>IF(D411="?OLD","!!!","")</f>
@@ -15971,7 +15951,10 @@
     </row>
     <row r="412" spans="1:12">
       <c r="A412" s="20" t="s">
-        <v>226</v>
+        <v>113</v>
+      </c>
+      <c r="B412" s="21" t="s">
+        <v>164</v>
       </c>
       <c r="E412" s="22">
         <f>IF(D412="?OLD","!!!","")</f>
@@ -16005,7 +15988,7 @@
     </row>
     <row r="413" spans="1:12">
       <c r="A413" s="20" t="s">
-        <v>322</v>
+        <v>181</v>
       </c>
       <c r="E413" s="22">
         <f>IF(D413="?OLD","!!!","")</f>
@@ -16039,7 +16022,7 @@
     </row>
     <row r="414" spans="1:12">
       <c r="A414" s="20" t="s">
-        <v>323</v>
+        <v>230</v>
       </c>
       <c r="E414" s="22">
         <f>IF(D414="?OLD","!!!","")</f>
@@ -16073,7 +16056,7 @@
     </row>
     <row r="415" spans="1:12">
       <c r="A415" s="20" t="s">
-        <v>12</v>
+        <v>326</v>
       </c>
       <c r="E415" s="22">
         <f>IF(D415="?OLD","!!!","")</f>
@@ -16107,13 +16090,7 @@
     </row>
     <row r="416" spans="1:12">
       <c r="A416" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="B416" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C416" s="21" t="s">
-        <v>123</v>
+        <v>327</v>
       </c>
       <c r="E416" s="22">
         <f>IF(D416="?OLD","!!!","")</f>
@@ -16147,7 +16124,7 @@
     </row>
     <row r="417" spans="1:12">
       <c r="A417" s="20" t="s">
-        <v>325</v>
+        <v>12</v>
       </c>
       <c r="E417" s="22">
         <f>IF(D417="?OLD","!!!","")</f>
@@ -16181,7 +16158,13 @@
     </row>
     <row r="418" spans="1:12">
       <c r="A418" s="20" t="s">
-        <v>326</v>
+        <v>328</v>
+      </c>
+      <c r="B418" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C418" s="21" t="s">
+        <v>127</v>
       </c>
       <c r="E418" s="22">
         <f>IF(D418="?OLD","!!!","")</f>
@@ -16215,13 +16198,7 @@
     </row>
     <row r="419" spans="1:12">
       <c r="A419" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="B419" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="C419" s="21" t="s">
-        <v>123</v>
+        <v>329</v>
       </c>
       <c r="E419" s="22">
         <f>IF(D419="?OLD","!!!","")</f>
@@ -16255,7 +16232,7 @@
     </row>
     <row r="420" spans="1:12">
       <c r="A420" s="20" t="s">
-        <v>254</v>
+        <v>330</v>
       </c>
       <c r="E420" s="22">
         <f>IF(D420="?OLD","!!!","")</f>
@@ -16289,7 +16266,13 @@
     </row>
     <row r="421" spans="1:12">
       <c r="A421" s="20" t="s">
-        <v>97</v>
+        <v>331</v>
+      </c>
+      <c r="B421" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="C421" s="21" t="s">
+        <v>127</v>
       </c>
       <c r="E421" s="22">
         <f>IF(D421="?OLD","!!!","")</f>
@@ -16323,7 +16306,7 @@
     </row>
     <row r="422" spans="1:12">
       <c r="A422" s="20" t="s">
-        <v>328</v>
+        <v>258</v>
       </c>
       <c r="E422" s="22">
         <f>IF(D422="?OLD","!!!","")</f>
@@ -16357,15 +16340,6 @@
     </row>
     <row r="423" spans="1:12">
       <c r="A423" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="B423" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C423" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D423" s="21" t="s">
         <v>100</v>
       </c>
       <c r="E423" s="22">
@@ -16400,7 +16374,7 @@
     </row>
     <row r="424" spans="1:12">
       <c r="A424" s="20" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E424" s="22">
         <f>IF(D424="?OLD","!!!","")</f>
@@ -16434,7 +16408,16 @@
     </row>
     <row r="425" spans="1:12">
       <c r="A425" s="20" t="s">
-        <v>118</v>
+        <v>200</v>
+      </c>
+      <c r="B425" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C425" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D425" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E425" s="22">
         <f>IF(D425="?OLD","!!!","")</f>
@@ -16468,7 +16451,7 @@
     </row>
     <row r="426" spans="1:12">
       <c r="A426" s="20" t="s">
-        <v>133</v>
+        <v>333</v>
       </c>
       <c r="E426" s="22">
         <f>IF(D426="?OLD","!!!","")</f>
@@ -16502,16 +16485,7 @@
     </row>
     <row r="427" spans="1:12">
       <c r="A427" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="B427" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="C427" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="D427" s="21" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E427" s="22">
         <f>IF(D427="?OLD","!!!","")</f>
@@ -16545,7 +16519,7 @@
     </row>
     <row r="428" spans="1:12">
       <c r="A428" s="20" t="s">
-        <v>330</v>
+        <v>137</v>
       </c>
       <c r="E428" s="22">
         <f>IF(D428="?OLD","!!!","")</f>
@@ -16579,7 +16553,16 @@
     </row>
     <row r="429" spans="1:12">
       <c r="A429" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B429" s="21" t="s">
         <v>263</v>
+      </c>
+      <c r="C429" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D429" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E429" s="22">
         <f>IF(D429="?OLD","!!!","")</f>
@@ -16613,7 +16596,7 @@
     </row>
     <row r="430" spans="1:12">
       <c r="A430" s="20" t="s">
-        <v>106</v>
+        <v>334</v>
       </c>
       <c r="E430" s="22">
         <f>IF(D430="?OLD","!!!","")</f>
@@ -16647,7 +16630,7 @@
     </row>
     <row r="431" spans="1:12">
       <c r="A431" s="20" t="s">
-        <v>194</v>
+        <v>267</v>
       </c>
       <c r="E431" s="22">
         <f>IF(D431="?OLD","!!!","")</f>
@@ -16681,16 +16664,7 @@
     </row>
     <row r="432" spans="1:12">
       <c r="A432" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="B432" s="21" t="s">
-        <v>331</v>
-      </c>
-      <c r="C432" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="D432" s="21" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E432" s="22">
         <f>IF(D432="?OLD","!!!","")</f>
@@ -16724,7 +16698,7 @@
     </row>
     <row r="433" spans="1:12">
       <c r="A433" s="20" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="E433" s="22">
         <f>IF(D433="?OLD","!!!","")</f>
@@ -16758,16 +16732,16 @@
     </row>
     <row r="434" spans="1:12">
       <c r="A434" s="20" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="B434" s="21" t="s">
-        <v>259</v>
+        <v>335</v>
       </c>
       <c r="C434" s="21" t="s">
-        <v>99</v>
+        <v>180</v>
       </c>
       <c r="D434" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E434" s="22">
         <f>IF(D434="?OLD","!!!","")</f>
@@ -16801,7 +16775,7 @@
     </row>
     <row r="435" spans="1:12">
       <c r="A435" s="20" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="E435" s="22">
         <f>IF(D435="?OLD","!!!","")</f>
@@ -16835,16 +16809,16 @@
     </row>
     <row r="436" spans="1:12">
       <c r="A436" s="20" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B436" s="21" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="C436" s="21" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D436" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E436" s="22">
         <f>IF(D436="?OLD","!!!","")</f>
@@ -16878,7 +16852,7 @@
     </row>
     <row r="437" spans="1:12">
       <c r="A437" s="20" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="E437" s="22">
         <f>IF(D437="?OLD","!!!","")</f>
@@ -16912,7 +16886,16 @@
     </row>
     <row r="438" spans="1:12">
       <c r="A438" s="20" t="s">
-        <v>147</v>
+        <v>337</v>
+      </c>
+      <c r="B438" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="C438" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D438" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E438" s="22">
         <f>IF(D438="?OLD","!!!","")</f>
@@ -16945,96 +16928,90 @@
       <c r="L438" s="27"/>
     </row>
     <row r="439" spans="1:12">
-      <c r="A439" s="20"/>
+      <c r="A439" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="E439" s="22">
+        <f>IF(D439="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F439" s="23" t="str">
+        <f>IF(OR(E439="",E439="!!!"),"",IF(NOT(ISNA(VLOOKUP(E439,E$1:E438,1,FALSE()))),"OLD",IF(AND(E439&lt;&gt;"",E439&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G439" s="24" t="str">
+        <f>IF(OR(E439="",E439="!!!"),"",IF(OR(J439=0,AND(J439=1,K439=1),AND(J439=1,I439="SBJ"),AND(J439=1,I439=0)),"?IN_FOCUS",IF(J439&lt;=2,"?ACTIVATED",IF(J439&lt;&gt;"","?FAMILIAR",IF(F439="NEW",IF(ISNA(VLOOKUP(E439,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H439" s="25" t="str">
+        <f>IF(J439&lt;&gt;1,"",IF(I439="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I439" s="26" t="str">
+        <f>IF(OR(E439="",E439="!!!",F439="NEW"),"",INDEX(B438:B$2,-1+SUMPRODUCT(MAX(ROW(E438:E$2)*(E439=E438:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J439" s="26" t="str">
+        <f>IF(OR(E439="",E439="!!!",F439="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E439)*(E439=E$2:E439)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E438)*(E2=E$1:E438))))))</f>
+        <v> </v>
+      </c>
+      <c r="K439" s="26" t="str">
+        <f>IF(OR(E439="",E439="!!!",F439="NEW"),"",INDEX(J$1:J438,SUMPRODUCT(MAX(ROW(E$1:E438)*(E439=E$1:E438)))))</f>
+        <v> </v>
+      </c>
+      <c r="L439" s="27"/>
     </row>
     <row r="440" spans="1:12">
       <c r="A440" s="20" t="s">
-        <v>334</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E440" s="22">
+        <f>IF(D440="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F440" s="23" t="str">
+        <f>IF(OR(E440="",E440="!!!"),"",IF(NOT(ISNA(VLOOKUP(E440,E$1:E439,1,FALSE()))),"OLD",IF(AND(E440&lt;&gt;"",E440&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G440" s="24" t="str">
+        <f>IF(OR(E440="",E440="!!!"),"",IF(OR(J440=0,AND(J440=1,K440=1),AND(J440=1,I440="SBJ"),AND(J440=1,I440=0)),"?IN_FOCUS",IF(J440&lt;=2,"?ACTIVATED",IF(J440&lt;&gt;"","?FAMILIAR",IF(F440="NEW",IF(ISNA(VLOOKUP(E440,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H440" s="25" t="str">
+        <f>IF(J440&lt;&gt;1,"",IF(I440="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I440" s="26" t="str">
+        <f>IF(OR(E440="",E440="!!!",F440="NEW"),"",INDEX(B439:B$2,-1+SUMPRODUCT(MAX(ROW(E439:E$2)*(E440=E439:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J440" s="26" t="str">
+        <f>IF(OR(E440="",E440="!!!",F440="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E440)*(E440=E$2:E440)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E439)*(E2=E$1:E439))))))</f>
+        <v> </v>
+      </c>
+      <c r="K440" s="26" t="str">
+        <f>IF(OR(E440="",E440="!!!",F440="NEW"),"",INDEX(J$1:J439,SUMPRODUCT(MAX(ROW(E$1:E439)*(E440=E$1:E439)))))</f>
+        <v> </v>
+      </c>
+      <c r="L440" s="27"/>
     </row>
     <row r="441" spans="1:12">
-      <c r="A441" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="B441" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C441" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="E441" s="22">
-        <f>IF(D441="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F441" s="23" t="str">
-        <f>IF(OR(E441="",E441="!!!"),"",IF(NOT(ISNA(VLOOKUP(E441,E$1:E440,1,FALSE()))),"OLD",IF(AND(E441&lt;&gt;"",E441&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G441" s="24" t="str">
-        <f>IF(OR(E441="",E441="!!!"),"",IF(OR(J441=0,AND(J441=1,K441=1),AND(J441=1,I441="SBJ"),AND(J441=1,I441=0)),"?IN_FOCUS",IF(J441&lt;=2,"?ACTIVATED",IF(J441&lt;&gt;"","?FAMILIAR",IF(F441="NEW",IF(ISNA(VLOOKUP(E441,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H441" s="25" t="str">
-        <f>IF(J441&lt;&gt;1,"",IF(I441="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I441" s="26" t="str">
-        <f>IF(OR(E441="",E441="!!!",F441="NEW"),"",INDEX(B440:B$2,-1+SUMPRODUCT(MAX(ROW(E440:E$2)*(E441=E440:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J441" s="26" t="str">
-        <f>IF(OR(E441="",E441="!!!",F441="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E441)*(E441=E$2:E441)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E440)*(E2=E$1:E440))))))</f>
-        <v> </v>
-      </c>
-      <c r="K441" s="26" t="str">
-        <f>IF(OR(E441="",E441="!!!",F441="NEW"),"",INDEX(J$1:J440,SUMPRODUCT(MAX(ROW(E$1:E440)*(E441=E$1:E440)))))</f>
-        <v> </v>
-      </c>
-      <c r="L441" s="27"/>
+      <c r="A441" s="20"/>
     </row>
     <row r="442" spans="1:12">
       <c r="A442" s="20" t="s">
-        <v>335</v>
-      </c>
-      <c r="E442" s="22">
-        <f>IF(D442="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F442" s="23" t="str">
-        <f>IF(OR(E442="",E442="!!!"),"",IF(NOT(ISNA(VLOOKUP(E442,E$1:E441,1,FALSE()))),"OLD",IF(AND(E442&lt;&gt;"",E442&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G442" s="24" t="str">
-        <f>IF(OR(E442="",E442="!!!"),"",IF(OR(J442=0,AND(J442=1,K442=1),AND(J442=1,I442="SBJ"),AND(J442=1,I442=0)),"?IN_FOCUS",IF(J442&lt;=2,"?ACTIVATED",IF(J442&lt;&gt;"","?FAMILIAR",IF(F442="NEW",IF(ISNA(VLOOKUP(E442,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H442" s="25" t="str">
-        <f>IF(J442&lt;&gt;1,"",IF(I442="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I442" s="26" t="str">
-        <f>IF(OR(E442="",E442="!!!",F442="NEW"),"",INDEX(B441:B$2,-1+SUMPRODUCT(MAX(ROW(E441:E$2)*(E442=E441:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J442" s="26" t="str">
-        <f>IF(OR(E442="",E442="!!!",F442="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E442)*(E442=E$2:E442)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E441)*(E2=E$1:E441))))))</f>
-        <v> </v>
-      </c>
-      <c r="K442" s="26" t="str">
-        <f>IF(OR(E442="",E442="!!!",F442="NEW"),"",INDEX(J$1:J441,SUMPRODUCT(MAX(ROW(E$1:E441)*(E442=E$1:E441)))))</f>
-        <v> </v>
-      </c>
-      <c r="L442" s="27"/>
+        <v>338</v>
+      </c>
     </row>
     <row r="443" spans="1:12">
       <c r="A443" s="20" t="s">
-        <v>336</v>
+        <v>227</v>
       </c>
       <c r="B443" s="21" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="C443" s="21" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E443" s="22">
         <f>IF(D443="?OLD","!!!","")</f>
@@ -17068,7 +17045,7 @@
     </row>
     <row r="444" spans="1:12">
       <c r="A444" s="20" t="s">
-        <v>118</v>
+        <v>339</v>
       </c>
       <c r="E444" s="22">
         <f>IF(D444="?OLD","!!!","")</f>
@@ -17102,7 +17079,13 @@
     </row>
     <row r="445" spans="1:12">
       <c r="A445" s="20" t="s">
-        <v>337</v>
+        <v>340</v>
+      </c>
+      <c r="B445" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C445" s="21" t="s">
+        <v>91</v>
       </c>
       <c r="E445" s="22">
         <f>IF(D445="?OLD","!!!","")</f>
@@ -17136,7 +17119,7 @@
     </row>
     <row r="446" spans="1:12">
       <c r="A446" s="20" t="s">
-        <v>325</v>
+        <v>122</v>
       </c>
       <c r="E446" s="22">
         <f>IF(D446="?OLD","!!!","")</f>
@@ -17170,13 +17153,7 @@
     </row>
     <row r="447" spans="1:12">
       <c r="A447" s="20" t="s">
-        <v>338</v>
-      </c>
-      <c r="B447" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="C447" s="21" t="s">
-        <v>123</v>
+        <v>341</v>
       </c>
       <c r="E447" s="22">
         <f>IF(D447="?OLD","!!!","")</f>
@@ -17210,7 +17187,7 @@
     </row>
     <row r="448" spans="1:12">
       <c r="A448" s="20" t="s">
-        <v>173</v>
+        <v>329</v>
       </c>
       <c r="E448" s="22">
         <f>IF(D448="?OLD","!!!","")</f>
@@ -17244,7 +17221,13 @@
     </row>
     <row r="449" spans="1:12">
       <c r="A449" s="20" t="s">
-        <v>97</v>
+        <v>342</v>
+      </c>
+      <c r="B449" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="C449" s="21" t="s">
+        <v>127</v>
       </c>
       <c r="E449" s="22">
         <f>IF(D449="?OLD","!!!","")</f>
@@ -17278,16 +17261,7 @@
     </row>
     <row r="450" spans="1:12">
       <c r="A450" s="20" t="s">
-        <v>339</v>
-      </c>
-      <c r="B450" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="C450" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D450" s="21" t="s">
-        <v>100</v>
+        <v>177</v>
       </c>
       <c r="E450" s="22">
         <f>IF(D450="?OLD","!!!","")</f>
@@ -17321,7 +17295,7 @@
     </row>
     <row r="451" spans="1:12">
       <c r="A451" s="20" t="s">
-        <v>340</v>
+        <v>100</v>
       </c>
       <c r="E451" s="22">
         <f>IF(D451="?OLD","!!!","")</f>
@@ -17355,13 +17329,16 @@
     </row>
     <row r="452" spans="1:12">
       <c r="A452" s="20" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B452" s="21" t="s">
         <v>102</v>
       </c>
       <c r="C452" s="21" t="s">
-        <v>88</v>
+        <v>103</v>
+      </c>
+      <c r="D452" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="E452" s="22">
         <f>IF(D452="?OLD","!!!","")</f>
@@ -17395,7 +17372,7 @@
     </row>
     <row r="453" spans="1:12">
       <c r="A453" s="20" t="s">
-        <v>173</v>
+        <v>344</v>
       </c>
       <c r="E453" s="22">
         <f>IF(D453="?OLD","!!!","")</f>
@@ -17429,7 +17406,13 @@
     </row>
     <row r="454" spans="1:12">
       <c r="A454" s="20" t="s">
-        <v>97</v>
+        <v>345</v>
+      </c>
+      <c r="B454" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C454" s="21" t="s">
+        <v>91</v>
       </c>
       <c r="E454" s="22">
         <f>IF(D454="?OLD","!!!","")</f>
@@ -17463,16 +17446,7 @@
     </row>
     <row r="455" spans="1:12">
       <c r="A455" s="20" t="s">
-        <v>342</v>
-      </c>
-      <c r="B455" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C455" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D455" s="21" t="s">
-        <v>100</v>
+        <v>177</v>
       </c>
       <c r="E455" s="22">
         <f>IF(D455="?OLD","!!!","")</f>
@@ -17506,7 +17480,7 @@
     </row>
     <row r="456" spans="1:12">
       <c r="A456" s="20" t="s">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="E456" s="22">
         <f>IF(D456="?OLD","!!!","")</f>
@@ -17539,7 +17513,84 @@
       <c r="L456" s="27"/>
     </row>
     <row r="457" spans="1:12">
-      <c r="A457" s="20"/>
+      <c r="A457" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="B457" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C457" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D457" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="E457" s="22">
+        <f>IF(D457="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F457" s="23" t="str">
+        <f>IF(OR(E457="",E457="!!!"),"",IF(NOT(ISNA(VLOOKUP(E457,E$1:E456,1,FALSE()))),"OLD",IF(AND(E457&lt;&gt;"",E457&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G457" s="24" t="str">
+        <f>IF(OR(E457="",E457="!!!"),"",IF(OR(J457=0,AND(J457=1,K457=1),AND(J457=1,I457="SBJ"),AND(J457=1,I457=0)),"?IN_FOCUS",IF(J457&lt;=2,"?ACTIVATED",IF(J457&lt;&gt;"","?FAMILIAR",IF(F457="NEW",IF(ISNA(VLOOKUP(E457,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H457" s="25" t="str">
+        <f>IF(J457&lt;&gt;1,"",IF(I457="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I457" s="26" t="str">
+        <f>IF(OR(E457="",E457="!!!",F457="NEW"),"",INDEX(B456:B$2,-1+SUMPRODUCT(MAX(ROW(E456:E$2)*(E457=E456:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J457" s="26" t="str">
+        <f>IF(OR(E457="",E457="!!!",F457="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E457)*(E457=E$2:E457)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E456)*(E2=E$1:E456))))))</f>
+        <v> </v>
+      </c>
+      <c r="K457" s="26" t="str">
+        <f>IF(OR(E457="",E457="!!!",F457="NEW"),"",INDEX(J$1:J456,SUMPRODUCT(MAX(ROW(E$1:E456)*(E457=E$1:E456)))))</f>
+        <v> </v>
+      </c>
+      <c r="L457" s="27"/>
+    </row>
+    <row r="458" spans="1:12">
+      <c r="A458" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="E458" s="22">
+        <f>IF(D458="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F458" s="23" t="str">
+        <f>IF(OR(E458="",E458="!!!"),"",IF(NOT(ISNA(VLOOKUP(E458,E$1:E457,1,FALSE()))),"OLD",IF(AND(E458&lt;&gt;"",E458&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G458" s="24" t="str">
+        <f>IF(OR(E458="",E458="!!!"),"",IF(OR(J458=0,AND(J458=1,K458=1),AND(J458=1,I458="SBJ"),AND(J458=1,I458=0)),"?IN_FOCUS",IF(J458&lt;=2,"?ACTIVATED",IF(J458&lt;&gt;"","?FAMILIAR",IF(F458="NEW",IF(ISNA(VLOOKUP(E458,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H458" s="25" t="str">
+        <f>IF(J458&lt;&gt;1,"",IF(I458="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I458" s="26" t="str">
+        <f>IF(OR(E458="",E458="!!!",F458="NEW"),"",INDEX(B457:B$2,-1+SUMPRODUCT(MAX(ROW(E457:E$2)*(E458=E457:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J458" s="26" t="str">
+        <f>IF(OR(E458="",E458="!!!",F458="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E458)*(E458=E$2:E458)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E457)*(E2=E$1:E457))))))</f>
+        <v> </v>
+      </c>
+      <c r="K458" s="26" t="str">
+        <f>IF(OR(E458="",E458="!!!",F458="NEW"),"",INDEX(J$1:J457,SUMPRODUCT(MAX(ROW(E$1:E457)*(E458=E$1:E457)))))</f>
+        <v> </v>
+      </c>
+      <c r="L458" s="27"/>
+    </row>
+    <row r="459" spans="1:12">
+      <c r="A459" s="20"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
